--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2263"/>
+  <dimension ref="A1:J2312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -86009,6 +86009,1863 @@
         <v>46023</v>
       </c>
     </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>A One Ispat Private Ltd</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2264">
+        <v>2619245</v>
+      </c>
+      <c r="D2264">
+        <v>471464.1</v>
+      </c>
+      <c r="E2264">
+        <v>3090710</v>
+      </c>
+      <c r="F2264">
+        <v>331.55</v>
+      </c>
+      <c r="G2264">
+        <v>7900.000000000001</v>
+      </c>
+      <c r="H2264">
+        <v>9</v>
+      </c>
+      <c r="I2264" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2264" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>Pushpit Steels Private Limited</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2265">
+        <v>2821971</v>
+      </c>
+      <c r="D2265">
+        <v>507954.84</v>
+      </c>
+      <c r="E2265">
+        <v>3329926</v>
+      </c>
+      <c r="F2265">
+        <v>316.14</v>
+      </c>
+      <c r="G2265">
+        <v>8926.333270070223</v>
+      </c>
+      <c r="H2265">
+        <v>12</v>
+      </c>
+      <c r="I2265" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2265" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2266">
+        <v>2602445</v>
+      </c>
+      <c r="D2266">
+        <v>468440.1</v>
+      </c>
+      <c r="E2266">
+        <v>3070887</v>
+      </c>
+      <c r="F2266">
+        <v>306.17</v>
+      </c>
+      <c r="G2266">
+        <v>8500.000000000002</v>
+      </c>
+      <c r="H2266">
+        <v>13</v>
+      </c>
+      <c r="I2266" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2266" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>Arun Vyapar Udyog Private Limited</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2267">
+        <v>1737705</v>
+      </c>
+      <c r="D2267">
+        <v>312786.9</v>
+      </c>
+      <c r="E2267">
+        <v>2050492</v>
+      </c>
+      <c r="F2267">
+        <v>186.85</v>
+      </c>
+      <c r="G2267">
+        <v>9300</v>
+      </c>
+      <c r="H2267">
+        <v>8</v>
+      </c>
+      <c r="I2267" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2267" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2268">
+        <v>1417803</v>
+      </c>
+      <c r="D2268">
+        <v>255204.54</v>
+      </c>
+      <c r="E2268">
+        <v>1673008</v>
+      </c>
+      <c r="F2268">
+        <v>178.34</v>
+      </c>
+      <c r="G2268">
+        <v>7950</v>
+      </c>
+      <c r="H2268">
+        <v>4</v>
+      </c>
+      <c r="I2268" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2268" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2269">
+        <v>1549269.5</v>
+      </c>
+      <c r="D2269">
+        <v>278868.51</v>
+      </c>
+      <c r="E2269">
+        <v>1828138</v>
+      </c>
+      <c r="F2269">
+        <v>171.19</v>
+      </c>
+      <c r="G2269">
+        <v>9050</v>
+      </c>
+      <c r="H2269">
+        <v>8</v>
+      </c>
+      <c r="I2269" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2269" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2270">
+        <v>1540172</v>
+      </c>
+      <c r="D2270">
+        <v>277230.96</v>
+      </c>
+      <c r="E2270">
+        <v>1817404</v>
+      </c>
+      <c r="F2270">
+        <v>167.41</v>
+      </c>
+      <c r="G2270">
+        <v>9200</v>
+      </c>
+      <c r="H2270">
+        <v>8</v>
+      </c>
+      <c r="I2270" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2270" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2271">
+        <v>1297530</v>
+      </c>
+      <c r="D2271">
+        <v>247942.08</v>
+      </c>
+      <c r="E2271">
+        <v>1625398</v>
+      </c>
+      <c r="F2271">
+        <v>166.35</v>
+      </c>
+      <c r="G2271">
+        <v>7800</v>
+      </c>
+      <c r="H2271">
+        <v>7</v>
+      </c>
+      <c r="I2271" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2271" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2272">
+        <v>1381968</v>
+      </c>
+      <c r="D2272">
+        <v>248754.24</v>
+      </c>
+      <c r="E2272">
+        <v>1630723</v>
+      </c>
+      <c r="F2272">
+        <v>164.52</v>
+      </c>
+      <c r="G2272">
+        <v>8400</v>
+      </c>
+      <c r="H2272">
+        <v>7</v>
+      </c>
+      <c r="I2272" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2272" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2273">
+        <v>1213758</v>
+      </c>
+      <c r="D2273">
+        <v>218476.44</v>
+      </c>
+      <c r="E2273">
+        <v>1432234</v>
+      </c>
+      <c r="F2273">
+        <v>155.61</v>
+      </c>
+      <c r="G2273">
+        <v>7799.999999999999</v>
+      </c>
+      <c r="H2273">
+        <v>4</v>
+      </c>
+      <c r="I2273" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2273" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>Adishakti Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2274">
+        <v>1224026</v>
+      </c>
+      <c r="D2274">
+        <v>232276.68</v>
+      </c>
+      <c r="E2274">
+        <v>1444350.86</v>
+      </c>
+      <c r="F2274">
+        <v>154.94</v>
+      </c>
+      <c r="G2274">
+        <v>7900</v>
+      </c>
+      <c r="H2274">
+        <v>4</v>
+      </c>
+      <c r="I2274" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2274" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>SREE SAI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2275">
+        <v>341251</v>
+      </c>
+      <c r="D2275">
+        <v>17062.55</v>
+      </c>
+      <c r="E2275">
+        <v>358316</v>
+      </c>
+      <c r="F2275">
+        <v>148.37</v>
+      </c>
+      <c r="G2275">
+        <v>2300</v>
+      </c>
+      <c r="H2275">
+        <v>7</v>
+      </c>
+      <c r="I2275" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2275" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2276">
+        <v>1057680</v>
+      </c>
+      <c r="D2276">
+        <v>190382.4</v>
+      </c>
+      <c r="E2276">
+        <v>1248063</v>
+      </c>
+      <c r="F2276">
+        <v>135.6</v>
+      </c>
+      <c r="G2276">
+        <v>7799.999999999999</v>
+      </c>
+      <c r="H2276">
+        <v>6</v>
+      </c>
+      <c r="I2276" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2276" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>KUBAIR STEEL AND POWER LLP</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2277">
+        <v>1007200</v>
+      </c>
+      <c r="D2277">
+        <v>181296</v>
+      </c>
+      <c r="E2277">
+        <v>1188497</v>
+      </c>
+      <c r="F2277">
+        <v>125.9</v>
+      </c>
+      <c r="G2277">
+        <v>7999.999999999999</v>
+      </c>
+      <c r="H2277">
+        <v>3</v>
+      </c>
+      <c r="I2277" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2277" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>Prime Gold International Limited</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2278">
+        <v>1010999.5</v>
+      </c>
+      <c r="D2278">
+        <v>181979.91</v>
+      </c>
+      <c r="E2278">
+        <v>1192980</v>
+      </c>
+      <c r="F2278">
+        <v>125.59</v>
+      </c>
+      <c r="G2278">
+        <v>8050</v>
+      </c>
+      <c r="H2278">
+        <v>6</v>
+      </c>
+      <c r="I2278" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2278" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2279">
+        <v>936092</v>
+      </c>
+      <c r="D2279">
+        <v>186130.26</v>
+      </c>
+      <c r="E2279">
+        <v>1104588.28</v>
+      </c>
+      <c r="F2279">
+        <v>123.17</v>
+      </c>
+      <c r="G2279">
+        <v>7600</v>
+      </c>
+      <c r="H2279">
+        <v>4</v>
+      </c>
+      <c r="I2279" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2279" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>Shri Tirupati Steel Cast Ltd</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2280">
+        <v>368928</v>
+      </c>
+      <c r="D2280">
+        <v>66407.04000000001</v>
+      </c>
+      <c r="E2280">
+        <v>435335</v>
+      </c>
+      <c r="F2280">
+        <v>115.29</v>
+      </c>
+      <c r="G2280">
+        <v>3200</v>
+      </c>
+      <c r="H2280">
+        <v>6</v>
+      </c>
+      <c r="I2280" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2280" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>TEXCON STEELS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2281">
+        <v>741433</v>
+      </c>
+      <c r="D2281">
+        <v>133457.94</v>
+      </c>
+      <c r="E2281">
+        <v>874891</v>
+      </c>
+      <c r="F2281">
+        <v>96.28999999999999</v>
+      </c>
+      <c r="G2281">
+        <v>7700.000000000001</v>
+      </c>
+      <c r="H2281">
+        <v>4</v>
+      </c>
+      <c r="I2281" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2281" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2282">
+        <v>701454</v>
+      </c>
+      <c r="D2282">
+        <v>126261.72</v>
+      </c>
+      <c r="E2282">
+        <v>827716</v>
+      </c>
+      <c r="F2282">
+        <v>89.93000000000001</v>
+      </c>
+      <c r="G2282">
+        <v>7799.999999999999</v>
+      </c>
+      <c r="H2282">
+        <v>2</v>
+      </c>
+      <c r="I2282" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2282" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2283">
+        <v>697135.5</v>
+      </c>
+      <c r="D2283">
+        <v>125484.4</v>
+      </c>
+      <c r="E2283">
+        <v>822620</v>
+      </c>
+      <c r="F2283">
+        <v>87.69</v>
+      </c>
+      <c r="G2283">
+        <v>7950</v>
+      </c>
+      <c r="H2283">
+        <v>2</v>
+      </c>
+      <c r="I2283" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2283" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>KAMACHI INDUSTRIES LIMITED</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2284">
+        <v>807240</v>
+      </c>
+      <c r="D2284">
+        <v>145303.2</v>
+      </c>
+      <c r="E2284">
+        <v>952543</v>
+      </c>
+      <c r="F2284">
+        <v>86.8</v>
+      </c>
+      <c r="G2284">
+        <v>9300</v>
+      </c>
+      <c r="H2284">
+        <v>4</v>
+      </c>
+      <c r="I2284" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2284" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>Mahrishi Alloys Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2285">
+        <v>321525</v>
+      </c>
+      <c r="D2285">
+        <v>57874.52</v>
+      </c>
+      <c r="E2285">
+        <v>379399</v>
+      </c>
+      <c r="F2285">
+        <v>85.73999999999999</v>
+      </c>
+      <c r="G2285">
+        <v>3750</v>
+      </c>
+      <c r="H2285">
+        <v>2</v>
+      </c>
+      <c r="I2285" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2285" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2286">
+        <v>671421</v>
+      </c>
+      <c r="D2286">
+        <v>120855.78</v>
+      </c>
+      <c r="E2286">
+        <v>792276</v>
+      </c>
+      <c r="F2286">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="G2286">
+        <v>7900.000000000001</v>
+      </c>
+      <c r="H2286">
+        <v>4</v>
+      </c>
+      <c r="I2286" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2286" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2287">
+        <v>335403</v>
+      </c>
+      <c r="D2287">
+        <v>60372.54</v>
+      </c>
+      <c r="E2287">
+        <v>395775.96</v>
+      </c>
+      <c r="F2287">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="G2287">
+        <v>4150</v>
+      </c>
+      <c r="H2287">
+        <v>4</v>
+      </c>
+      <c r="I2287" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2287" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2288">
+        <v>102859.24</v>
+      </c>
+      <c r="D2288">
+        <v>5142.98</v>
+      </c>
+      <c r="E2288">
+        <v>114864.2232</v>
+      </c>
+      <c r="F2288">
+        <v>70.21000000000001</v>
+      </c>
+      <c r="G2288">
+        <v>1465.022646346674</v>
+      </c>
+      <c r="H2288">
+        <v>4</v>
+      </c>
+      <c r="I2288" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2288" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>KAIRAV STEELS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2289">
+        <v>424216.5</v>
+      </c>
+      <c r="D2289">
+        <v>76358.97</v>
+      </c>
+      <c r="E2289">
+        <v>500576</v>
+      </c>
+      <c r="F2289">
+        <v>65.77</v>
+      </c>
+      <c r="G2289">
+        <v>6450</v>
+      </c>
+      <c r="H2289">
+        <v>3</v>
+      </c>
+      <c r="I2289" t="inlineStr">
+        <is>
+          <t>Sunil Rathi</t>
+        </is>
+      </c>
+      <c r="J2289" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>E RAMAMURTHY MINERALS AND METALS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2290">
+        <v>483960</v>
+      </c>
+      <c r="D2290">
+        <v>94885.2</v>
+      </c>
+      <c r="E2290">
+        <v>571072.6</v>
+      </c>
+      <c r="F2290">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="G2290">
+        <v>7400</v>
+      </c>
+      <c r="H2290">
+        <v>3</v>
+      </c>
+      <c r="I2290" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2290" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2291">
+        <v>466960</v>
+      </c>
+      <c r="D2291">
+        <v>91965.96000000001</v>
+      </c>
+      <c r="E2291">
+        <v>551013</v>
+      </c>
+      <c r="F2291">
+        <v>58.37</v>
+      </c>
+      <c r="G2291">
+        <v>7999.999999999999</v>
+      </c>
+      <c r="H2291">
+        <v>2</v>
+      </c>
+      <c r="I2291" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2291" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2292">
+        <v>397607</v>
+      </c>
+      <c r="D2292">
+        <v>72133.74000000001</v>
+      </c>
+      <c r="E2292">
+        <v>469176.56</v>
+      </c>
+      <c r="F2292">
+        <v>50.33</v>
+      </c>
+      <c r="G2292">
+        <v>7900</v>
+      </c>
+      <c r="H2292">
+        <v>4</v>
+      </c>
+      <c r="I2292" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2292" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>Keshree Metalurgies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2293">
+        <v>398475</v>
+      </c>
+      <c r="D2293">
+        <v>71725.5</v>
+      </c>
+      <c r="E2293">
+        <v>470201</v>
+      </c>
+      <c r="F2293">
+        <v>45.54</v>
+      </c>
+      <c r="G2293">
+        <v>8750</v>
+      </c>
+      <c r="H2293">
+        <v>2</v>
+      </c>
+      <c r="I2293" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2293" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2294">
+        <v>272670</v>
+      </c>
+      <c r="D2294">
+        <v>49080.6</v>
+      </c>
+      <c r="E2294">
+        <v>321751</v>
+      </c>
+      <c r="F2294">
+        <v>44.7</v>
+      </c>
+      <c r="G2294">
+        <v>6100</v>
+      </c>
+      <c r="H2294">
+        <v>2</v>
+      </c>
+      <c r="I2294" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2294" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>Sri M.S.T. Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2295">
+        <v>317772</v>
+      </c>
+      <c r="D2295">
+        <v>57198.96</v>
+      </c>
+      <c r="E2295">
+        <v>374971</v>
+      </c>
+      <c r="F2295">
+        <v>40.73999999999999</v>
+      </c>
+      <c r="G2295">
+        <v>7800.000000000001</v>
+      </c>
+      <c r="H2295">
+        <v>2</v>
+      </c>
+      <c r="I2295" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2295" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2296">
+        <v>113274</v>
+      </c>
+      <c r="D2296">
+        <v>20389.32</v>
+      </c>
+      <c r="E2296">
+        <v>133663</v>
+      </c>
+      <c r="F2296">
+        <v>35.96</v>
+      </c>
+      <c r="G2296">
+        <v>3150</v>
+      </c>
+      <c r="H2296">
+        <v>1</v>
+      </c>
+      <c r="I2296" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2296" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Limited</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2297">
+        <v>149722.4</v>
+      </c>
+      <c r="D2297">
+        <v>7486.12</v>
+      </c>
+      <c r="E2297">
+        <v>157209</v>
+      </c>
+      <c r="F2297">
+        <v>34.34</v>
+      </c>
+      <c r="G2297">
+        <v>4359.999999999999</v>
+      </c>
+      <c r="H2297">
+        <v>1</v>
+      </c>
+      <c r="I2297" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2297" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>BMM ISPAT LIMITED</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2298">
+        <v>227200</v>
+      </c>
+      <c r="D2298">
+        <v>40896</v>
+      </c>
+      <c r="E2298">
+        <v>268096</v>
+      </c>
+      <c r="F2298">
+        <v>32</v>
+      </c>
+      <c r="G2298">
+        <v>7100</v>
+      </c>
+      <c r="H2298">
+        <v>1</v>
+      </c>
+      <c r="I2298" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2298" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2299">
+        <v>105156</v>
+      </c>
+      <c r="D2299">
+        <v>18928.08</v>
+      </c>
+      <c r="E2299">
+        <v>124084</v>
+      </c>
+      <c r="F2299">
+        <v>30.48</v>
+      </c>
+      <c r="G2299">
+        <v>3450</v>
+      </c>
+      <c r="H2299">
+        <v>1</v>
+      </c>
+      <c r="I2299" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2299" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>KUTTIPPULAN IRON AND STEEL COMPANY PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2300">
+        <v>188874</v>
+      </c>
+      <c r="D2300">
+        <v>33997.32</v>
+      </c>
+      <c r="E2300">
+        <v>222871</v>
+      </c>
+      <c r="F2300">
+        <v>29.98</v>
+      </c>
+      <c r="G2300">
+        <v>6300</v>
+      </c>
+      <c r="H2300">
+        <v>1</v>
+      </c>
+      <c r="I2300" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2300" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2301">
+        <v>161847</v>
+      </c>
+      <c r="D2301">
+        <v>29132.46</v>
+      </c>
+      <c r="E2301">
+        <v>190980</v>
+      </c>
+      <c r="F2301">
+        <v>25.69</v>
+      </c>
+      <c r="G2301">
+        <v>6300</v>
+      </c>
+      <c r="H2301">
+        <v>1</v>
+      </c>
+      <c r="I2301" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2301" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>Adishakti Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2302">
+        <v>66400</v>
+      </c>
+      <c r="D2302">
+        <v>0</v>
+      </c>
+      <c r="E2302">
+        <v>78352</v>
+      </c>
+      <c r="F2302">
+        <v>20.75</v>
+      </c>
+      <c r="G2302">
+        <v>3200</v>
+      </c>
+      <c r="H2302">
+        <v>2</v>
+      </c>
+      <c r="I2302" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2302" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2303">
+        <v>133584</v>
+      </c>
+      <c r="D2303">
+        <v>24045.12</v>
+      </c>
+      <c r="E2303">
+        <v>157629</v>
+      </c>
+      <c r="F2303">
+        <v>20.24</v>
+      </c>
+      <c r="G2303">
+        <v>6600.000000000001</v>
+      </c>
+      <c r="H2303">
+        <v>1</v>
+      </c>
+      <c r="I2303" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2303" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2304">
+        <v>63342</v>
+      </c>
+      <c r="D2304">
+        <v>3488.4</v>
+      </c>
+      <c r="E2304">
+        <v>74744.16</v>
+      </c>
+      <c r="F2304">
+        <v>18.63</v>
+      </c>
+      <c r="G2304">
+        <v>3400</v>
+      </c>
+      <c r="H2304">
+        <v>2</v>
+      </c>
+      <c r="I2304" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2304" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>PRINCE ALLOYS (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2305">
+        <v>98595</v>
+      </c>
+      <c r="D2305">
+        <v>17747.1</v>
+      </c>
+      <c r="E2305">
+        <v>116342</v>
+      </c>
+      <c r="F2305">
+        <v>15.65</v>
+      </c>
+      <c r="G2305">
+        <v>6300</v>
+      </c>
+      <c r="H2305">
+        <v>1</v>
+      </c>
+      <c r="I2305" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2305" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>PRINCE ROLLINGS  (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2306">
+        <v>98280</v>
+      </c>
+      <c r="D2306">
+        <v>17690.4</v>
+      </c>
+      <c r="E2306">
+        <v>115970</v>
+      </c>
+      <c r="F2306">
+        <v>15.6</v>
+      </c>
+      <c r="G2306">
+        <v>6300</v>
+      </c>
+      <c r="H2306">
+        <v>1</v>
+      </c>
+      <c r="I2306" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2306" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2307">
+        <v>97965</v>
+      </c>
+      <c r="D2307">
+        <v>0</v>
+      </c>
+      <c r="E2307">
+        <v>115598.7</v>
+      </c>
+      <c r="F2307">
+        <v>15.55</v>
+      </c>
+      <c r="G2307">
+        <v>6300</v>
+      </c>
+      <c r="H2307">
+        <v>1</v>
+      </c>
+      <c r="I2307" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2307" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>E RAMAMURTHY MINERALS AND METALS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2308">
+        <v>43180</v>
+      </c>
+      <c r="D2308">
+        <v>0</v>
+      </c>
+      <c r="E2308">
+        <v>50952.39999999999</v>
+      </c>
+      <c r="F2308">
+        <v>10.16</v>
+      </c>
+      <c r="G2308">
+        <v>4250</v>
+      </c>
+      <c r="H2308">
+        <v>1</v>
+      </c>
+      <c r="I2308" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2308" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>Tundish Ramming Mix</t>
+        </is>
+      </c>
+      <c r="C2309">
+        <v>270000</v>
+      </c>
+      <c r="D2309">
+        <v>48600</v>
+      </c>
+      <c r="E2309">
+        <v>318600</v>
+      </c>
+      <c r="F2309">
+        <v>10</v>
+      </c>
+      <c r="G2309">
+        <v>27000</v>
+      </c>
+      <c r="H2309">
+        <v>2</v>
+      </c>
+      <c r="I2309" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2309" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2310">
+        <v>23680</v>
+      </c>
+      <c r="D2310">
+        <v>3697.92</v>
+      </c>
+      <c r="E2310">
+        <v>27942.48</v>
+      </c>
+      <c r="F2310">
+        <v>7.4</v>
+      </c>
+      <c r="G2310">
+        <v>3200</v>
+      </c>
+      <c r="H2310">
+        <v>2</v>
+      </c>
+      <c r="I2310" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2310" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C2311">
+        <v>250200</v>
+      </c>
+      <c r="D2311">
+        <v>45036</v>
+      </c>
+      <c r="E2311">
+        <v>295236</v>
+      </c>
+      <c r="F2311">
+        <v>1.8</v>
+      </c>
+      <c r="G2311">
+        <v>139000</v>
+      </c>
+      <c r="H2311">
+        <v>4</v>
+      </c>
+      <c r="I2311" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2311" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>SAMKRG PISTONS AND RINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2312">
+        <v>8000</v>
+      </c>
+      <c r="D2312">
+        <v>1440</v>
+      </c>
+      <c r="E2312">
+        <v>9440</v>
+      </c>
+      <c r="F2312">
+        <v>1</v>
+      </c>
+      <c r="G2312">
+        <v>8000</v>
+      </c>
+      <c r="H2312">
+        <v>1</v>
+      </c>
+      <c r="I2312" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2312" s="2">
+        <v>46054</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2373"/>
+  <dimension ref="A1:J2374"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -87907,7 +87907,7 @@
     <row r="2314">
       <c r="A2314" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+          <t>A One Ispat Private Ltd</t>
         </is>
       </c>
       <c r="B2314" t="inlineStr">
@@ -87916,22 +87916,22 @@
         </is>
       </c>
       <c r="C2314">
-        <v>2285386.5</v>
+        <v>2470014</v>
       </c>
       <c r="D2314">
-        <v>411369.57</v>
+        <v>444602.52</v>
       </c>
       <c r="E2314">
-        <v>2696756</v>
+        <v>2914617.56</v>
       </c>
       <c r="F2314">
-        <v>287.47</v>
+        <v>312.66</v>
       </c>
       <c r="G2314">
-        <v>7950.000000000001</v>
+        <v>7900</v>
       </c>
       <c r="H2314">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2314" t="inlineStr">
         <is>
@@ -87945,7 +87945,7 @@
     <row r="2315">
       <c r="A2315" t="inlineStr">
         <is>
-          <t>A One Ispat Private Ltd</t>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
         </is>
       </c>
       <c r="B2315" t="inlineStr">
@@ -87954,22 +87954,22 @@
         </is>
       </c>
       <c r="C2315">
-        <v>2189722</v>
+        <v>2285386.5</v>
       </c>
       <c r="D2315">
-        <v>394149.96</v>
+        <v>411369.57</v>
       </c>
       <c r="E2315">
-        <v>2583873</v>
+        <v>2696756</v>
       </c>
       <c r="F2315">
-        <v>277.18</v>
+        <v>287.47</v>
       </c>
       <c r="G2315">
-        <v>7900</v>
+        <v>7950.000000000001</v>
       </c>
       <c r="H2315">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2315" t="inlineStr">
         <is>
@@ -88021,7 +88021,7 @@
     <row r="2317">
       <c r="A2317" t="inlineStr">
         <is>
-          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+          <t>KUBAIR STEEL AND POWER LLP</t>
         </is>
       </c>
       <c r="B2317" t="inlineStr">
@@ -88030,26 +88030,26 @@
         </is>
       </c>
       <c r="C2317">
-        <v>1487910.5</v>
+        <v>1310180</v>
       </c>
       <c r="D2317">
-        <v>267823.89</v>
+        <v>235832.4</v>
       </c>
       <c r="E2317">
-        <v>1755733</v>
+        <v>1546012.6</v>
       </c>
       <c r="F2317">
-        <v>164.41</v>
+        <v>166.82</v>
       </c>
       <c r="G2317">
-        <v>9050</v>
+        <v>7853.85445390241</v>
       </c>
       <c r="H2317">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I2317" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2317" s="2">
@@ -88059,7 +88059,7 @@
     <row r="2318">
       <c r="A2318" t="inlineStr">
         <is>
-          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
         </is>
       </c>
       <c r="B2318" t="inlineStr">
@@ -88068,26 +88068,26 @@
         </is>
       </c>
       <c r="C2318">
-        <v>1269138</v>
+        <v>1487910.5</v>
       </c>
       <c r="D2318">
-        <v>258939.36</v>
+        <v>267823.89</v>
       </c>
       <c r="E2318">
-        <v>1619517.36</v>
+        <v>1755733</v>
       </c>
       <c r="F2318">
-        <v>162.71</v>
+        <v>164.41</v>
       </c>
       <c r="G2318">
-        <v>7800.000000000001</v>
+        <v>9050</v>
       </c>
       <c r="H2318">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2318" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2318" s="2">
@@ -88097,7 +88097,7 @@
     <row r="2319">
       <c r="A2319" t="inlineStr">
         <is>
-          <t>KUBAIR STEEL AND POWER LLP</t>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2319" t="inlineStr">
@@ -88106,22 +88106,22 @@
         </is>
       </c>
       <c r="C2319">
-        <v>1292160</v>
+        <v>1269138</v>
       </c>
       <c r="D2319">
-        <v>232588.8</v>
+        <v>258939.36</v>
       </c>
       <c r="E2319">
-        <v>1524749</v>
+        <v>1619517.36</v>
       </c>
       <c r="F2319">
-        <v>161.52</v>
+        <v>162.71</v>
       </c>
       <c r="G2319">
-        <v>7999.999999999999</v>
+        <v>7800.000000000001</v>
       </c>
       <c r="H2319">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2319" t="inlineStr">
         <is>
@@ -89873,7 +89873,7 @@
       </c>
       <c r="I2365" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2365" s="2">
@@ -89883,35 +89883,35 @@
     <row r="2366">
       <c r="A2366" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
         </is>
       </c>
       <c r="B2366" t="inlineStr">
         <is>
-          <t>Tundish Ramming Mix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2366">
-        <v>135000</v>
+        <v>19754</v>
       </c>
       <c r="D2366">
-        <v>24300</v>
+        <v>3555.72</v>
       </c>
       <c r="E2366">
-        <v>159300</v>
+        <v>23309.72</v>
       </c>
       <c r="F2366">
-        <v>5</v>
+        <v>5.81</v>
       </c>
       <c r="G2366">
-        <v>27000</v>
+        <v>3400</v>
       </c>
       <c r="H2366">
         <v>1</v>
       </c>
       <c r="I2366" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2366" s="2">
@@ -89921,35 +89921,35 @@
     <row r="2367">
       <c r="A2367" t="inlineStr">
         <is>
-          <t>ADRI STEEL PRIVATE LIMITED</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2367" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Tundish Ramming Mix</t>
         </is>
       </c>
       <c r="C2367">
-        <v>15744</v>
+        <v>135000</v>
       </c>
       <c r="D2367">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="E2367">
-        <v>18577.92</v>
+        <v>159300</v>
       </c>
       <c r="F2367">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="G2367">
-        <v>3200</v>
+        <v>27000</v>
       </c>
       <c r="H2367">
         <v>1</v>
       </c>
       <c r="I2367" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2367" s="2">
@@ -89959,26 +89959,31 @@
     <row r="2368">
       <c r="A2368" t="inlineStr">
         <is>
-          <t>Mahrishi Meltchems Pvt Ltd</t>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2368">
-        <v>556000</v>
+        <v>15744</v>
       </c>
       <c r="D2368">
-        <v>100080</v>
+        <v>0</v>
       </c>
       <c r="E2368">
-        <v>656080</v>
+        <v>18577.92</v>
       </c>
       <c r="F2368">
-        <v>4</v>
+        <v>4.92</v>
       </c>
       <c r="G2368">
-        <v>139000</v>
+        <v>3200</v>
       </c>
       <c r="H2368">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2368" t="inlineStr">
         <is>
@@ -89996,22 +90001,22 @@
         </is>
       </c>
       <c r="C2369">
-        <v>1145500</v>
+        <v>556000</v>
       </c>
       <c r="D2369">
-        <v>206190</v>
+        <v>100080</v>
       </c>
       <c r="E2369">
-        <v>1351690</v>
+        <v>656080</v>
       </c>
       <c r="F2369">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G2369">
-        <v>327285.7142857143</v>
+        <v>139000</v>
       </c>
       <c r="H2369">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2369" t="inlineStr">
         <is>
@@ -90025,31 +90030,26 @@
     <row r="2370">
       <c r="A2370" t="inlineStr">
         <is>
-          <t>SNAM ALLOYS PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="B2370" t="inlineStr">
-        <is>
-          <t>Ordinary Ramming Mass</t>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
         </is>
       </c>
       <c r="C2370">
-        <v>11836</v>
+        <v>1145500</v>
       </c>
       <c r="D2370">
-        <v>29098.08</v>
+        <v>206190</v>
       </c>
       <c r="E2370">
-        <v>13966.48</v>
+        <v>1351690</v>
       </c>
       <c r="F2370">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="G2370">
-        <v>4400</v>
+        <v>327285.7142857143</v>
       </c>
       <c r="H2370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2370" t="inlineStr">
         <is>
@@ -90063,28 +90063,28 @@
     <row r="2371">
       <c r="A2371" t="inlineStr">
         <is>
-          <t>SRI BHAVANI CASTINGS LTD</t>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2371" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Ordinary Ramming Mass</t>
         </is>
       </c>
       <c r="C2371">
-        <v>9200</v>
+        <v>11836</v>
       </c>
       <c r="D2371">
-        <v>0</v>
+        <v>29098.08</v>
       </c>
       <c r="E2371">
-        <v>10856</v>
+        <v>13966.48</v>
       </c>
       <c r="F2371">
-        <v>1</v>
+        <v>2.69</v>
       </c>
       <c r="G2371">
-        <v>9200</v>
+        <v>4400</v>
       </c>
       <c r="H2371">
         <v>1</v>
@@ -90106,23 +90106,23 @@
       </c>
       <c r="B2372" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2372">
-        <v>10800</v>
+        <v>9200</v>
       </c>
       <c r="D2372">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="E2372">
-        <v>12744</v>
+        <v>10856</v>
       </c>
       <c r="F2372">
         <v>1</v>
       </c>
       <c r="G2372">
-        <v>10800</v>
+        <v>9200</v>
       </c>
       <c r="H2372">
         <v>1</v>
@@ -90139,23 +90139,28 @@
     <row r="2373">
       <c r="A2373" t="inlineStr">
         <is>
-          <t>RDTMT Steels India Pvt Ltd</t>
+          <t>SRI BHAVANI CASTINGS LTD</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2373">
-        <v>8500</v>
+        <v>10800</v>
       </c>
       <c r="D2373">
-        <v>1530</v>
+        <v>3600</v>
       </c>
       <c r="E2373">
-        <v>10030</v>
+        <v>12744</v>
       </c>
       <c r="F2373">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="G2373">
-        <v>170000</v>
+        <v>10800</v>
       </c>
       <c r="H2373">
         <v>1</v>
@@ -90166,6 +90171,39 @@
         </is>
       </c>
       <c r="J2373" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C2374">
+        <v>8500</v>
+      </c>
+      <c r="D2374">
+        <v>1530</v>
+      </c>
+      <c r="E2374">
+        <v>10030</v>
+      </c>
+      <c r="F2374">
+        <v>0.05</v>
+      </c>
+      <c r="G2374">
+        <v>170000</v>
+      </c>
+      <c r="H2374">
+        <v>1</v>
+      </c>
+      <c r="I2374" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2374" s="2">
         <v>46082</v>
       </c>
     </row>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J261" s="2">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J319" s="2">
@@ -87992,22 +87992,22 @@
         </is>
       </c>
       <c r="C2316">
-        <v>2034730</v>
+        <v>2336395</v>
       </c>
       <c r="D2316">
-        <v>366251.4</v>
+        <v>420551.1</v>
       </c>
       <c r="E2316">
-        <v>2400983</v>
+        <v>2756947.7</v>
       </c>
       <c r="F2316">
-        <v>239.38</v>
+        <v>274.87</v>
       </c>
       <c r="G2316">
         <v>8500</v>
       </c>
       <c r="H2316">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2316" t="inlineStr">
         <is>
@@ -88287,31 +88287,31 @@
     <row r="2324">
       <c r="A2324" t="inlineStr">
         <is>
-          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+          <t>Shri Tirupati Steel Cast Ltd</t>
         </is>
       </c>
       <c r="B2324" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2324">
-        <v>956904</v>
+        <v>397856</v>
       </c>
       <c r="D2324">
-        <v>172242.72</v>
+        <v>71614.08</v>
       </c>
       <c r="E2324">
-        <v>1129147</v>
+        <v>469471.04</v>
       </c>
       <c r="F2324">
-        <v>122.68</v>
+        <v>124.33</v>
       </c>
       <c r="G2324">
-        <v>7799.999999999999</v>
+        <v>3200</v>
       </c>
       <c r="H2324">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I2324" t="inlineStr">
         <is>
@@ -88325,7 +88325,7 @@
     <row r="2325">
       <c r="A2325" t="inlineStr">
         <is>
-          <t>KAMACHI INDUSTRIES LIMITED</t>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
         </is>
       </c>
       <c r="B2325" t="inlineStr">
@@ -88334,26 +88334,26 @@
         </is>
       </c>
       <c r="C2325">
-        <v>1136739</v>
+        <v>956904</v>
       </c>
       <c r="D2325">
-        <v>204613.02</v>
+        <v>172242.72</v>
       </c>
       <c r="E2325">
-        <v>1341353</v>
+        <v>1129147</v>
       </c>
       <c r="F2325">
-        <v>122.23</v>
+        <v>122.68</v>
       </c>
       <c r="G2325">
-        <v>9300</v>
+        <v>7799.999999999999</v>
       </c>
       <c r="H2325">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2325" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2325" s="2">
@@ -88363,7 +88363,7 @@
     <row r="2326">
       <c r="A2326" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>KAMACHI INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="B2326" t="inlineStr">
@@ -88372,19 +88372,19 @@
         </is>
       </c>
       <c r="C2326">
-        <v>1123320</v>
+        <v>1136739</v>
       </c>
       <c r="D2326">
-        <v>202197.6</v>
+        <v>204613.02</v>
       </c>
       <c r="E2326">
-        <v>1325519</v>
+        <v>1341353</v>
       </c>
       <c r="F2326">
-        <v>122.1</v>
+        <v>122.23</v>
       </c>
       <c r="G2326">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="H2326">
         <v>6</v>
@@ -88401,7 +88401,7 @@
     <row r="2327">
       <c r="A2327" t="inlineStr">
         <is>
-          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2327" t="inlineStr">
@@ -88410,26 +88410,26 @@
         </is>
       </c>
       <c r="C2327">
-        <v>910800</v>
+        <v>1123320</v>
       </c>
       <c r="D2327">
-        <v>163944</v>
+        <v>202197.6</v>
       </c>
       <c r="E2327">
-        <v>1074744</v>
+        <v>1325519</v>
       </c>
       <c r="F2327">
-        <v>113.85</v>
+        <v>122.1</v>
       </c>
       <c r="G2327">
-        <v>7999.999999999999</v>
+        <v>9200</v>
       </c>
       <c r="H2327">
         <v>6</v>
       </c>
       <c r="I2327" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2327" s="2">
@@ -88439,7 +88439,7 @@
     <row r="2328">
       <c r="A2328" t="inlineStr">
         <is>
-          <t>Minera Steel &amp; Power Pvt Ltd</t>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
         </is>
       </c>
       <c r="B2328" t="inlineStr">
@@ -88448,22 +88448,22 @@
         </is>
       </c>
       <c r="C2328">
-        <v>945000</v>
+        <v>910800</v>
       </c>
       <c r="D2328">
-        <v>170100</v>
+        <v>163944</v>
       </c>
       <c r="E2328">
-        <v>1115100</v>
+        <v>1074744</v>
       </c>
       <c r="F2328">
-        <v>112.5</v>
+        <v>113.85</v>
       </c>
       <c r="G2328">
-        <v>8400</v>
+        <v>7999.999999999999</v>
       </c>
       <c r="H2328">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I2328" t="inlineStr">
         <is>
@@ -88477,35 +88477,35 @@
     <row r="2329">
       <c r="A2329" t="inlineStr">
         <is>
-          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2329" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2329">
-        <v>707868</v>
+        <v>945000</v>
       </c>
       <c r="D2329">
-        <v>111166.02</v>
+        <v>170100</v>
       </c>
       <c r="E2329">
-        <v>835284.22</v>
+        <v>1115100</v>
       </c>
       <c r="F2329">
-        <v>112.36</v>
+        <v>112.5</v>
       </c>
       <c r="G2329">
-        <v>6300</v>
+        <v>8400</v>
       </c>
       <c r="H2329">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2329" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2329" s="2">
@@ -88515,35 +88515,35 @@
     <row r="2330">
       <c r="A2330" t="inlineStr">
         <is>
-          <t>S.R. STEEL PVT LTD</t>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2330" t="inlineStr">
         <is>
-          <t>Ordinary Ramming Mass</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2330">
-        <v>11872</v>
+        <v>707868</v>
       </c>
       <c r="D2330">
-        <v>0</v>
+        <v>111166.02</v>
       </c>
       <c r="E2330">
-        <v>12852</v>
+        <v>835284.22</v>
       </c>
       <c r="F2330">
-        <v>112</v>
+        <v>112.36</v>
       </c>
       <c r="G2330">
-        <v>106</v>
+        <v>6300</v>
       </c>
       <c r="H2330">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2330" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2330" s="2">
@@ -88553,31 +88553,31 @@
     <row r="2331">
       <c r="A2331" t="inlineStr">
         <is>
-          <t>Shri Tirupati Steel Cast Ltd</t>
+          <t>S.R. STEEL PVT LTD</t>
         </is>
       </c>
       <c r="B2331" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Ordinary Ramming Mass</t>
         </is>
       </c>
       <c r="C2331">
-        <v>352928</v>
+        <v>11872</v>
       </c>
       <c r="D2331">
-        <v>63527.04</v>
+        <v>0</v>
       </c>
       <c r="E2331">
-        <v>416456</v>
+        <v>12852</v>
       </c>
       <c r="F2331">
-        <v>110.29</v>
+        <v>112</v>
       </c>
       <c r="G2331">
-        <v>3200</v>
+        <v>106</v>
       </c>
       <c r="H2331">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I2331" t="inlineStr">
         <is>
@@ -88809,7 +88809,7 @@
       </c>
       <c r="I2337" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2337" s="2">

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2374"/>
+  <dimension ref="A1:J2434"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -90207,6 +90207,2261 @@
         <v>46082</v>
       </c>
     </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2375">
+        <v>2667368</v>
+      </c>
+      <c r="D2375">
+        <v>505603.8</v>
+      </c>
+      <c r="E2375">
+        <v>3314515</v>
+      </c>
+      <c r="F2375">
+        <v>303.11</v>
+      </c>
+      <c r="G2375">
+        <v>8800</v>
+      </c>
+      <c r="H2375">
+        <v>11</v>
+      </c>
+      <c r="I2375" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2375" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>Pushpit Steels Private Limited</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2376">
+        <v>2731024.5</v>
+      </c>
+      <c r="D2376">
+        <v>491584.44</v>
+      </c>
+      <c r="E2376">
+        <v>3222610</v>
+      </c>
+      <c r="F2376">
+        <v>291.72</v>
+      </c>
+      <c r="G2376">
+        <v>9361.8006993007</v>
+      </c>
+      <c r="H2376">
+        <v>11</v>
+      </c>
+      <c r="I2376" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2376" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>A One Ispat Private Ltd</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2377">
+        <v>2419812.5</v>
+      </c>
+      <c r="D2377">
+        <v>435566.3</v>
+      </c>
+      <c r="E2377">
+        <v>2855380</v>
+      </c>
+      <c r="F2377">
+        <v>276.55</v>
+      </c>
+      <c r="G2377">
+        <v>8750</v>
+      </c>
+      <c r="H2377">
+        <v>10</v>
+      </c>
+      <c r="I2377" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2377" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2378">
+        <v>2073082</v>
+      </c>
+      <c r="D2378">
+        <v>373154.76</v>
+      </c>
+      <c r="E2378">
+        <v>2446238</v>
+      </c>
+      <c r="F2378">
+        <v>221.72</v>
+      </c>
+      <c r="G2378">
+        <v>9350</v>
+      </c>
+      <c r="H2378">
+        <v>8</v>
+      </c>
+      <c r="I2378" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2378" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2379">
+        <v>1621566</v>
+      </c>
+      <c r="D2379">
+        <v>324374.4</v>
+      </c>
+      <c r="E2379">
+        <v>2126454</v>
+      </c>
+      <c r="F2379">
+        <v>195.56</v>
+      </c>
+      <c r="G2379">
+        <v>8291.910411127019</v>
+      </c>
+      <c r="H2379">
+        <v>8</v>
+      </c>
+      <c r="I2379" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2379" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2380">
+        <v>1519728</v>
+      </c>
+      <c r="D2380">
+        <v>273551.04</v>
+      </c>
+      <c r="E2380">
+        <v>1793279</v>
+      </c>
+      <c r="F2380">
+        <v>180.92</v>
+      </c>
+      <c r="G2380">
+        <v>8400</v>
+      </c>
+      <c r="H2380">
+        <v>6</v>
+      </c>
+      <c r="I2380" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2380" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>KUBAIR STEEL AND POWER LLP</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2381">
+        <v>1452865.5</v>
+      </c>
+      <c r="D2381">
+        <v>261515.82</v>
+      </c>
+      <c r="E2381">
+        <v>1714382</v>
+      </c>
+      <c r="F2381">
+        <v>164.25</v>
+      </c>
+      <c r="G2381">
+        <v>8845.452054794521</v>
+      </c>
+      <c r="H2381">
+        <v>7</v>
+      </c>
+      <c r="I2381" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2381" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>Arun Vyapar Udyog Private Limited</t>
+        </is>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2382">
+        <v>1658521</v>
+      </c>
+      <c r="D2382">
+        <v>298533.78</v>
+      </c>
+      <c r="E2382">
+        <v>1957056</v>
+      </c>
+      <c r="F2382">
+        <v>164.21</v>
+      </c>
+      <c r="G2382">
+        <v>10100</v>
+      </c>
+      <c r="H2382">
+        <v>8</v>
+      </c>
+      <c r="I2382" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2382" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>Adishakti Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2383">
+        <v>1433950</v>
+      </c>
+      <c r="D2383">
+        <v>286366.54</v>
+      </c>
+      <c r="E2383">
+        <v>1877291</v>
+      </c>
+      <c r="F2383">
+        <v>163.88</v>
+      </c>
+      <c r="G2383">
+        <v>8750</v>
+      </c>
+      <c r="H2383">
+        <v>6</v>
+      </c>
+      <c r="I2383" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2383" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2384">
+        <v>1258402</v>
+      </c>
+      <c r="D2384">
+        <v>226512.4</v>
+      </c>
+      <c r="E2384">
+        <v>1484915</v>
+      </c>
+      <c r="F2384">
+        <v>145.48</v>
+      </c>
+      <c r="G2384">
+        <v>8650</v>
+      </c>
+      <c r="H2384">
+        <v>5</v>
+      </c>
+      <c r="I2384" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2384" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>TEXCON STEELS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2385">
+        <v>1167442.5</v>
+      </c>
+      <c r="D2385">
+        <v>210139.65</v>
+      </c>
+      <c r="E2385">
+        <v>1377582</v>
+      </c>
+      <c r="F2385">
+        <v>139.94</v>
+      </c>
+      <c r="G2385">
+        <v>8342.450335858224</v>
+      </c>
+      <c r="H2385">
+        <v>4</v>
+      </c>
+      <c r="I2385" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2385" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+        </is>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2386">
+        <v>1205025</v>
+      </c>
+      <c r="D2386">
+        <v>216904.5</v>
+      </c>
+      <c r="E2386">
+        <v>1421932</v>
+      </c>
+      <c r="F2386">
+        <v>123.63</v>
+      </c>
+      <c r="G2386">
+        <v>9747.027420528997</v>
+      </c>
+      <c r="H2386">
+        <v>6</v>
+      </c>
+      <c r="I2386" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2386" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2387">
+        <v>1063681.5</v>
+      </c>
+      <c r="D2387">
+        <v>191462.67</v>
+      </c>
+      <c r="E2387">
+        <v>1255144</v>
+      </c>
+      <c r="F2387">
+        <v>120.19</v>
+      </c>
+      <c r="G2387">
+        <v>8850</v>
+      </c>
+      <c r="H2387">
+        <v>6</v>
+      </c>
+      <c r="I2387" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2387" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+        </is>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2388">
+        <v>963670.5</v>
+      </c>
+      <c r="D2388">
+        <v>173460.69</v>
+      </c>
+      <c r="E2388">
+        <v>1137131</v>
+      </c>
+      <c r="F2388">
+        <v>112.71</v>
+      </c>
+      <c r="G2388">
+        <v>8550</v>
+      </c>
+      <c r="H2388">
+        <v>5</v>
+      </c>
+      <c r="I2388" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2388" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2389">
+        <v>931393.5</v>
+      </c>
+      <c r="D2389">
+        <v>167650.83</v>
+      </c>
+      <c r="E2389">
+        <v>1099045</v>
+      </c>
+      <c r="F2389">
+        <v>111.22</v>
+      </c>
+      <c r="G2389">
+        <v>8374.334652041</v>
+      </c>
+      <c r="H2389">
+        <v>3</v>
+      </c>
+      <c r="I2389" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2389" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2390">
+        <v>1045657.5</v>
+      </c>
+      <c r="D2390">
+        <v>188218.35</v>
+      </c>
+      <c r="E2390">
+        <v>1233876</v>
+      </c>
+      <c r="F2390">
+        <v>109.62</v>
+      </c>
+      <c r="G2390">
+        <v>9538.929939792009</v>
+      </c>
+      <c r="H2390">
+        <v>5</v>
+      </c>
+      <c r="I2390" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2390" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2391">
+        <v>918808</v>
+      </c>
+      <c r="D2391">
+        <v>165385.44</v>
+      </c>
+      <c r="E2391">
+        <v>1084194</v>
+      </c>
+      <c r="F2391">
+        <v>104.41</v>
+      </c>
+      <c r="G2391">
+        <v>8800</v>
+      </c>
+      <c r="H2391">
+        <v>3</v>
+      </c>
+      <c r="I2391" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2391" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2392">
+        <v>681179</v>
+      </c>
+      <c r="D2392">
+        <v>122612.22</v>
+      </c>
+      <c r="E2392">
+        <v>803791</v>
+      </c>
+      <c r="F2392">
+        <v>101.31</v>
+      </c>
+      <c r="G2392">
+        <v>6723.709406771295</v>
+      </c>
+      <c r="H2392">
+        <v>3</v>
+      </c>
+      <c r="I2392" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2392" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>Shri Tirupati Steel Cast Ltd</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2393">
+        <v>331136.5</v>
+      </c>
+      <c r="D2393">
+        <v>59604.58</v>
+      </c>
+      <c r="E2393">
+        <v>390742</v>
+      </c>
+      <c r="F2393">
+        <v>97.02</v>
+      </c>
+      <c r="G2393">
+        <v>3413.07462378891</v>
+      </c>
+      <c r="H2393">
+        <v>5</v>
+      </c>
+      <c r="I2393" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2393" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>Mahrishi Alloys Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2394">
+        <v>389124</v>
+      </c>
+      <c r="D2394">
+        <v>70042.34</v>
+      </c>
+      <c r="E2394">
+        <v>459167</v>
+      </c>
+      <c r="F2394">
+        <v>96.08</v>
+      </c>
+      <c r="G2394">
+        <v>4050</v>
+      </c>
+      <c r="H2394">
+        <v>3</v>
+      </c>
+      <c r="I2394" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2394" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>Kanishk Steel Industries Ltd</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2395">
+        <v>842231</v>
+      </c>
+      <c r="D2395">
+        <v>151601.58</v>
+      </c>
+      <c r="E2395">
+        <v>993833</v>
+      </c>
+      <c r="F2395">
+        <v>81.77</v>
+      </c>
+      <c r="G2395">
+        <v>10300</v>
+      </c>
+      <c r="H2395">
+        <v>4</v>
+      </c>
+      <c r="I2395" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2395" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2396">
+        <v>689720</v>
+      </c>
+      <c r="D2396">
+        <v>124149.6</v>
+      </c>
+      <c r="E2396">
+        <v>813871</v>
+      </c>
+      <c r="F2396">
+        <v>80.23</v>
+      </c>
+      <c r="G2396">
+        <v>8596.784245294777</v>
+      </c>
+      <c r="H2396">
+        <v>4</v>
+      </c>
+      <c r="I2396" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2396" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>Meenakshi Udyog India Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2397">
+        <v>765667.5</v>
+      </c>
+      <c r="D2397">
+        <v>137820.15</v>
+      </c>
+      <c r="E2397">
+        <v>903488</v>
+      </c>
+      <c r="F2397">
+        <v>78.53</v>
+      </c>
+      <c r="G2397">
+        <v>9750</v>
+      </c>
+      <c r="H2397">
+        <v>4</v>
+      </c>
+      <c r="I2397" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2397" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>Prakash Ferrous Industries Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2398">
+        <v>732845</v>
+      </c>
+      <c r="D2398">
+        <v>131912.1</v>
+      </c>
+      <c r="E2398">
+        <v>864757</v>
+      </c>
+      <c r="F2398">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="G2398">
+        <v>10300</v>
+      </c>
+      <c r="H2398">
+        <v>2</v>
+      </c>
+      <c r="I2398" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2398" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2399">
+        <v>87828</v>
+      </c>
+      <c r="D2399">
+        <v>4391.4</v>
+      </c>
+      <c r="E2399">
+        <v>92219</v>
+      </c>
+      <c r="F2399">
+        <v>67.56</v>
+      </c>
+      <c r="G2399">
+        <v>1300</v>
+      </c>
+      <c r="H2399">
+        <v>2</v>
+      </c>
+      <c r="I2399" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2399" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2400">
+        <v>286979</v>
+      </c>
+      <c r="D2400">
+        <v>51656.22</v>
+      </c>
+      <c r="E2400">
+        <v>338635</v>
+      </c>
+      <c r="F2400">
+        <v>67.00999999999999</v>
+      </c>
+      <c r="G2400">
+        <v>4282.629458289808</v>
+      </c>
+      <c r="H2400">
+        <v>3</v>
+      </c>
+      <c r="I2400" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2400" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2401">
+        <v>553601.5</v>
+      </c>
+      <c r="D2401">
+        <v>106274.36</v>
+      </c>
+      <c r="E2401">
+        <v>696689</v>
+      </c>
+      <c r="F2401">
+        <v>65.81</v>
+      </c>
+      <c r="G2401">
+        <v>8412.118219115637</v>
+      </c>
+      <c r="H2401">
+        <v>6</v>
+      </c>
+      <c r="I2401" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2401" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>PARAGON STEEL DISTRIBUITORS</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2402">
+        <v>436356</v>
+      </c>
+      <c r="D2402">
+        <v>78544.08</v>
+      </c>
+      <c r="E2402">
+        <v>514900</v>
+      </c>
+      <c r="F2402">
+        <v>64.17</v>
+      </c>
+      <c r="G2402">
+        <v>6800</v>
+      </c>
+      <c r="H2402">
+        <v>3</v>
+      </c>
+      <c r="I2402" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2402" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2403">
+        <v>212738</v>
+      </c>
+      <c r="D2403">
+        <v>12815.28</v>
+      </c>
+      <c r="E2403">
+        <v>251030.56</v>
+      </c>
+      <c r="F2403">
+        <v>62.57</v>
+      </c>
+      <c r="G2403">
+        <v>3400</v>
+      </c>
+      <c r="H2403">
+        <v>3</v>
+      </c>
+      <c r="I2403" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2403" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+        </is>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2404">
+        <v>225314.5</v>
+      </c>
+      <c r="D2404">
+        <v>30399.4</v>
+      </c>
+      <c r="E2404">
+        <v>265871.22</v>
+      </c>
+      <c r="F2404">
+        <v>61.73</v>
+      </c>
+      <c r="G2404">
+        <v>3650</v>
+      </c>
+      <c r="H2404">
+        <v>3</v>
+      </c>
+      <c r="I2404" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2404" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2405">
+        <v>485511</v>
+      </c>
+      <c r="D2405">
+        <v>97549.24000000001</v>
+      </c>
+      <c r="E2405">
+        <v>639489</v>
+      </c>
+      <c r="F2405">
+        <v>54.86</v>
+      </c>
+      <c r="G2405">
+        <v>8850</v>
+      </c>
+      <c r="H2405">
+        <v>4</v>
+      </c>
+      <c r="I2405" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2405" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2406">
+        <v>349920</v>
+      </c>
+      <c r="D2406">
+        <v>75715.20000000001</v>
+      </c>
+      <c r="E2406">
+        <v>496356</v>
+      </c>
+      <c r="F2406">
+        <v>51.84</v>
+      </c>
+      <c r="G2406">
+        <v>6750.000000000001</v>
+      </c>
+      <c r="H2406">
+        <v>2</v>
+      </c>
+      <c r="I2406" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2406" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>Adishakti Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2407">
+        <v>156975</v>
+      </c>
+      <c r="D2407">
+        <v>0</v>
+      </c>
+      <c r="E2407">
+        <v>185230.5</v>
+      </c>
+      <c r="F2407">
+        <v>45.5</v>
+      </c>
+      <c r="G2407">
+        <v>3450</v>
+      </c>
+      <c r="H2407">
+        <v>3</v>
+      </c>
+      <c r="I2407" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2407" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>Shyam Ferrous Ltd.</t>
+        </is>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2408">
+        <v>364000</v>
+      </c>
+      <c r="D2408">
+        <v>65520.04</v>
+      </c>
+      <c r="E2408">
+        <v>429521</v>
+      </c>
+      <c r="F2408">
+        <v>41.6</v>
+      </c>
+      <c r="G2408">
+        <v>8750</v>
+      </c>
+      <c r="H2408">
+        <v>7</v>
+      </c>
+      <c r="I2408" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2408" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>Keshree Metalurgies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2409">
+        <v>349300</v>
+      </c>
+      <c r="D2409">
+        <v>62874</v>
+      </c>
+      <c r="E2409">
+        <v>412174</v>
+      </c>
+      <c r="F2409">
+        <v>39.92</v>
+      </c>
+      <c r="G2409">
+        <v>8750</v>
+      </c>
+      <c r="H2409">
+        <v>2</v>
+      </c>
+      <c r="I2409" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2409" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2410">
+        <v>124992</v>
+      </c>
+      <c r="D2410">
+        <v>10869.12</v>
+      </c>
+      <c r="E2410">
+        <v>147490.44</v>
+      </c>
+      <c r="F2410">
+        <v>39.06</v>
+      </c>
+      <c r="G2410">
+        <v>3200</v>
+      </c>
+      <c r="H2410">
+        <v>3</v>
+      </c>
+      <c r="I2410" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2410" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2411">
+        <v>138084</v>
+      </c>
+      <c r="D2411">
+        <v>24855.12</v>
+      </c>
+      <c r="E2411">
+        <v>162939</v>
+      </c>
+      <c r="F2411">
+        <v>37.32</v>
+      </c>
+      <c r="G2411">
+        <v>3700</v>
+      </c>
+      <c r="H2411">
+        <v>1</v>
+      </c>
+      <c r="I2411" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2411" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>Sri M.S.T. Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2412">
+        <v>310016</v>
+      </c>
+      <c r="D2412">
+        <v>55802.88</v>
+      </c>
+      <c r="E2412">
+        <v>365819</v>
+      </c>
+      <c r="F2412">
+        <v>35.84</v>
+      </c>
+      <c r="G2412">
+        <v>8650</v>
+      </c>
+      <c r="H2412">
+        <v>1</v>
+      </c>
+      <c r="I2412" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2412" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>TEXCON STEELS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2413">
+        <v>228215</v>
+      </c>
+      <c r="D2413">
+        <v>41078.7</v>
+      </c>
+      <c r="E2413">
+        <v>269294</v>
+      </c>
+      <c r="F2413">
+        <v>35.11</v>
+      </c>
+      <c r="G2413">
+        <v>6500</v>
+      </c>
+      <c r="H2413">
+        <v>1</v>
+      </c>
+      <c r="I2413" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2413" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>M.A.STEELS (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2414">
+        <v>243389</v>
+      </c>
+      <c r="D2414">
+        <v>43810.02</v>
+      </c>
+      <c r="E2414">
+        <v>287199</v>
+      </c>
+      <c r="F2414">
+        <v>35.02</v>
+      </c>
+      <c r="G2414">
+        <v>6950.000000000001</v>
+      </c>
+      <c r="H2414">
+        <v>2</v>
+      </c>
+      <c r="I2414" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2414" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>MINAR ISPAT PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2415">
+        <v>243111</v>
+      </c>
+      <c r="D2415">
+        <v>43759.98</v>
+      </c>
+      <c r="E2415">
+        <v>286871</v>
+      </c>
+      <c r="F2415">
+        <v>34.98</v>
+      </c>
+      <c r="G2415">
+        <v>6949.999999999999</v>
+      </c>
+      <c r="H2415">
+        <v>2</v>
+      </c>
+      <c r="I2415" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2415" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>SREE PALANIANDAVAR ALLOYS AND STEELS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2416">
+        <v>219240</v>
+      </c>
+      <c r="D2416">
+        <v>39463.2</v>
+      </c>
+      <c r="E2416">
+        <v>258703</v>
+      </c>
+      <c r="F2416">
+        <v>34.8</v>
+      </c>
+      <c r="G2416">
+        <v>6300.000000000001</v>
+      </c>
+      <c r="H2416">
+        <v>2</v>
+      </c>
+      <c r="I2416" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2416" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Limited</t>
+        </is>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2417">
+        <v>143487.6</v>
+      </c>
+      <c r="D2417">
+        <v>7174.379999999999</v>
+      </c>
+      <c r="E2417">
+        <v>150662</v>
+      </c>
+      <c r="F2417">
+        <v>32.91</v>
+      </c>
+      <c r="G2417">
+        <v>4360.000000000001</v>
+      </c>
+      <c r="H2417">
+        <v>2</v>
+      </c>
+      <c r="I2417" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2417" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2418">
+        <v>274746</v>
+      </c>
+      <c r="D2418">
+        <v>49454.28</v>
+      </c>
+      <c r="E2418">
+        <v>324200</v>
+      </c>
+      <c r="F2418">
+        <v>31.58</v>
+      </c>
+      <c r="G2418">
+        <v>8700</v>
+      </c>
+      <c r="H2418">
+        <v>1</v>
+      </c>
+      <c r="I2418" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2418" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>Pattambi Brothers</t>
+        </is>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2419">
+        <v>208708.5</v>
+      </c>
+      <c r="D2419">
+        <v>37567.53</v>
+      </c>
+      <c r="E2419">
+        <v>246276</v>
+      </c>
+      <c r="F2419">
+        <v>30.03</v>
+      </c>
+      <c r="G2419">
+        <v>6950</v>
+      </c>
+      <c r="H2419">
+        <v>2</v>
+      </c>
+      <c r="I2419" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2419" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>VGK STEELS</t>
+        </is>
+      </c>
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2420">
+        <v>233922</v>
+      </c>
+      <c r="D2420">
+        <v>42105.96</v>
+      </c>
+      <c r="E2420">
+        <v>276028</v>
+      </c>
+      <c r="F2420">
+        <v>29.99</v>
+      </c>
+      <c r="G2420">
+        <v>7800</v>
+      </c>
+      <c r="H2420">
+        <v>1</v>
+      </c>
+      <c r="I2420" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2420" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C2421">
+        <v>181540</v>
+      </c>
+      <c r="D2421">
+        <v>32677.2</v>
+      </c>
+      <c r="E2421">
+        <v>214217</v>
+      </c>
+      <c r="F2421">
+        <v>25.04</v>
+      </c>
+      <c r="G2421">
+        <v>7250</v>
+      </c>
+      <c r="H2421">
+        <v>1</v>
+      </c>
+      <c r="I2421" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2421" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2422">
+        <v>70720</v>
+      </c>
+      <c r="D2422">
+        <v>0</v>
+      </c>
+      <c r="E2422">
+        <v>83449.59999999999</v>
+      </c>
+      <c r="F2422">
+        <v>21.76</v>
+      </c>
+      <c r="G2422">
+        <v>3250</v>
+      </c>
+      <c r="H2422">
+        <v>1</v>
+      </c>
+      <c r="I2422" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2422" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PVT LTD</t>
+        </is>
+      </c>
+      <c r="C2423">
+        <v>145145</v>
+      </c>
+      <c r="D2423">
+        <v>26126.1</v>
+      </c>
+      <c r="E2423">
+        <v>171271</v>
+      </c>
+      <c r="F2423">
+        <v>20.02</v>
+      </c>
+      <c r="G2423">
+        <v>7250</v>
+      </c>
+      <c r="H2423">
+        <v>1</v>
+      </c>
+      <c r="I2423" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2423" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2424">
+        <v>54199.5</v>
+      </c>
+      <c r="D2424">
+        <v>3129.84</v>
+      </c>
+      <c r="E2424">
+        <v>63955.57</v>
+      </c>
+      <c r="F2424">
+        <v>15.71</v>
+      </c>
+      <c r="G2424">
+        <v>3450</v>
+      </c>
+      <c r="H2424">
+        <v>2</v>
+      </c>
+      <c r="I2424" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2424" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>PRINCE ALLOYS (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2425">
+        <v>108976</v>
+      </c>
+      <c r="D2425">
+        <v>19615.68</v>
+      </c>
+      <c r="E2425">
+        <v>128592</v>
+      </c>
+      <c r="F2425">
+        <v>15.68</v>
+      </c>
+      <c r="G2425">
+        <v>6950</v>
+      </c>
+      <c r="H2425">
+        <v>1</v>
+      </c>
+      <c r="I2425" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2425" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>PRINCE ROLLINGS  (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2426">
+        <v>107725</v>
+      </c>
+      <c r="D2426">
+        <v>19390.5</v>
+      </c>
+      <c r="E2426">
+        <v>127116</v>
+      </c>
+      <c r="F2426">
+        <v>15.5</v>
+      </c>
+      <c r="G2426">
+        <v>6950</v>
+      </c>
+      <c r="H2426">
+        <v>1</v>
+      </c>
+      <c r="I2426" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2426" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>Ordinary Ramming Mass</t>
+        </is>
+      </c>
+      <c r="C2427">
+        <v>45430.5</v>
+      </c>
+      <c r="D2427">
+        <v>8177.5</v>
+      </c>
+      <c r="E2427">
+        <v>53608</v>
+      </c>
+      <c r="F2427">
+        <v>9.77</v>
+      </c>
+      <c r="G2427">
+        <v>4650</v>
+      </c>
+      <c r="H2427">
+        <v>1</v>
+      </c>
+      <c r="I2427" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2427" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C2428">
+        <v>825000</v>
+      </c>
+      <c r="D2428">
+        <v>148500</v>
+      </c>
+      <c r="E2428">
+        <v>973500</v>
+      </c>
+      <c r="F2428">
+        <v>5</v>
+      </c>
+      <c r="G2428">
+        <v>165000</v>
+      </c>
+      <c r="H2428">
+        <v>1</v>
+      </c>
+      <c r="I2428" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2428" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>Tundish Ramming Mix</t>
+        </is>
+      </c>
+      <c r="C2429">
+        <v>135000</v>
+      </c>
+      <c r="D2429">
+        <v>24300</v>
+      </c>
+      <c r="E2429">
+        <v>159300</v>
+      </c>
+      <c r="F2429">
+        <v>5</v>
+      </c>
+      <c r="G2429">
+        <v>27000</v>
+      </c>
+      <c r="H2429">
+        <v>1</v>
+      </c>
+      <c r="I2429" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2429" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2430">
+        <v>34333</v>
+      </c>
+      <c r="D2430">
+        <v>6179.94</v>
+      </c>
+      <c r="E2430">
+        <v>40513</v>
+      </c>
+      <c r="F2430">
+        <v>4.94</v>
+      </c>
+      <c r="G2430">
+        <v>6949.999999999999</v>
+      </c>
+      <c r="H2430">
+        <v>1</v>
+      </c>
+      <c r="I2430" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2430" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>SRI LAXMI GANESH MINERALS UNIT - II</t>
+        </is>
+      </c>
+      <c r="C2431">
+        <v>1597500</v>
+      </c>
+      <c r="D2431">
+        <v>287550</v>
+      </c>
+      <c r="E2431">
+        <v>1885050</v>
+      </c>
+      <c r="F2431">
+        <v>4.5</v>
+      </c>
+      <c r="G2431">
+        <v>355000</v>
+      </c>
+      <c r="H2431">
+        <v>1</v>
+      </c>
+      <c r="I2431" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2431" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2432">
+        <v>28482</v>
+      </c>
+      <c r="D2432">
+        <v>5126.76</v>
+      </c>
+      <c r="E2432">
+        <v>33609</v>
+      </c>
+      <c r="F2432">
+        <v>4.04</v>
+      </c>
+      <c r="G2432">
+        <v>7050</v>
+      </c>
+      <c r="H2432">
+        <v>1</v>
+      </c>
+      <c r="I2432" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2432" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C2433">
+        <v>887500</v>
+      </c>
+      <c r="D2433">
+        <v>159750</v>
+      </c>
+      <c r="E2433">
+        <v>1047250</v>
+      </c>
+      <c r="F2433">
+        <v>2.5</v>
+      </c>
+      <c r="G2433">
+        <v>355000</v>
+      </c>
+      <c r="H2433">
+        <v>1</v>
+      </c>
+      <c r="I2433" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2433" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>JAJOO EXIM PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2434">
+        <v>764000</v>
+      </c>
+      <c r="D2434">
+        <v>137520</v>
+      </c>
+      <c r="E2434">
+        <v>901520</v>
+      </c>
+      <c r="F2434">
+        <v>2</v>
+      </c>
+      <c r="G2434">
+        <v>382000</v>
+      </c>
+      <c r="H2434">
+        <v>1</v>
+      </c>
+      <c r="I2434" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2434" s="2">
+        <v>46113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -91961,6 +91961,11 @@
           <t>SNAM ALLOYS PRIVATE LIMITED</t>
         </is>
       </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
       <c r="C2421">
         <v>181540</v>
       </c>
@@ -92030,6 +92035,11 @@
       <c r="A2423" t="inlineStr">
         <is>
           <t>SNAM ALLOYS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2423">

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2434"/>
+  <dimension ref="A1:J2489"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -90694,7 +90694,7 @@
       </c>
       <c r="I2387" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2387" s="2">
@@ -92356,7 +92356,7 @@
       </c>
       <c r="I2431" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2431" s="2">
@@ -92465,11 +92465,1661 @@
       </c>
       <c r="I2434" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2434" s="2">
         <v>46113</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>Pushpit Steels Private Limited</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2435">
+        <v>1911094</v>
+      </c>
+      <c r="D2435">
+        <v>343996.92</v>
+      </c>
+      <c r="E2435">
+        <v>2255092</v>
+      </c>
+      <c r="F2435">
+        <v>197.02</v>
+      </c>
+      <c r="G2435">
+        <v>9700</v>
+      </c>
+      <c r="H2435">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>A One Ispat Private Ltd</t>
+        </is>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2436">
+        <v>1325537.5</v>
+      </c>
+      <c r="D2436">
+        <v>238596.8</v>
+      </c>
+      <c r="E2436">
+        <v>1564133</v>
+      </c>
+      <c r="F2436">
+        <v>151.49</v>
+      </c>
+      <c r="G2436">
+        <v>8750</v>
+      </c>
+      <c r="H2436">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2437">
+        <v>1272398</v>
+      </c>
+      <c r="D2437">
+        <v>229031.64</v>
+      </c>
+      <c r="E2437">
+        <v>1501429</v>
+      </c>
+      <c r="F2437">
+        <v>125.98</v>
+      </c>
+      <c r="G2437">
+        <v>10100</v>
+      </c>
+      <c r="H2437">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2438">
+        <v>1092344</v>
+      </c>
+      <c r="D2438">
+        <v>202686.84</v>
+      </c>
+      <c r="E2438">
+        <v>1328724</v>
+      </c>
+      <c r="F2438">
+        <v>124.13</v>
+      </c>
+      <c r="G2438">
+        <v>8800</v>
+      </c>
+      <c r="H2438">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2439">
+        <v>1106479</v>
+      </c>
+      <c r="D2439">
+        <v>199166.22</v>
+      </c>
+      <c r="E2439">
+        <v>1305646</v>
+      </c>
+      <c r="F2439">
+        <v>118.34</v>
+      </c>
+      <c r="G2439">
+        <v>9350</v>
+      </c>
+      <c r="H2439">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2440">
+        <v>1056960</v>
+      </c>
+      <c r="D2440">
+        <v>190252.8</v>
+      </c>
+      <c r="E2440">
+        <v>1247212</v>
+      </c>
+      <c r="F2440">
+        <v>117.44</v>
+      </c>
+      <c r="G2440">
+        <v>9000</v>
+      </c>
+      <c r="H2440">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>Meenakshi Udyog India Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2441">
+        <v>1123687.5</v>
+      </c>
+      <c r="D2441">
+        <v>202263.75</v>
+      </c>
+      <c r="E2441">
+        <v>1325952</v>
+      </c>
+      <c r="F2441">
+        <v>115.25</v>
+      </c>
+      <c r="G2441">
+        <v>9750</v>
+      </c>
+      <c r="H2441">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>KUBAIR STEEL AND POWER LLP</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2442">
+        <v>989285</v>
+      </c>
+      <c r="D2442">
+        <v>178071.3</v>
+      </c>
+      <c r="E2442">
+        <v>1167358</v>
+      </c>
+      <c r="F2442">
+        <v>112.03</v>
+      </c>
+      <c r="G2442">
+        <v>8830.536463447292</v>
+      </c>
+      <c r="H2442">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>S.R. STEEL PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>Ordinary Ramming Mass</t>
+        </is>
+      </c>
+      <c r="C2443">
+        <v>13328</v>
+      </c>
+      <c r="D2443">
+        <v>0</v>
+      </c>
+      <c r="E2443">
+        <v>13328</v>
+      </c>
+      <c r="F2443">
+        <v>112</v>
+      </c>
+      <c r="G2443">
+        <v>119</v>
+      </c>
+      <c r="H2443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>Adishakti Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2444">
+        <v>971950</v>
+      </c>
+      <c r="D2444">
+        <v>174951.04</v>
+      </c>
+      <c r="E2444">
+        <v>1146902</v>
+      </c>
+      <c r="F2444">
+        <v>111.08</v>
+      </c>
+      <c r="G2444">
+        <v>8749.999999999998</v>
+      </c>
+      <c r="H2444">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2445">
+        <v>329154</v>
+      </c>
+      <c r="D2445">
+        <v>53182.8</v>
+      </c>
+      <c r="E2445">
+        <v>388401.92</v>
+      </c>
+      <c r="F2445">
+        <v>96.81</v>
+      </c>
+      <c r="G2445">
+        <v>3400</v>
+      </c>
+      <c r="H2445">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2446">
+        <v>165644.5</v>
+      </c>
+      <c r="D2446">
+        <v>8282.225</v>
+      </c>
+      <c r="E2446">
+        <v>173926.725</v>
+      </c>
+      <c r="F2446">
+        <v>85.75</v>
+      </c>
+      <c r="G2446">
+        <v>1931.714285714286</v>
+      </c>
+      <c r="H2446">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>Arun Vyapar Udyog Private Limited</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2447">
+        <v>860722</v>
+      </c>
+      <c r="D2447">
+        <v>154929.96</v>
+      </c>
+      <c r="E2447">
+        <v>1015652</v>
+      </c>
+      <c r="F2447">
+        <v>85.22</v>
+      </c>
+      <c r="G2447">
+        <v>10100</v>
+      </c>
+      <c r="H2447">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+        </is>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2448">
+        <v>714609</v>
+      </c>
+      <c r="D2448">
+        <v>128629.62</v>
+      </c>
+      <c r="E2448">
+        <v>843239</v>
+      </c>
+      <c r="F2448">
+        <v>83.58</v>
+      </c>
+      <c r="G2448">
+        <v>8550</v>
+      </c>
+      <c r="H2448">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>BMM ISPAT LIMITED</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2449">
+        <v>616231</v>
+      </c>
+      <c r="D2449">
+        <v>110921.58</v>
+      </c>
+      <c r="E2449">
+        <v>727153</v>
+      </c>
+      <c r="F2449">
+        <v>81.62</v>
+      </c>
+      <c r="G2449">
+        <v>7550</v>
+      </c>
+      <c r="H2449">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2450">
+        <v>676536</v>
+      </c>
+      <c r="D2450">
+        <v>130065.12</v>
+      </c>
+      <c r="E2450">
+        <v>852649</v>
+      </c>
+      <c r="F2450">
+        <v>80.53999999999999</v>
+      </c>
+      <c r="G2450">
+        <v>8400</v>
+      </c>
+      <c r="H2450">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2451">
+        <v>667201.5</v>
+      </c>
+      <c r="D2451">
+        <v>120096.27</v>
+      </c>
+      <c r="E2451">
+        <v>787298</v>
+      </c>
+      <c r="F2451">
+        <v>75.39</v>
+      </c>
+      <c r="G2451">
+        <v>8850</v>
+      </c>
+      <c r="H2451">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2452">
+        <v>650307</v>
+      </c>
+      <c r="D2452">
+        <v>117055.26</v>
+      </c>
+      <c r="E2452">
+        <v>767362</v>
+      </c>
+      <c r="F2452">
+        <v>75.18000000000001</v>
+      </c>
+      <c r="G2452">
+        <v>8650</v>
+      </c>
+      <c r="H2452">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>Mahrishi Alloys Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2453">
+        <v>294151.5</v>
+      </c>
+      <c r="D2453">
+        <v>52947.28</v>
+      </c>
+      <c r="E2453">
+        <v>347099</v>
+      </c>
+      <c r="F2453">
+        <v>72.63</v>
+      </c>
+      <c r="G2453">
+        <v>4050</v>
+      </c>
+      <c r="H2453">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>TEXCON STEELS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2454">
+        <v>608247</v>
+      </c>
+      <c r="D2454">
+        <v>109484.46</v>
+      </c>
+      <c r="E2454">
+        <v>717731</v>
+      </c>
+      <c r="F2454">
+        <v>71.14</v>
+      </c>
+      <c r="G2454">
+        <v>8550</v>
+      </c>
+      <c r="H2454">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+        </is>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2455">
+        <v>611424</v>
+      </c>
+      <c r="D2455">
+        <v>110056.32</v>
+      </c>
+      <c r="E2455">
+        <v>721480</v>
+      </c>
+      <c r="F2455">
+        <v>69.47999999999999</v>
+      </c>
+      <c r="G2455">
+        <v>8800.000000000002</v>
+      </c>
+      <c r="H2455">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2456">
+        <v>468013</v>
+      </c>
+      <c r="D2456">
+        <v>84242.34</v>
+      </c>
+      <c r="E2456">
+        <v>552256</v>
+      </c>
+      <c r="F2456">
+        <v>67.34</v>
+      </c>
+      <c r="G2456">
+        <v>6950</v>
+      </c>
+      <c r="H2456">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>RELIANCE CONCAST SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2457">
+        <v>182544</v>
+      </c>
+      <c r="D2457">
+        <v>9127.200000000001</v>
+      </c>
+      <c r="E2457">
+        <v>191671</v>
+      </c>
+      <c r="F2457">
+        <v>61.35</v>
+      </c>
+      <c r="G2457">
+        <v>2975.452322738387</v>
+      </c>
+      <c r="H2457">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>Shyam Ferrous Ltd.</t>
+        </is>
+      </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2458">
+        <v>512662.5</v>
+      </c>
+      <c r="D2458">
+        <v>92279.25999999999</v>
+      </c>
+      <c r="E2458">
+        <v>604943</v>
+      </c>
+      <c r="F2458">
+        <v>58.59</v>
+      </c>
+      <c r="G2458">
+        <v>8750</v>
+      </c>
+      <c r="H2458">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>Shri Tirupati Steel Cast Ltd</t>
+        </is>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2459">
+        <v>191095.5</v>
+      </c>
+      <c r="D2459">
+        <v>34397.22</v>
+      </c>
+      <c r="E2459">
+        <v>225493</v>
+      </c>
+      <c r="F2459">
+        <v>55.39</v>
+      </c>
+      <c r="G2459">
+        <v>3450</v>
+      </c>
+      <c r="H2459">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2460">
+        <v>476612.5</v>
+      </c>
+      <c r="D2460">
+        <v>91627.66</v>
+      </c>
+      <c r="E2460">
+        <v>600670</v>
+      </c>
+      <c r="F2460">
+        <v>54.47</v>
+      </c>
+      <c r="G2460">
+        <v>8750</v>
+      </c>
+      <c r="H2460">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2461">
+        <v>443700</v>
+      </c>
+      <c r="D2461">
+        <v>79866</v>
+      </c>
+      <c r="E2461">
+        <v>523566</v>
+      </c>
+      <c r="F2461">
+        <v>51</v>
+      </c>
+      <c r="G2461">
+        <v>8700</v>
+      </c>
+      <c r="H2461">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>Prakash Ferrous Industries Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2462">
+        <v>465148</v>
+      </c>
+      <c r="D2462">
+        <v>83726.64</v>
+      </c>
+      <c r="E2462">
+        <v>548875</v>
+      </c>
+      <c r="F2462">
+        <v>45.16</v>
+      </c>
+      <c r="G2462">
+        <v>10300</v>
+      </c>
+      <c r="H2462">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>Kanishk Steel Industries Ltd</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2463">
+        <v>462470</v>
+      </c>
+      <c r="D2463">
+        <v>83244.60000000001</v>
+      </c>
+      <c r="E2463">
+        <v>545715</v>
+      </c>
+      <c r="F2463">
+        <v>44.9</v>
+      </c>
+      <c r="G2463">
+        <v>10300</v>
+      </c>
+      <c r="H2463">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>GBR Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2464">
+        <v>439295</v>
+      </c>
+      <c r="D2464">
+        <v>79073.10000000001</v>
+      </c>
+      <c r="E2464">
+        <v>518368</v>
+      </c>
+      <c r="F2464">
+        <v>42.65</v>
+      </c>
+      <c r="G2464">
+        <v>10300</v>
+      </c>
+      <c r="H2464">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2465">
+        <v>271012.5</v>
+      </c>
+      <c r="D2465">
+        <v>48782.25</v>
+      </c>
+      <c r="E2465">
+        <v>319794</v>
+      </c>
+      <c r="F2465">
+        <v>40.15000000000001</v>
+      </c>
+      <c r="G2465">
+        <v>6749.999999999999</v>
+      </c>
+      <c r="H2465">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>Keshree Metalurgies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2466">
+        <v>384000</v>
+      </c>
+      <c r="D2466">
+        <v>69120</v>
+      </c>
+      <c r="E2466">
+        <v>453120</v>
+      </c>
+      <c r="F2466">
+        <v>40</v>
+      </c>
+      <c r="G2466">
+        <v>9600</v>
+      </c>
+      <c r="H2466">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+        </is>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2467">
+        <v>134274</v>
+      </c>
+      <c r="D2467">
+        <v>24169.32</v>
+      </c>
+      <c r="E2467">
+        <v>158443</v>
+      </c>
+      <c r="F2467">
+        <v>38.92</v>
+      </c>
+      <c r="G2467">
+        <v>3450</v>
+      </c>
+      <c r="H2467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+        </is>
+      </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2468">
+        <v>327056.5</v>
+      </c>
+      <c r="D2468">
+        <v>58870.17</v>
+      </c>
+      <c r="E2468">
+        <v>385927</v>
+      </c>
+      <c r="F2468">
+        <v>37.81</v>
+      </c>
+      <c r="G2468">
+        <v>8650</v>
+      </c>
+      <c r="H2468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+        </is>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2469">
+        <v>327980</v>
+      </c>
+      <c r="D2469">
+        <v>59036.4</v>
+      </c>
+      <c r="E2469">
+        <v>387017</v>
+      </c>
+      <c r="F2469">
+        <v>35.65</v>
+      </c>
+      <c r="G2469">
+        <v>9200</v>
+      </c>
+      <c r="H2469">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>VMC Steel and Alloys Industry</t>
+        </is>
+      </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2470">
+        <v>368445</v>
+      </c>
+      <c r="D2470">
+        <v>66320.10000000001</v>
+      </c>
+      <c r="E2470">
+        <v>434765</v>
+      </c>
+      <c r="F2470">
+        <v>35.09</v>
+      </c>
+      <c r="G2470">
+        <v>10500</v>
+      </c>
+      <c r="H2470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>PARAGON STEEL DISTRIBUITORS</t>
+        </is>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2471">
+        <v>238000</v>
+      </c>
+      <c r="D2471">
+        <v>42840</v>
+      </c>
+      <c r="E2471">
+        <v>280840</v>
+      </c>
+      <c r="F2471">
+        <v>35</v>
+      </c>
+      <c r="G2471">
+        <v>6800</v>
+      </c>
+      <c r="H2471">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+        </is>
+      </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2472">
+        <v>306298.5</v>
+      </c>
+      <c r="D2472">
+        <v>55133.74</v>
+      </c>
+      <c r="E2472">
+        <v>361432</v>
+      </c>
+      <c r="F2472">
+        <v>34.61</v>
+      </c>
+      <c r="G2472">
+        <v>8850</v>
+      </c>
+      <c r="H2472">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+        </is>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2473">
+        <v>141655</v>
+      </c>
+      <c r="D2473">
+        <v>25497.9</v>
+      </c>
+      <c r="E2473">
+        <v>167153</v>
+      </c>
+      <c r="F2473">
+        <v>34.55</v>
+      </c>
+      <c r="G2473">
+        <v>4100</v>
+      </c>
+      <c r="H2473">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>Sri M.S.T. Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2474">
+        <v>264430.5</v>
+      </c>
+      <c r="D2474">
+        <v>47597.49</v>
+      </c>
+      <c r="E2474">
+        <v>312028</v>
+      </c>
+      <c r="F2474">
+        <v>30.57</v>
+      </c>
+      <c r="G2474">
+        <v>8650</v>
+      </c>
+      <c r="H2474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2475">
+        <v>306324</v>
+      </c>
+      <c r="D2475">
+        <v>55138.32</v>
+      </c>
+      <c r="E2475">
+        <v>361463</v>
+      </c>
+      <c r="F2475">
+        <v>30.48</v>
+      </c>
+      <c r="G2475">
+        <v>10050</v>
+      </c>
+      <c r="H2475">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>Meenakshi Steels</t>
+        </is>
+      </c>
+      <c r="B2476" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2476">
+        <v>315420</v>
+      </c>
+      <c r="D2476">
+        <v>56775.6</v>
+      </c>
+      <c r="E2476">
+        <v>372196</v>
+      </c>
+      <c r="F2476">
+        <v>30.04</v>
+      </c>
+      <c r="G2476">
+        <v>10500</v>
+      </c>
+      <c r="H2476">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2477" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2477">
+        <v>131208</v>
+      </c>
+      <c r="D2477">
+        <v>23617.44</v>
+      </c>
+      <c r="E2477">
+        <v>154825</v>
+      </c>
+      <c r="F2477">
+        <v>29.82</v>
+      </c>
+      <c r="G2477">
+        <v>4400</v>
+      </c>
+      <c r="H2477">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>BLUE GOLD STEEL INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="B2478" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2478">
+        <v>228112.5</v>
+      </c>
+      <c r="D2478">
+        <v>41060.26</v>
+      </c>
+      <c r="E2478">
+        <v>269173</v>
+      </c>
+      <c r="F2478">
+        <v>26.07</v>
+      </c>
+      <c r="G2478">
+        <v>8750</v>
+      </c>
+      <c r="H2478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2479" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2479">
+        <v>171948</v>
+      </c>
+      <c r="D2479">
+        <v>30950.64</v>
+      </c>
+      <c r="E2479">
+        <v>202899</v>
+      </c>
+      <c r="F2479">
+        <v>24.92</v>
+      </c>
+      <c r="G2479">
+        <v>6899.999999999999</v>
+      </c>
+      <c r="H2479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>BLUE GOLD STEEL INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="B2480" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2480">
+        <v>65895</v>
+      </c>
+      <c r="D2480">
+        <v>11861.1</v>
+      </c>
+      <c r="E2480">
+        <v>77756</v>
+      </c>
+      <c r="F2480">
+        <v>19.1</v>
+      </c>
+      <c r="G2480">
+        <v>3450</v>
+      </c>
+      <c r="H2480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+        </is>
+      </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2481">
+        <v>69301</v>
+      </c>
+      <c r="D2481">
+        <v>12474.18</v>
+      </c>
+      <c r="E2481">
+        <v>81775</v>
+      </c>
+      <c r="F2481">
+        <v>18.73</v>
+      </c>
+      <c r="G2481">
+        <v>3700</v>
+      </c>
+      <c r="H2481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>KRISHNA STEEL ROLLING MILLS</t>
+        </is>
+      </c>
+      <c r="B2482" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2482">
+        <v>60758</v>
+      </c>
+      <c r="D2482">
+        <v>0</v>
+      </c>
+      <c r="E2482">
+        <v>71694.44</v>
+      </c>
+      <c r="F2482">
+        <v>17.87</v>
+      </c>
+      <c r="G2482">
+        <v>3400</v>
+      </c>
+      <c r="H2482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>PRINCE ALLOYS (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2483">
+        <v>124127</v>
+      </c>
+      <c r="D2483">
+        <v>22342.86</v>
+      </c>
+      <c r="E2483">
+        <v>146470</v>
+      </c>
+      <c r="F2483">
+        <v>17.86</v>
+      </c>
+      <c r="G2483">
+        <v>6950</v>
+      </c>
+      <c r="H2483">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>PRINCE ROLLINGS  (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2484" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2484">
+        <v>123710</v>
+      </c>
+      <c r="D2484">
+        <v>22267.8</v>
+      </c>
+      <c r="E2484">
+        <v>145978</v>
+      </c>
+      <c r="F2484">
+        <v>17.8</v>
+      </c>
+      <c r="G2484">
+        <v>6950</v>
+      </c>
+      <c r="H2484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>KRISHNA STEEL ROLLING MILLS</t>
+        </is>
+      </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2485">
+        <v>124110</v>
+      </c>
+      <c r="D2485">
+        <v>33276.24</v>
+      </c>
+      <c r="E2485">
+        <v>218144</v>
+      </c>
+      <c r="F2485">
+        <v>17.73</v>
+      </c>
+      <c r="G2485">
+        <v>7000</v>
+      </c>
+      <c r="H2485">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2486" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2486">
+        <v>105820.5</v>
+      </c>
+      <c r="D2486">
+        <v>13210.3</v>
+      </c>
+      <c r="E2486">
+        <v>124868.4</v>
+      </c>
+      <c r="F2486">
+        <v>15.01</v>
+      </c>
+      <c r="G2486">
+        <v>7050</v>
+      </c>
+      <c r="H2486">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2487" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2487">
+        <v>46048</v>
+      </c>
+      <c r="D2487">
+        <v>0</v>
+      </c>
+      <c r="E2487">
+        <v>54336.64</v>
+      </c>
+      <c r="F2487">
+        <v>14.39</v>
+      </c>
+      <c r="G2487">
+        <v>3200</v>
+      </c>
+      <c r="H2487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2488" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2488">
+        <v>37074</v>
+      </c>
+      <c r="D2488">
+        <v>6673.32</v>
+      </c>
+      <c r="E2488">
+        <v>43747</v>
+      </c>
+      <c r="F2488">
+        <v>10.02</v>
+      </c>
+      <c r="G2488">
+        <v>3700</v>
+      </c>
+      <c r="H2488">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2489" t="inlineStr">
+        <is>
+          <t>Tundish Ramming Mix</t>
+        </is>
+      </c>
+      <c r="C2489">
+        <v>252450</v>
+      </c>
+      <c r="D2489">
+        <v>45441</v>
+      </c>
+      <c r="E2489">
+        <v>297891</v>
+      </c>
+      <c r="F2489">
+        <v>9.35</v>
+      </c>
+      <c r="G2489">
+        <v>27000</v>
+      </c>
+      <c r="H2489">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -92501,6 +92501,14 @@
       <c r="H2435">
         <v>8</v>
       </c>
+      <c r="I2435" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2435" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2436">
       <c r="A2436" t="inlineStr">
@@ -92531,6 +92539,14 @@
       <c r="H2436">
         <v>5</v>
       </c>
+      <c r="I2436" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2436" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2437">
       <c r="A2437" t="inlineStr">
@@ -92561,6 +92577,14 @@
       <c r="H2437">
         <v>6</v>
       </c>
+      <c r="I2437" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2437" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2438">
       <c r="A2438" t="inlineStr">
@@ -92591,6 +92615,14 @@
       <c r="H2438">
         <v>4</v>
       </c>
+      <c r="I2438" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2438" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2439">
       <c r="A2439" t="inlineStr">
@@ -92621,6 +92653,14 @@
       <c r="H2439">
         <v>6</v>
       </c>
+      <c r="I2439" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2439" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2440">
       <c r="A2440" t="inlineStr">
@@ -92651,6 +92691,14 @@
       <c r="H2440">
         <v>5</v>
       </c>
+      <c r="I2440" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2440" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2441">
       <c r="A2441" t="inlineStr">
@@ -92681,6 +92729,14 @@
       <c r="H2441">
         <v>6</v>
       </c>
+      <c r="I2441" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2441" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2442">
       <c r="A2442" t="inlineStr">
@@ -92711,6 +92767,14 @@
       <c r="H2442">
         <v>4</v>
       </c>
+      <c r="I2442" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2442" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2443">
       <c r="A2443" t="inlineStr">
@@ -92741,6 +92805,14 @@
       <c r="H2443">
         <v>1</v>
       </c>
+      <c r="I2443" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2443" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2444">
       <c r="A2444" t="inlineStr">
@@ -92771,6 +92843,14 @@
       <c r="H2444">
         <v>6</v>
       </c>
+      <c r="I2444" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2444" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2445">
       <c r="A2445" t="inlineStr">
@@ -92801,6 +92881,14 @@
       <c r="H2445">
         <v>4</v>
       </c>
+      <c r="I2445" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2445" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2446">
       <c r="A2446" t="inlineStr">
@@ -92831,6 +92919,14 @@
       <c r="H2446">
         <v>6</v>
       </c>
+      <c r="I2446" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2446" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2447">
       <c r="A2447" t="inlineStr">
@@ -92861,6 +92957,14 @@
       <c r="H2447">
         <v>4</v>
       </c>
+      <c r="I2447" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2447" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2448">
       <c r="A2448" t="inlineStr">
@@ -92891,6 +92995,14 @@
       <c r="H2448">
         <v>4</v>
       </c>
+      <c r="I2448" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2448" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2449">
       <c r="A2449" t="inlineStr">
@@ -92921,6 +93033,14 @@
       <c r="H2449">
         <v>2</v>
       </c>
+      <c r="I2449" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2449" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2450">
       <c r="A2450" t="inlineStr">
@@ -92951,6 +93071,14 @@
       <c r="H2450">
         <v>4</v>
       </c>
+      <c r="I2450" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2450" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2451">
       <c r="A2451" t="inlineStr">
@@ -92981,6 +93109,14 @@
       <c r="H2451">
         <v>4</v>
       </c>
+      <c r="I2451" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2451" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2452">
       <c r="A2452" t="inlineStr">
@@ -93011,6 +93147,14 @@
       <c r="H2452">
         <v>3</v>
       </c>
+      <c r="I2452" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2452" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2453">
       <c r="A2453" t="inlineStr">
@@ -93041,6 +93185,14 @@
       <c r="H2453">
         <v>2</v>
       </c>
+      <c r="I2453" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2453" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2454">
       <c r="A2454" t="inlineStr">
@@ -93071,6 +93223,14 @@
       <c r="H2454">
         <v>2</v>
       </c>
+      <c r="I2454" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2454" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2455">
       <c r="A2455" t="inlineStr">
@@ -93101,6 +93261,14 @@
       <c r="H2455">
         <v>2</v>
       </c>
+      <c r="I2455" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2455" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2456">
       <c r="A2456" t="inlineStr">
@@ -93131,6 +93299,14 @@
       <c r="H2456">
         <v>2</v>
       </c>
+      <c r="I2456" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2456" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2457">
       <c r="A2457" t="inlineStr">
@@ -93161,6 +93337,14 @@
       <c r="H2457">
         <v>3</v>
       </c>
+      <c r="I2457" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2457" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2458">
       <c r="A2458" t="inlineStr">
@@ -93191,6 +93375,14 @@
       <c r="H2458">
         <v>5</v>
       </c>
+      <c r="I2458" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2458" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2459">
       <c r="A2459" t="inlineStr">
@@ -93221,6 +93413,14 @@
       <c r="H2459">
         <v>3</v>
       </c>
+      <c r="I2459" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2459" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2460">
       <c r="A2460" t="inlineStr">
@@ -93251,6 +93451,14 @@
       <c r="H2460">
         <v>3</v>
       </c>
+      <c r="I2460" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2460" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2461">
       <c r="A2461" t="inlineStr">
@@ -93281,6 +93489,14 @@
       <c r="H2461">
         <v>2</v>
       </c>
+      <c r="I2461" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2461" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2462">
       <c r="A2462" t="inlineStr">
@@ -93311,6 +93527,14 @@
       <c r="H2462">
         <v>2</v>
       </c>
+      <c r="I2462" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2462" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2463">
       <c r="A2463" t="inlineStr">
@@ -93341,6 +93565,14 @@
       <c r="H2463">
         <v>2</v>
       </c>
+      <c r="I2463" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2463" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2464">
       <c r="A2464" t="inlineStr">
@@ -93371,6 +93603,14 @@
       <c r="H2464">
         <v>2</v>
       </c>
+      <c r="I2464" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2464" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2465">
       <c r="A2465" t="inlineStr">
@@ -93401,6 +93641,14 @@
       <c r="H2465">
         <v>2</v>
       </c>
+      <c r="I2465" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2465" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2466">
       <c r="A2466" t="inlineStr">
@@ -93431,6 +93679,14 @@
       <c r="H2466">
         <v>2</v>
       </c>
+      <c r="I2466" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2466" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2467">
       <c r="A2467" t="inlineStr">
@@ -93461,6 +93717,14 @@
       <c r="H2467">
         <v>1</v>
       </c>
+      <c r="I2467" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2467" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2468">
       <c r="A2468" t="inlineStr">
@@ -93491,6 +93755,14 @@
       <c r="H2468">
         <v>1</v>
       </c>
+      <c r="I2468" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2468" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2469">
       <c r="A2469" t="inlineStr">
@@ -93521,6 +93793,14 @@
       <c r="H2469">
         <v>2</v>
       </c>
+      <c r="I2469" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2469" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2470">
       <c r="A2470" t="inlineStr">
@@ -93551,6 +93831,14 @@
       <c r="H2470">
         <v>1</v>
       </c>
+      <c r="I2470" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2470" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2471">
       <c r="A2471" t="inlineStr">
@@ -93581,6 +93869,14 @@
       <c r="H2471">
         <v>2</v>
       </c>
+      <c r="I2471" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2471" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2472">
       <c r="A2472" t="inlineStr">
@@ -93611,6 +93907,14 @@
       <c r="H2472">
         <v>1</v>
       </c>
+      <c r="I2472" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2472" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2473">
       <c r="A2473" t="inlineStr">
@@ -93641,6 +93945,14 @@
       <c r="H2473">
         <v>2</v>
       </c>
+      <c r="I2473" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2473" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2474">
       <c r="A2474" t="inlineStr">
@@ -93671,6 +93983,14 @@
       <c r="H2474">
         <v>1</v>
       </c>
+      <c r="I2474" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2474" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2475">
       <c r="A2475" t="inlineStr">
@@ -93701,6 +94021,14 @@
       <c r="H2475">
         <v>1</v>
       </c>
+      <c r="I2475" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2475" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2476">
       <c r="A2476" t="inlineStr">
@@ -93731,6 +94059,14 @@
       <c r="H2476">
         <v>2</v>
       </c>
+      <c r="I2476" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2476" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2477">
       <c r="A2477" t="inlineStr">
@@ -93761,6 +94097,14 @@
       <c r="H2477">
         <v>2</v>
       </c>
+      <c r="I2477" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2477" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2478">
       <c r="A2478" t="inlineStr">
@@ -93791,6 +94135,14 @@
       <c r="H2478">
         <v>1</v>
       </c>
+      <c r="I2478" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2478" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2479">
       <c r="A2479" t="inlineStr">
@@ -93821,6 +94173,14 @@
       <c r="H2479">
         <v>1</v>
       </c>
+      <c r="I2479" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2479" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2480">
       <c r="A2480" t="inlineStr">
@@ -93851,6 +94211,14 @@
       <c r="H2480">
         <v>1</v>
       </c>
+      <c r="I2480" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2480" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2481">
       <c r="A2481" t="inlineStr">
@@ -93881,6 +94249,14 @@
       <c r="H2481">
         <v>1</v>
       </c>
+      <c r="I2481" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2481" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2482">
       <c r="A2482" t="inlineStr">
@@ -93911,6 +94287,14 @@
       <c r="H2482">
         <v>1</v>
       </c>
+      <c r="I2482" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2482" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2483">
       <c r="A2483" t="inlineStr">
@@ -93941,6 +94325,14 @@
       <c r="H2483">
         <v>1</v>
       </c>
+      <c r="I2483" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2483" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2484">
       <c r="A2484" t="inlineStr">
@@ -93971,6 +94363,14 @@
       <c r="H2484">
         <v>1</v>
       </c>
+      <c r="I2484" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2484" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2485">
       <c r="A2485" t="inlineStr">
@@ -94001,6 +94401,14 @@
       <c r="H2485">
         <v>3</v>
       </c>
+      <c r="I2485" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2485" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2486">
       <c r="A2486" t="inlineStr">
@@ -94031,6 +94439,14 @@
       <c r="H2486">
         <v>2</v>
       </c>
+      <c r="I2486" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2486" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2487">
       <c r="A2487" t="inlineStr">
@@ -94061,6 +94477,14 @@
       <c r="H2487">
         <v>1</v>
       </c>
+      <c r="I2487" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2487" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2488">
       <c r="A2488" t="inlineStr">
@@ -94091,6 +94515,14 @@
       <c r="H2488">
         <v>2</v>
       </c>
+      <c r="I2488" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2488" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2489">
       <c r="A2489" t="inlineStr">
@@ -94120,6 +94552,14 @@
       </c>
       <c r="H2489">
         <v>1</v>
+      </c>
+      <c r="I2489" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2489" s="2">
+        <v>46143</v>
       </c>
     </row>
   </sheetData>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2489"/>
+  <dimension ref="A1:J2497"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -90694,7 +90694,7 @@
       </c>
       <c r="I2387" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2387" s="2">
@@ -92356,7 +92356,7 @@
       </c>
       <c r="I2431" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2431" s="2">
@@ -92465,7 +92465,7 @@
       </c>
       <c r="I2434" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2434" s="2">
@@ -92484,22 +92484,22 @@
         </is>
       </c>
       <c r="C2435">
-        <v>1911094</v>
+        <v>4119008</v>
       </c>
       <c r="D2435">
-        <v>343996.92</v>
+        <v>741421.4399999999</v>
       </c>
       <c r="E2435">
-        <v>2255092</v>
+        <v>4860431</v>
       </c>
       <c r="F2435">
-        <v>197.02</v>
+        <v>424.64</v>
       </c>
       <c r="G2435">
         <v>9700</v>
       </c>
       <c r="H2435">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I2435" t="inlineStr">
         <is>
@@ -92513,7 +92513,7 @@
     <row r="2436">
       <c r="A2436" t="inlineStr">
         <is>
-          <t>A One Ispat Private Ltd</t>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
         </is>
       </c>
       <c r="B2436" t="inlineStr">
@@ -92522,22 +92522,22 @@
         </is>
       </c>
       <c r="C2436">
-        <v>1325537.5</v>
+        <v>2723374.5</v>
       </c>
       <c r="D2436">
-        <v>238596.8</v>
+        <v>490207.41</v>
       </c>
       <c r="E2436">
-        <v>1564133</v>
+        <v>3213582</v>
       </c>
       <c r="F2436">
-        <v>151.49</v>
+        <v>291.27</v>
       </c>
       <c r="G2436">
-        <v>8750</v>
+        <v>9350</v>
       </c>
       <c r="H2436">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I2436" t="inlineStr">
         <is>
@@ -92551,7 +92551,7 @@
     <row r="2437">
       <c r="A2437" t="inlineStr">
         <is>
-          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+          <t>A One Ispat Private Ltd</t>
         </is>
       </c>
       <c r="B2437" t="inlineStr">
@@ -92560,26 +92560,26 @@
         </is>
       </c>
       <c r="C2437">
-        <v>1272398</v>
+        <v>2201150</v>
       </c>
       <c r="D2437">
-        <v>229031.64</v>
+        <v>396207.06</v>
       </c>
       <c r="E2437">
-        <v>1501429</v>
+        <v>2597357</v>
       </c>
       <c r="F2437">
-        <v>125.98</v>
+        <v>251.56</v>
       </c>
       <c r="G2437">
-        <v>10100</v>
+        <v>8750</v>
       </c>
       <c r="H2437">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2437" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2437" s="2">
@@ -92589,7 +92589,7 @@
     <row r="2438">
       <c r="A2438" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
         </is>
       </c>
       <c r="B2438" t="inlineStr">
@@ -92598,26 +92598,26 @@
         </is>
       </c>
       <c r="C2438">
-        <v>1092344</v>
+        <v>2182711</v>
       </c>
       <c r="D2438">
-        <v>202686.84</v>
+        <v>392887.98</v>
       </c>
       <c r="E2438">
-        <v>1328724</v>
+        <v>2575598</v>
       </c>
       <c r="F2438">
-        <v>124.13</v>
+        <v>216.11</v>
       </c>
       <c r="G2438">
-        <v>8800</v>
+        <v>10100</v>
       </c>
       <c r="H2438">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I2438" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2438" s="2">
@@ -92627,7 +92627,7 @@
     <row r="2439">
       <c r="A2439" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
         </is>
       </c>
       <c r="B2439" t="inlineStr">
@@ -92636,22 +92636,22 @@
         </is>
       </c>
       <c r="C2439">
-        <v>1106479</v>
+        <v>1846504</v>
       </c>
       <c r="D2439">
-        <v>199166.22</v>
+        <v>354011.04</v>
       </c>
       <c r="E2439">
-        <v>1305646</v>
+        <v>2320738</v>
       </c>
       <c r="F2439">
-        <v>118.34</v>
+        <v>209.83</v>
       </c>
       <c r="G2439">
-        <v>9350</v>
+        <v>8800</v>
       </c>
       <c r="H2439">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2439" t="inlineStr">
         <is>
@@ -92665,7 +92665,7 @@
     <row r="2440">
       <c r="A2440" t="inlineStr">
         <is>
-          <t>Minera Steel &amp; Power Pvt Ltd</t>
+          <t>Adishakti Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2440" t="inlineStr">
@@ -92674,22 +92674,22 @@
         </is>
       </c>
       <c r="C2440">
-        <v>1056960</v>
+        <v>1822100</v>
       </c>
       <c r="D2440">
-        <v>190252.8</v>
+        <v>340273.86</v>
       </c>
       <c r="E2440">
-        <v>1247212</v>
+        <v>2230685</v>
       </c>
       <c r="F2440">
-        <v>117.44</v>
+        <v>208.24</v>
       </c>
       <c r="G2440">
-        <v>9000</v>
+        <v>8750</v>
       </c>
       <c r="H2440">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I2440" t="inlineStr">
         <is>
@@ -92703,7 +92703,7 @@
     <row r="2441">
       <c r="A2441" t="inlineStr">
         <is>
-          <t>Meenakshi Udyog India Pvt Ltd.</t>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2441" t="inlineStr">
@@ -92712,26 +92712,26 @@
         </is>
       </c>
       <c r="C2441">
-        <v>1123687.5</v>
+        <v>1787400</v>
       </c>
       <c r="D2441">
-        <v>202263.75</v>
+        <v>321732</v>
       </c>
       <c r="E2441">
-        <v>1325952</v>
+        <v>2109131</v>
       </c>
       <c r="F2441">
-        <v>115.25</v>
+        <v>198.6</v>
       </c>
       <c r="G2441">
-        <v>9750</v>
+        <v>9000</v>
       </c>
       <c r="H2441">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I2441" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2441" s="2">
@@ -92741,31 +92741,28 @@
     <row r="2442">
       <c r="A2442" t="inlineStr">
         <is>
-          <t>KUBAIR STEEL AND POWER LLP</t>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
         </is>
       </c>
       <c r="B2442" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2442">
-        <v>989285</v>
+        <v>659702</v>
       </c>
       <c r="D2442">
-        <v>178071.3</v>
-      </c>
-      <c r="E2442">
-        <v>1167358</v>
+        <v>97106.04000000001</v>
       </c>
       <c r="F2442">
-        <v>112.03</v>
+        <v>194.03</v>
       </c>
       <c r="G2442">
-        <v>8830.536463447292</v>
+        <v>3400</v>
       </c>
       <c r="H2442">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I2442" t="inlineStr">
         <is>
@@ -92779,31 +92776,31 @@
     <row r="2443">
       <c r="A2443" t="inlineStr">
         <is>
-          <t>S.R. STEEL PVT LTD</t>
+          <t>TEXCON STEELS LIMITED</t>
         </is>
       </c>
       <c r="B2443" t="inlineStr">
         <is>
-          <t>Ordinary Ramming Mass</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2443">
-        <v>13328</v>
+        <v>1521301.5</v>
       </c>
       <c r="D2443">
-        <v>0</v>
+        <v>273834.27</v>
       </c>
       <c r="E2443">
-        <v>13328</v>
+        <v>1795135</v>
       </c>
       <c r="F2443">
-        <v>112</v>
+        <v>177.93</v>
       </c>
       <c r="G2443">
-        <v>119</v>
+        <v>8550</v>
       </c>
       <c r="H2443">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2443" t="inlineStr">
         <is>
@@ -92817,7 +92814,7 @@
     <row r="2444">
       <c r="A2444" t="inlineStr">
         <is>
-          <t>Adishakti Smelters Private Limited</t>
+          <t>Prakash Ferrous Industries Pvt Ltd</t>
         </is>
       </c>
       <c r="B2444" t="inlineStr">
@@ -92826,26 +92823,26 @@
         </is>
       </c>
       <c r="C2444">
-        <v>971950</v>
+        <v>1825984</v>
       </c>
       <c r="D2444">
-        <v>174951.04</v>
+        <v>328677.12</v>
       </c>
       <c r="E2444">
-        <v>1146902</v>
+        <v>2154661</v>
       </c>
       <c r="F2444">
-        <v>111.08</v>
+        <v>177.28</v>
       </c>
       <c r="G2444">
-        <v>8749.999999999998</v>
+        <v>10300</v>
       </c>
       <c r="H2444">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2444" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2444" s="2">
@@ -92855,31 +92852,31 @@
     <row r="2445">
       <c r="A2445" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+          <t>Arun Vyapar Udyog Private Limited</t>
         </is>
       </c>
       <c r="B2445" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2445">
-        <v>329154</v>
+        <v>1784973</v>
       </c>
       <c r="D2445">
-        <v>53182.8</v>
+        <v>321295.14</v>
       </c>
       <c r="E2445">
-        <v>388401.92</v>
+        <v>2106269</v>
       </c>
       <c r="F2445">
-        <v>96.81</v>
+        <v>176.73</v>
       </c>
       <c r="G2445">
-        <v>3400</v>
+        <v>10100</v>
       </c>
       <c r="H2445">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I2445" t="inlineStr">
         <is>
@@ -92893,35 +92890,35 @@
     <row r="2446">
       <c r="A2446" t="inlineStr">
         <is>
-          <t>Mahrishi Meltchems Pvt Ltd</t>
+          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
         </is>
       </c>
       <c r="B2446" t="inlineStr">
         <is>
-          <t>Quartz Powder</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2446">
-        <v>165644.5</v>
+        <v>1417150.5</v>
       </c>
       <c r="D2446">
-        <v>8282.225</v>
+        <v>255087.09</v>
       </c>
       <c r="E2446">
-        <v>173926.725</v>
+        <v>1672237</v>
       </c>
       <c r="F2446">
-        <v>85.75</v>
+        <v>160.13</v>
       </c>
       <c r="G2446">
-        <v>1931.714285714286</v>
+        <v>8850</v>
       </c>
       <c r="H2446">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2446" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2446" s="2">
@@ -92931,7 +92928,7 @@
     <row r="2447">
       <c r="A2447" t="inlineStr">
         <is>
-          <t>Arun Vyapar Udyog Private Limited</t>
+          <t>RDTMT Steels India Pvt Ltd</t>
         </is>
       </c>
       <c r="B2447" t="inlineStr">
@@ -92940,22 +92937,22 @@
         </is>
       </c>
       <c r="C2447">
-        <v>860722</v>
+        <v>1355801</v>
       </c>
       <c r="D2447">
-        <v>154929.96</v>
+        <v>244044.2</v>
       </c>
       <c r="E2447">
-        <v>1015652</v>
+        <v>1599845</v>
       </c>
       <c r="F2447">
-        <v>85.22</v>
+        <v>156.74</v>
       </c>
       <c r="G2447">
-        <v>10100</v>
+        <v>8650</v>
       </c>
       <c r="H2447">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2447" t="inlineStr">
         <is>
@@ -92969,7 +92966,7 @@
     <row r="2448">
       <c r="A2448" t="inlineStr">
         <is>
-          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+          <t>Meenakshi Udyog India Pvt Ltd.</t>
         </is>
       </c>
       <c r="B2448" t="inlineStr">
@@ -92978,26 +92975,26 @@
         </is>
       </c>
       <c r="C2448">
-        <v>714609</v>
+        <v>1517490</v>
       </c>
       <c r="D2448">
-        <v>128629.62</v>
+        <v>273148.2</v>
       </c>
       <c r="E2448">
-        <v>843239</v>
+        <v>1790639</v>
       </c>
       <c r="F2448">
-        <v>83.58</v>
+        <v>155.64</v>
       </c>
       <c r="G2448">
-        <v>8550</v>
+        <v>9750</v>
       </c>
       <c r="H2448">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I2448" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2448" s="2">
@@ -93007,31 +93004,31 @@
     <row r="2449">
       <c r="A2449" t="inlineStr">
         <is>
-          <t>BMM ISPAT LIMITED</t>
+          <t>Mahrishi Alloys Pvt. Ltd.</t>
         </is>
       </c>
       <c r="B2449" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2449">
-        <v>616231</v>
+        <v>629689</v>
       </c>
       <c r="D2449">
-        <v>110921.58</v>
+        <v>113344.04</v>
       </c>
       <c r="E2449">
-        <v>727153</v>
+        <v>743033</v>
       </c>
       <c r="F2449">
-        <v>81.62</v>
+        <v>151.58</v>
       </c>
       <c r="G2449">
-        <v>7550</v>
+        <v>4154.16941549017</v>
       </c>
       <c r="H2449">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2449" t="inlineStr">
         <is>
@@ -93054,22 +93051,22 @@
         </is>
       </c>
       <c r="C2450">
-        <v>676536</v>
+        <v>1289103</v>
       </c>
       <c r="D2450">
-        <v>130065.12</v>
+        <v>249517.44</v>
       </c>
       <c r="E2450">
-        <v>852649</v>
+        <v>1635725</v>
       </c>
       <c r="F2450">
-        <v>80.53999999999999</v>
+        <v>150.95</v>
       </c>
       <c r="G2450">
-        <v>8400</v>
+        <v>8539.933752898311</v>
       </c>
       <c r="H2450">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I2450" t="inlineStr">
         <is>
@@ -93083,7 +93080,7 @@
     <row r="2451">
       <c r="A2451" t="inlineStr">
         <is>
-          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
+          <t>KUBAIR STEEL AND POWER LLP</t>
         </is>
       </c>
       <c r="B2451" t="inlineStr">
@@ -93092,22 +93089,22 @@
         </is>
       </c>
       <c r="C2451">
-        <v>667201.5</v>
+        <v>1293017</v>
       </c>
       <c r="D2451">
-        <v>120096.27</v>
+        <v>232743.06</v>
       </c>
       <c r="E2451">
-        <v>787298</v>
+        <v>1525762</v>
       </c>
       <c r="F2451">
-        <v>75.39</v>
+        <v>146.35</v>
       </c>
       <c r="G2451">
-        <v>8850</v>
+        <v>8835.100785787496</v>
       </c>
       <c r="H2451">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2451" t="inlineStr">
         <is>
@@ -93121,31 +93118,31 @@
     <row r="2452">
       <c r="A2452" t="inlineStr">
         <is>
-          <t>RDTMT Steels India Pvt Ltd</t>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
         </is>
       </c>
       <c r="B2452" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Quartz Powder</t>
         </is>
       </c>
       <c r="C2452">
-        <v>650307</v>
+        <v>267538.5</v>
       </c>
       <c r="D2452">
-        <v>117055.26</v>
+        <v>13376.945</v>
       </c>
       <c r="E2452">
-        <v>767362</v>
+        <v>280915.725</v>
       </c>
       <c r="F2452">
-        <v>75.18000000000001</v>
+        <v>138.84</v>
       </c>
       <c r="G2452">
-        <v>8650</v>
+        <v>1926.955488331893</v>
       </c>
       <c r="H2452">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I2452" t="inlineStr">
         <is>
@@ -93159,7 +93156,7 @@
     <row r="2453">
       <c r="A2453" t="inlineStr">
         <is>
-          <t>Mahrishi Alloys Pvt. Ltd.</t>
+          <t>Kanishk Steel Industries Ltd</t>
         </is>
       </c>
       <c r="B2453" t="inlineStr">
@@ -93168,26 +93165,26 @@
         </is>
       </c>
       <c r="C2453">
-        <v>294151.5</v>
+        <v>1391530</v>
       </c>
       <c r="D2453">
-        <v>52947.28</v>
+        <v>250475.4</v>
       </c>
       <c r="E2453">
-        <v>347099</v>
+        <v>1642006</v>
       </c>
       <c r="F2453">
-        <v>72.63</v>
+        <v>135.1</v>
       </c>
       <c r="G2453">
-        <v>4050</v>
+        <v>10300</v>
       </c>
       <c r="H2453">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2453" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2453" s="2">
@@ -93197,7 +93194,7 @@
     <row r="2454">
       <c r="A2454" t="inlineStr">
         <is>
-          <t>TEXCON STEELS LIMITED</t>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
         </is>
       </c>
       <c r="B2454" t="inlineStr">
@@ -93206,22 +93203,22 @@
         </is>
       </c>
       <c r="C2454">
-        <v>608247</v>
+        <v>1083632</v>
       </c>
       <c r="D2454">
-        <v>109484.46</v>
+        <v>195053.76</v>
       </c>
       <c r="E2454">
-        <v>717731</v>
+        <v>1278685</v>
       </c>
       <c r="F2454">
-        <v>71.14</v>
+        <v>123.14</v>
       </c>
       <c r="G2454">
-        <v>8550</v>
+        <v>8800.000000000002</v>
       </c>
       <c r="H2454">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2454" t="inlineStr">
         <is>
@@ -93235,31 +93232,31 @@
     <row r="2455">
       <c r="A2455" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+          <t>BMM ISPAT LIMITED</t>
         </is>
       </c>
       <c r="B2455" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2455">
-        <v>611424</v>
+        <v>913625.5</v>
       </c>
       <c r="D2455">
-        <v>110056.32</v>
+        <v>164452.59</v>
       </c>
       <c r="E2455">
-        <v>721480</v>
+        <v>1078079</v>
       </c>
       <c r="F2455">
-        <v>69.47999999999999</v>
+        <v>121.01</v>
       </c>
       <c r="G2455">
-        <v>8800.000000000002</v>
+        <v>7550</v>
       </c>
       <c r="H2455">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2455" t="inlineStr">
         <is>
@@ -93273,35 +93270,35 @@
     <row r="2456">
       <c r="A2456" t="inlineStr">
         <is>
-          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
         </is>
       </c>
       <c r="B2456" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2456">
-        <v>468013</v>
+        <v>1018048.5</v>
       </c>
       <c r="D2456">
-        <v>84242.34</v>
+        <v>183248.73</v>
       </c>
       <c r="E2456">
-        <v>552256</v>
+        <v>1201298</v>
       </c>
       <c r="F2456">
-        <v>67.34</v>
+        <v>119.07</v>
       </c>
       <c r="G2456">
-        <v>6950</v>
+        <v>8550</v>
       </c>
       <c r="H2456">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2456" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2456" s="2">
@@ -93311,31 +93308,31 @@
     <row r="2457">
       <c r="A2457" t="inlineStr">
         <is>
-          <t>RELIANCE CONCAST SOLUTIONS</t>
+          <t>S.R. STEEL PVT LTD</t>
         </is>
       </c>
       <c r="B2457" t="inlineStr">
         <is>
-          <t>Quartz Powder</t>
+          <t>Ordinary Ramming Mass</t>
         </is>
       </c>
       <c r="C2457">
-        <v>182544</v>
+        <v>11709.6</v>
       </c>
       <c r="D2457">
-        <v>9127.200000000001</v>
+        <v>0</v>
       </c>
       <c r="E2457">
-        <v>191671</v>
+        <v>11709.6</v>
       </c>
       <c r="F2457">
-        <v>61.35</v>
+        <v>112</v>
       </c>
       <c r="G2457">
-        <v>2975.452322738387</v>
+        <v>104.55</v>
       </c>
       <c r="H2457">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2457" t="inlineStr">
         <is>
@@ -93349,35 +93346,35 @@
     <row r="2458">
       <c r="A2458" t="inlineStr">
         <is>
-          <t>Shyam Ferrous Ltd.</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2458" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2458">
-        <v>512662.5</v>
+        <v>485100</v>
       </c>
       <c r="D2458">
-        <v>92279.25999999999</v>
+        <v>87318</v>
       </c>
       <c r="E2458">
-        <v>604943</v>
+        <v>572418</v>
       </c>
       <c r="F2458">
-        <v>58.59</v>
+        <v>110.25</v>
       </c>
       <c r="G2458">
-        <v>8750</v>
+        <v>4400</v>
       </c>
       <c r="H2458">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2458" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2458" s="2">
@@ -93387,31 +93384,31 @@
     <row r="2459">
       <c r="A2459" t="inlineStr">
         <is>
-          <t>Shri Tirupati Steel Cast Ltd</t>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
         </is>
       </c>
       <c r="B2459" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2459">
-        <v>191095.5</v>
+        <v>975384</v>
       </c>
       <c r="D2459">
-        <v>34397.22</v>
+        <v>175569.12</v>
       </c>
       <c r="E2459">
-        <v>225493</v>
+        <v>1150954</v>
       </c>
       <c r="F2459">
-        <v>55.39</v>
+        <v>106.02</v>
       </c>
       <c r="G2459">
-        <v>3450</v>
+        <v>9200</v>
       </c>
       <c r="H2459">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I2459" t="inlineStr">
         <is>
@@ -93425,35 +93422,35 @@
     <row r="2460">
       <c r="A2460" t="inlineStr">
         <is>
-          <t>ADRI STEEL PRIVATE LIMITED</t>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2460" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2460">
-        <v>476612.5</v>
+        <v>715433</v>
       </c>
       <c r="D2460">
-        <v>91627.66</v>
+        <v>128777.94</v>
       </c>
       <c r="E2460">
-        <v>600670</v>
+        <v>844212</v>
       </c>
       <c r="F2460">
-        <v>54.47</v>
+        <v>102.94</v>
       </c>
       <c r="G2460">
-        <v>8750</v>
+        <v>6950</v>
       </c>
       <c r="H2460">
         <v>3</v>
       </c>
       <c r="I2460" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2460" s="2">
@@ -93463,7 +93460,7 @@
     <row r="2461">
       <c r="A2461" t="inlineStr">
         <is>
-          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2461" t="inlineStr">
@@ -93472,26 +93469,26 @@
         </is>
       </c>
       <c r="C2461">
-        <v>443700</v>
+        <v>1016859</v>
       </c>
       <c r="D2461">
-        <v>79866</v>
+        <v>183034.62</v>
       </c>
       <c r="E2461">
-        <v>523566</v>
+        <v>1199895</v>
       </c>
       <c r="F2461">
-        <v>51</v>
+        <v>101.18</v>
       </c>
       <c r="G2461">
-        <v>8700</v>
+        <v>10050</v>
       </c>
       <c r="H2461">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2461" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2461" s="2">
@@ -93501,7 +93498,7 @@
     <row r="2462">
       <c r="A2462" t="inlineStr">
         <is>
-          <t>Prakash Ferrous Industries Pvt Ltd</t>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
         </is>
       </c>
       <c r="B2462" t="inlineStr">
@@ -93510,26 +93507,26 @@
         </is>
       </c>
       <c r="C2462">
-        <v>465148</v>
+        <v>835440</v>
       </c>
       <c r="D2462">
-        <v>83726.64</v>
+        <v>150379.22</v>
       </c>
       <c r="E2462">
-        <v>548875</v>
+        <v>985819</v>
       </c>
       <c r="F2462">
-        <v>45.16</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G2462">
-        <v>10300</v>
+        <v>8850</v>
       </c>
       <c r="H2462">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2462" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2462" s="2">
@@ -93539,7 +93536,7 @@
     <row r="2463">
       <c r="A2463" t="inlineStr">
         <is>
-          <t>Kanishk Steel Industries Ltd</t>
+          <t>Keshree Metalurgies Pvt Ltd</t>
         </is>
       </c>
       <c r="B2463" t="inlineStr">
@@ -93548,26 +93545,26 @@
         </is>
       </c>
       <c r="C2463">
-        <v>462470</v>
+        <v>811968</v>
       </c>
       <c r="D2463">
-        <v>83244.60000000001</v>
+        <v>146154.24</v>
       </c>
       <c r="E2463">
-        <v>545715</v>
+        <v>958123</v>
       </c>
       <c r="F2463">
-        <v>44.9</v>
+        <v>84.58</v>
       </c>
       <c r="G2463">
-        <v>10300</v>
+        <v>9600</v>
       </c>
       <c r="H2463">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2463" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2463" s="2">
@@ -93577,7 +93574,7 @@
     <row r="2464">
       <c r="A2464" t="inlineStr">
         <is>
-          <t>GBR Metals Pvt Ltd</t>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2464" t="inlineStr">
@@ -93586,26 +93583,26 @@
         </is>
       </c>
       <c r="C2464">
-        <v>439295</v>
+        <v>690550</v>
       </c>
       <c r="D2464">
-        <v>79073.10000000001</v>
+        <v>130136.42</v>
       </c>
       <c r="E2464">
-        <v>518368</v>
+        <v>853116</v>
       </c>
       <c r="F2464">
-        <v>42.65</v>
+        <v>78.92</v>
       </c>
       <c r="G2464">
-        <v>10300</v>
+        <v>8750</v>
       </c>
       <c r="H2464">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2464" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2464" s="2">
@@ -93615,28 +93612,28 @@
     <row r="2465">
       <c r="A2465" t="inlineStr">
         <is>
-          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
         </is>
       </c>
       <c r="B2465" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2465">
-        <v>271012.5</v>
+        <v>678592.5</v>
       </c>
       <c r="D2465">
-        <v>48782.25</v>
+        <v>122146.65</v>
       </c>
       <c r="E2465">
-        <v>319794</v>
+        <v>800740</v>
       </c>
       <c r="F2465">
-        <v>40.15000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="G2465">
-        <v>6749.999999999999</v>
+        <v>8650</v>
       </c>
       <c r="H2465">
         <v>2</v>
@@ -93653,7 +93650,7 @@
     <row r="2466">
       <c r="A2466" t="inlineStr">
         <is>
-          <t>Keshree Metalurgies Pvt Ltd</t>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2466" t="inlineStr">
@@ -93662,26 +93659,26 @@
         </is>
       </c>
       <c r="C2466">
-        <v>384000</v>
+        <v>678861</v>
       </c>
       <c r="D2466">
-        <v>69120</v>
+        <v>122194.98</v>
       </c>
       <c r="E2466">
-        <v>453120</v>
+        <v>801056</v>
       </c>
       <c r="F2466">
-        <v>40</v>
+        <v>78.03</v>
       </c>
       <c r="G2466">
-        <v>9600</v>
+        <v>8700</v>
       </c>
       <c r="H2466">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2466" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2466" s="2">
@@ -93691,7 +93688,7 @@
     <row r="2467">
       <c r="A2467" t="inlineStr">
         <is>
-          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+          <t>Shri Tirupati Steel Cast Ltd</t>
         </is>
       </c>
       <c r="B2467" t="inlineStr">
@@ -93700,26 +93697,26 @@
         </is>
       </c>
       <c r="C2467">
-        <v>134274</v>
+        <v>264063</v>
       </c>
       <c r="D2467">
-        <v>24169.32</v>
+        <v>47531.38</v>
       </c>
       <c r="E2467">
-        <v>158443</v>
+        <v>311595</v>
       </c>
       <c r="F2467">
-        <v>38.92</v>
+        <v>76.53999999999999</v>
       </c>
       <c r="G2467">
         <v>3450</v>
       </c>
       <c r="H2467">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2467" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2467" s="2">
@@ -93729,35 +93726,35 @@
     <row r="2468">
       <c r="A2468" t="inlineStr">
         <is>
-          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+          <t>RELIANCE CONCAST SOLUTIONS</t>
         </is>
       </c>
       <c r="B2468" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Quartz Powder</t>
         </is>
       </c>
       <c r="C2468">
-        <v>327056.5</v>
+        <v>182544</v>
       </c>
       <c r="D2468">
-        <v>58870.17</v>
+        <v>9127.200000000001</v>
       </c>
       <c r="E2468">
-        <v>385927</v>
+        <v>191671</v>
       </c>
       <c r="F2468">
-        <v>37.81</v>
+        <v>61.35</v>
       </c>
       <c r="G2468">
-        <v>8650</v>
+        <v>2975.452322738387</v>
       </c>
       <c r="H2468">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2468" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2468" s="2">
@@ -93767,7 +93764,7 @@
     <row r="2469">
       <c r="A2469" t="inlineStr">
         <is>
-          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+          <t>Shyam Ferrous Ltd.</t>
         </is>
       </c>
       <c r="B2469" t="inlineStr">
@@ -93776,26 +93773,26 @@
         </is>
       </c>
       <c r="C2469">
-        <v>327980</v>
+        <v>512662.5</v>
       </c>
       <c r="D2469">
-        <v>59036.4</v>
+        <v>92279.25999999999</v>
       </c>
       <c r="E2469">
-        <v>387017</v>
+        <v>604943</v>
       </c>
       <c r="F2469">
-        <v>35.65</v>
+        <v>58.59</v>
       </c>
       <c r="G2469">
-        <v>9200</v>
+        <v>8750</v>
       </c>
       <c r="H2469">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2469" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2469" s="2">
@@ -93805,35 +93802,35 @@
     <row r="2470">
       <c r="A2470" t="inlineStr">
         <is>
-          <t>VMC Steel and Alloys Industry</t>
+          <t>RDTMT Steels India Pvt Ltd</t>
         </is>
       </c>
       <c r="B2470" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2470">
-        <v>368445</v>
+        <v>169571</v>
       </c>
       <c r="D2470">
-        <v>66320.10000000001</v>
+        <v>30522.78</v>
       </c>
       <c r="E2470">
-        <v>434765</v>
+        <v>200093</v>
       </c>
       <c r="F2470">
-        <v>35.09</v>
+        <v>45.83000000000001</v>
       </c>
       <c r="G2470">
-        <v>10500</v>
+        <v>3700</v>
       </c>
       <c r="H2470">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2470" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2470" s="2">
@@ -93843,28 +93840,28 @@
     <row r="2471">
       <c r="A2471" t="inlineStr">
         <is>
-          <t>PARAGON STEEL DISTRIBUITORS</t>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
         </is>
       </c>
       <c r="B2471" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2471">
-        <v>238000</v>
+        <v>162615</v>
       </c>
       <c r="D2471">
-        <v>42840</v>
+        <v>29270.7</v>
       </c>
       <c r="E2471">
-        <v>280840</v>
+        <v>191886</v>
       </c>
       <c r="F2471">
-        <v>35</v>
+        <v>43.95</v>
       </c>
       <c r="G2471">
-        <v>6800</v>
+        <v>3700</v>
       </c>
       <c r="H2471">
         <v>2</v>
@@ -93881,7 +93878,7 @@
     <row r="2472">
       <c r="A2472" t="inlineStr">
         <is>
-          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+          <t>GBR Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2472" t="inlineStr">
@@ -93890,26 +93887,26 @@
         </is>
       </c>
       <c r="C2472">
-        <v>306298.5</v>
+        <v>439295</v>
       </c>
       <c r="D2472">
-        <v>55133.74</v>
+        <v>79073.10000000001</v>
       </c>
       <c r="E2472">
-        <v>361432</v>
+        <v>518368</v>
       </c>
       <c r="F2472">
-        <v>34.61</v>
+        <v>42.65</v>
       </c>
       <c r="G2472">
-        <v>8850</v>
+        <v>10300</v>
       </c>
       <c r="H2472">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2472" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2472" s="2">
@@ -93919,35 +93916,35 @@
     <row r="2473">
       <c r="A2473" t="inlineStr">
         <is>
-          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+          <t>KRISHNA STEEL ROLLING MILLS</t>
         </is>
       </c>
       <c r="B2473" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2473">
-        <v>141655</v>
+        <v>286160</v>
       </c>
       <c r="D2473">
-        <v>25497.9</v>
+        <v>66912.84</v>
       </c>
       <c r="E2473">
-        <v>167153</v>
+        <v>438651</v>
       </c>
       <c r="F2473">
-        <v>34.55</v>
+        <v>40.88</v>
       </c>
       <c r="G2473">
-        <v>4100</v>
+        <v>7000.000000000001</v>
       </c>
       <c r="H2473">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2473" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2473" s="2">
@@ -93957,35 +93954,35 @@
     <row r="2474">
       <c r="A2474" t="inlineStr">
         <is>
-          <t>Sri M.S.T. Smelters Private Limited</t>
+          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2474" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2474">
-        <v>264430.5</v>
+        <v>271012.5</v>
       </c>
       <c r="D2474">
-        <v>47597.49</v>
+        <v>48782.25</v>
       </c>
       <c r="E2474">
-        <v>312028</v>
+        <v>319794</v>
       </c>
       <c r="F2474">
-        <v>30.57</v>
+        <v>40.15000000000001</v>
       </c>
       <c r="G2474">
-        <v>8650</v>
+        <v>6749.999999999999</v>
       </c>
       <c r="H2474">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2474" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2474" s="2">
@@ -93995,35 +93992,35 @@
     <row r="2475">
       <c r="A2475" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
         </is>
       </c>
       <c r="B2475" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2475">
-        <v>306324</v>
+        <v>134274</v>
       </c>
       <c r="D2475">
-        <v>55138.32</v>
+        <v>24169.32</v>
       </c>
       <c r="E2475">
-        <v>361463</v>
+        <v>158443</v>
       </c>
       <c r="F2475">
-        <v>30.48</v>
+        <v>38.92</v>
       </c>
       <c r="G2475">
-        <v>10050</v>
+        <v>3450</v>
       </c>
       <c r="H2475">
         <v>1</v>
       </c>
       <c r="I2475" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2475" s="2">
@@ -94033,35 +94030,35 @@
     <row r="2476">
       <c r="A2476" t="inlineStr">
         <is>
-          <t>Meenakshi Steels</t>
+          <t>SREE PALANIANDAVAR ALLOYS AND STEELS PVT LTD</t>
         </is>
       </c>
       <c r="B2476" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2476">
-        <v>315420</v>
+        <v>244779</v>
       </c>
       <c r="D2476">
-        <v>56775.6</v>
+        <v>44060.22</v>
       </c>
       <c r="E2476">
-        <v>372196</v>
+        <v>288839</v>
       </c>
       <c r="F2476">
-        <v>30.04</v>
+        <v>35.22</v>
       </c>
       <c r="G2476">
-        <v>10500</v>
+        <v>6950</v>
       </c>
       <c r="H2476">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2476" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2476" s="2">
@@ -94071,35 +94068,35 @@
     <row r="2477">
       <c r="A2477" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>VGK STEELS</t>
         </is>
       </c>
       <c r="B2477" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2477">
-        <v>131208</v>
+        <v>307737.5</v>
       </c>
       <c r="D2477">
-        <v>23617.44</v>
+        <v>55392.75</v>
       </c>
       <c r="E2477">
-        <v>154825</v>
+        <v>363130</v>
       </c>
       <c r="F2477">
-        <v>29.82</v>
+        <v>35.17</v>
       </c>
       <c r="G2477">
-        <v>4400</v>
+        <v>8750</v>
       </c>
       <c r="H2477">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2477" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2477" s="2">
@@ -94109,7 +94106,7 @@
     <row r="2478">
       <c r="A2478" t="inlineStr">
         <is>
-          <t>BLUE GOLD STEEL INDUSTRIES</t>
+          <t>VMC Steel and Alloys Industry</t>
         </is>
       </c>
       <c r="B2478" t="inlineStr">
@@ -94118,19 +94115,19 @@
         </is>
       </c>
       <c r="C2478">
-        <v>228112.5</v>
+        <v>368445</v>
       </c>
       <c r="D2478">
-        <v>41060.26</v>
+        <v>66320.10000000001</v>
       </c>
       <c r="E2478">
-        <v>269173</v>
+        <v>434765</v>
       </c>
       <c r="F2478">
-        <v>26.07</v>
+        <v>35.09</v>
       </c>
       <c r="G2478">
-        <v>8750</v>
+        <v>10500</v>
       </c>
       <c r="H2478">
         <v>1</v>
@@ -94147,7 +94144,7 @@
     <row r="2479">
       <c r="A2479" t="inlineStr">
         <is>
-          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+          <t>PARAGON STEEL DISTRIBUITORS</t>
         </is>
       </c>
       <c r="B2479" t="inlineStr">
@@ -94156,26 +94153,26 @@
         </is>
       </c>
       <c r="C2479">
-        <v>171948</v>
+        <v>238000</v>
       </c>
       <c r="D2479">
-        <v>30950.64</v>
+        <v>42840</v>
       </c>
       <c r="E2479">
-        <v>202899</v>
+        <v>280840</v>
       </c>
       <c r="F2479">
-        <v>24.92</v>
+        <v>35</v>
       </c>
       <c r="G2479">
-        <v>6899.999999999999</v>
+        <v>6800</v>
       </c>
       <c r="H2479">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2479" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2479" s="2">
@@ -94185,7 +94182,7 @@
     <row r="2480">
       <c r="A2480" t="inlineStr">
         <is>
-          <t>BLUE GOLD STEEL INDUSTRIES</t>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
         </is>
       </c>
       <c r="B2480" t="inlineStr">
@@ -94194,26 +94191,26 @@
         </is>
       </c>
       <c r="C2480">
-        <v>65895</v>
+        <v>141655</v>
       </c>
       <c r="D2480">
-        <v>11861.1</v>
+        <v>25497.9</v>
       </c>
       <c r="E2480">
-        <v>77756</v>
+        <v>167153</v>
       </c>
       <c r="F2480">
-        <v>19.1</v>
+        <v>34.55</v>
       </c>
       <c r="G2480">
-        <v>3450</v>
+        <v>4100</v>
       </c>
       <c r="H2480">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2480" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2480" s="2">
@@ -94223,35 +94220,35 @@
     <row r="2481">
       <c r="A2481" t="inlineStr">
         <is>
-          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+          <t>Sri M.S.T. Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2481" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2481">
-        <v>69301</v>
+        <v>264430.5</v>
       </c>
       <c r="D2481">
-        <v>12474.18</v>
+        <v>47597.49</v>
       </c>
       <c r="E2481">
-        <v>81775</v>
+        <v>312028</v>
       </c>
       <c r="F2481">
-        <v>18.73</v>
+        <v>30.57</v>
       </c>
       <c r="G2481">
-        <v>3700</v>
+        <v>8650</v>
       </c>
       <c r="H2481">
         <v>1</v>
       </c>
       <c r="I2481" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2481" s="2">
@@ -94261,35 +94258,35 @@
     <row r="2482">
       <c r="A2482" t="inlineStr">
         <is>
-          <t>KRISHNA STEEL ROLLING MILLS</t>
+          <t>Meenakshi Steels</t>
         </is>
       </c>
       <c r="B2482" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2482">
-        <v>60758</v>
+        <v>315420</v>
       </c>
       <c r="D2482">
-        <v>0</v>
+        <v>56775.6</v>
       </c>
       <c r="E2482">
-        <v>71694.44</v>
+        <v>372196</v>
       </c>
       <c r="F2482">
-        <v>17.87</v>
+        <v>30.04</v>
       </c>
       <c r="G2482">
-        <v>3400</v>
+        <v>10500</v>
       </c>
       <c r="H2482">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2482" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2482" s="2">
@@ -94299,7 +94296,7 @@
     <row r="2483">
       <c r="A2483" t="inlineStr">
         <is>
-          <t>PRINCE ALLOYS (P) LTD</t>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
         </is>
       </c>
       <c r="B2483" t="inlineStr">
@@ -94308,22 +94305,19 @@
         </is>
       </c>
       <c r="C2483">
-        <v>124127</v>
+        <v>203292.5</v>
       </c>
       <c r="D2483">
-        <v>22342.86</v>
-      </c>
-      <c r="E2483">
-        <v>146470</v>
+        <v>30950.64</v>
       </c>
       <c r="F2483">
-        <v>17.86</v>
+        <v>29.43</v>
       </c>
       <c r="G2483">
-        <v>6950</v>
+        <v>6907.662249405369</v>
       </c>
       <c r="H2483">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2483" t="inlineStr">
         <is>
@@ -94337,35 +94331,35 @@
     <row r="2484">
       <c r="A2484" t="inlineStr">
         <is>
-          <t>PRINCE ROLLINGS  (P) LTD</t>
+          <t>BLUE GOLD STEEL INDUSTRIES</t>
         </is>
       </c>
       <c r="B2484" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2484">
-        <v>123710</v>
+        <v>228112.5</v>
       </c>
       <c r="D2484">
-        <v>22267.8</v>
+        <v>41060.26</v>
       </c>
       <c r="E2484">
-        <v>145978</v>
+        <v>269173</v>
       </c>
       <c r="F2484">
-        <v>17.8</v>
+        <v>26.07</v>
       </c>
       <c r="G2484">
-        <v>6950</v>
+        <v>8750</v>
       </c>
       <c r="H2484">
         <v>1</v>
       </c>
       <c r="I2484" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2484" s="2">
@@ -94375,35 +94369,35 @@
     <row r="2485">
       <c r="A2485" t="inlineStr">
         <is>
-          <t>KRISHNA STEEL ROLLING MILLS</t>
+          <t>KUBAIR STEEL AND POWER LLP</t>
         </is>
       </c>
       <c r="B2485" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2485">
-        <v>124110</v>
+        <v>92016.5</v>
       </c>
       <c r="D2485">
-        <v>33276.24</v>
+        <v>16562.98</v>
       </c>
       <c r="E2485">
-        <v>218144</v>
+        <v>108579</v>
       </c>
       <c r="F2485">
-        <v>17.73</v>
+        <v>25.21</v>
       </c>
       <c r="G2485">
-        <v>7000</v>
+        <v>3650</v>
       </c>
       <c r="H2485">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2485" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2485" s="2">
@@ -94413,35 +94407,32 @@
     <row r="2486">
       <c r="A2486" t="inlineStr">
         <is>
-          <t>ADRI STEEL PRIVATE LIMITED</t>
+          <t>KRISHNA STEEL ROLLING MILLS</t>
         </is>
       </c>
       <c r="B2486" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2486">
-        <v>105820.5</v>
+        <v>85578</v>
       </c>
       <c r="D2486">
-        <v>13210.3</v>
-      </c>
-      <c r="E2486">
-        <v>124868.4</v>
+        <v>0</v>
       </c>
       <c r="F2486">
-        <v>15.01</v>
+        <v>25.17</v>
       </c>
       <c r="G2486">
-        <v>7050</v>
+        <v>3400</v>
       </c>
       <c r="H2486">
         <v>2</v>
       </c>
       <c r="I2486" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2486" s="2">
@@ -94451,28 +94442,28 @@
     <row r="2487">
       <c r="A2487" t="inlineStr">
         <is>
-          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2487" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2487">
-        <v>46048</v>
+        <v>145000</v>
       </c>
       <c r="D2487">
-        <v>0</v>
+        <v>26100</v>
       </c>
       <c r="E2487">
-        <v>54336.64</v>
+        <v>171100</v>
       </c>
       <c r="F2487">
-        <v>14.39</v>
+        <v>20</v>
       </c>
       <c r="G2487">
-        <v>3200</v>
+        <v>7250</v>
       </c>
       <c r="H2487">
         <v>1</v>
@@ -94489,7 +94480,7 @@
     <row r="2488">
       <c r="A2488" t="inlineStr">
         <is>
-          <t>RDTMT Steels India Pvt Ltd</t>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
         </is>
       </c>
       <c r="B2488" t="inlineStr">
@@ -94498,26 +94489,26 @@
         </is>
       </c>
       <c r="C2488">
-        <v>37074</v>
+        <v>65802</v>
       </c>
       <c r="D2488">
-        <v>6673.32</v>
+        <v>17486.37</v>
       </c>
       <c r="E2488">
-        <v>43747</v>
+        <v>114633</v>
       </c>
       <c r="F2488">
-        <v>10.02</v>
+        <v>19.94</v>
       </c>
       <c r="G2488">
-        <v>3700</v>
+        <v>3300</v>
       </c>
       <c r="H2488">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2488" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2488" s="2">
@@ -94527,38 +94518,329 @@
     <row r="2489">
       <c r="A2489" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>Adishakti Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2489" t="inlineStr">
         <is>
-          <t>Tundish Ramming Mix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2489">
-        <v>252450</v>
+        <v>68310</v>
       </c>
       <c r="D2489">
-        <v>45441</v>
-      </c>
-      <c r="E2489">
-        <v>297891</v>
+        <v>0</v>
       </c>
       <c r="F2489">
-        <v>9.35</v>
+        <v>19.8</v>
       </c>
       <c r="G2489">
-        <v>27000</v>
+        <v>3450</v>
       </c>
       <c r="H2489">
         <v>1</v>
       </c>
       <c r="I2489" t="inlineStr">
         <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2489" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="inlineStr">
+        <is>
+          <t>BLUE GOLD STEEL INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="B2490" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2490">
+        <v>65895</v>
+      </c>
+      <c r="D2490">
+        <v>11861.1</v>
+      </c>
+      <c r="E2490">
+        <v>77756</v>
+      </c>
+      <c r="F2490">
+        <v>19.1</v>
+      </c>
+      <c r="G2490">
+        <v>3450</v>
+      </c>
+      <c r="H2490">
+        <v>1</v>
+      </c>
+      <c r="I2490" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2490" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>PRINCE ALLOYS (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2491" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2491">
+        <v>124127</v>
+      </c>
+      <c r="D2491">
+        <v>22342.86</v>
+      </c>
+      <c r="E2491">
+        <v>146470</v>
+      </c>
+      <c r="F2491">
+        <v>17.86</v>
+      </c>
+      <c r="G2491">
+        <v>6950</v>
+      </c>
+      <c r="H2491">
+        <v>1</v>
+      </c>
+      <c r="I2491" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2491" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="inlineStr">
+        <is>
+          <t>PRINCE ROLLINGS  (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2492" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2492">
+        <v>123710</v>
+      </c>
+      <c r="D2492">
+        <v>22267.8</v>
+      </c>
+      <c r="E2492">
+        <v>145978</v>
+      </c>
+      <c r="F2492">
+        <v>17.8</v>
+      </c>
+      <c r="G2492">
+        <v>6950</v>
+      </c>
+      <c r="H2492">
+        <v>1</v>
+      </c>
+      <c r="I2492" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2492" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2493">
+        <v>105820.5</v>
+      </c>
+      <c r="D2493">
+        <v>13210.3</v>
+      </c>
+      <c r="E2493">
+        <v>124868.4</v>
+      </c>
+      <c r="F2493">
+        <v>15.01</v>
+      </c>
+      <c r="G2493">
+        <v>7050</v>
+      </c>
+      <c r="H2493">
+        <v>2</v>
+      </c>
+      <c r="I2493" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2493" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2494" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2494">
+        <v>46048</v>
+      </c>
+      <c r="D2494">
+        <v>0</v>
+      </c>
+      <c r="E2494">
+        <v>54336.64</v>
+      </c>
+      <c r="F2494">
+        <v>14.39</v>
+      </c>
+      <c r="G2494">
+        <v>3200</v>
+      </c>
+      <c r="H2494">
+        <v>1</v>
+      </c>
+      <c r="I2494" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2494" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>Tundish Ramming Mix</t>
+        </is>
+      </c>
+      <c r="C2495">
+        <v>252450</v>
+      </c>
+      <c r="D2495">
+        <v>45441</v>
+      </c>
+      <c r="E2495">
+        <v>297891</v>
+      </c>
+      <c r="F2495">
+        <v>9.35</v>
+      </c>
+      <c r="G2495">
+        <v>27000</v>
+      </c>
+      <c r="H2495">
+        <v>1</v>
+      </c>
+      <c r="I2495" t="inlineStr">
+        <is>
           <t>Abhijit Maloo</t>
         </is>
       </c>
-      <c r="J2489" s="2">
+      <c r="J2495" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C2496">
+        <v>825000</v>
+      </c>
+      <c r="D2496">
+        <v>148500</v>
+      </c>
+      <c r="E2496">
+        <v>973500</v>
+      </c>
+      <c r="F2496">
+        <v>5</v>
+      </c>
+      <c r="G2496">
+        <v>165000</v>
+      </c>
+      <c r="H2496">
+        <v>1</v>
+      </c>
+      <c r="I2496" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2496" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C2497">
+        <v>696600</v>
+      </c>
+      <c r="D2497">
+        <v>125388</v>
+      </c>
+      <c r="E2497">
+        <v>821988</v>
+      </c>
+      <c r="F2497">
+        <v>1.8</v>
+      </c>
+      <c r="G2497">
+        <v>387000</v>
+      </c>
+      <c r="H2497">
+        <v>1</v>
+      </c>
+      <c r="I2497" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2497" s="2">
         <v>46143</v>
       </c>
     </row>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -90694,7 +90694,7 @@
       </c>
       <c r="I2387" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2387" s="2">
@@ -92356,7 +92356,7 @@
       </c>
       <c r="I2431" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2431" s="2">
@@ -92465,7 +92465,7 @@
       </c>
       <c r="I2434" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2434" s="2">
@@ -92755,6 +92755,9 @@
       <c r="D2442">
         <v>97106.04000000001</v>
       </c>
+      <c r="E2442">
+        <v>778449.3199999999</v>
+      </c>
       <c r="F2442">
         <v>194.03</v>
       </c>
@@ -92918,7 +92921,7 @@
       </c>
       <c r="I2446" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2446" s="2">
@@ -93317,19 +93320,19 @@
         </is>
       </c>
       <c r="C2457">
+        <v>1279488</v>
+      </c>
+      <c r="D2457">
         <v>11709.6</v>
       </c>
-      <c r="D2457">
-        <v>0</v>
-      </c>
       <c r="E2457">
-        <v>11709.6</v>
+        <v>1279488</v>
       </c>
       <c r="F2457">
         <v>112</v>
       </c>
       <c r="G2457">
-        <v>104.55</v>
+        <v>11424</v>
       </c>
       <c r="H2457">
         <v>1</v>
@@ -94310,6 +94313,9 @@
       <c r="D2483">
         <v>30950.64</v>
       </c>
+      <c r="E2483">
+        <v>239885.51</v>
+      </c>
       <c r="F2483">
         <v>29.43</v>
       </c>
@@ -94421,6 +94427,9 @@
       <c r="D2486">
         <v>0</v>
       </c>
+      <c r="E2486">
+        <v>100982.04</v>
+      </c>
       <c r="F2486">
         <v>25.17</v>
       </c>
@@ -94531,6 +94540,9 @@
       </c>
       <c r="D2489">
         <v>0</v>
+      </c>
+      <c r="E2489">
+        <v>80605.8</v>
       </c>
       <c r="F2489">
         <v>19.8</v>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2497"/>
+  <dimension ref="A1:J2560"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -93909,7 +93909,7 @@
       </c>
       <c r="I2472" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2472" s="2">
@@ -93947,7 +93947,7 @@
       </c>
       <c r="I2473" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2473" s="2">
@@ -94137,7 +94137,7 @@
       </c>
       <c r="I2478" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2478" s="2">
@@ -94441,7 +94441,7 @@
       </c>
       <c r="I2486" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2486" s="2">
@@ -94854,6 +94854,2388 @@
       </c>
       <c r="J2497" s="2">
         <v>46143</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" t="inlineStr">
+        <is>
+          <t>Pushpit Steels Private Limited</t>
+        </is>
+      </c>
+      <c r="B2498" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2498">
+        <v>3109044</v>
+      </c>
+      <c r="D2498">
+        <v>559627.92</v>
+      </c>
+      <c r="E2498">
+        <v>3668672</v>
+      </c>
+      <c r="F2498">
+        <v>320.52</v>
+      </c>
+      <c r="G2498">
+        <v>9700</v>
+      </c>
+      <c r="H2498">
+        <v>12</v>
+      </c>
+      <c r="I2498" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2498" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>A One Ispat Private Ltd</t>
+        </is>
+      </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2499">
+        <v>2788100</v>
+      </c>
+      <c r="D2499">
+        <v>501858.02</v>
+      </c>
+      <c r="E2499">
+        <v>3289959</v>
+      </c>
+      <c r="F2499">
+        <v>318.64</v>
+      </c>
+      <c r="G2499">
+        <v>8750</v>
+      </c>
+      <c r="H2499">
+        <v>9</v>
+      </c>
+      <c r="I2499" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2499" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" t="inlineStr">
+        <is>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2500" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2500">
+        <v>2024190</v>
+      </c>
+      <c r="D2500">
+        <v>364354.2</v>
+      </c>
+      <c r="E2500">
+        <v>2388544</v>
+      </c>
+      <c r="F2500">
+        <v>224.91</v>
+      </c>
+      <c r="G2500">
+        <v>9000</v>
+      </c>
+      <c r="H2500">
+        <v>10</v>
+      </c>
+      <c r="I2500" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2500" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+        </is>
+      </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2501">
+        <v>2087200.5</v>
+      </c>
+      <c r="D2501">
+        <v>375696.09</v>
+      </c>
+      <c r="E2501">
+        <v>2462897</v>
+      </c>
+      <c r="F2501">
+        <v>223.23</v>
+      </c>
+      <c r="G2501">
+        <v>9350</v>
+      </c>
+      <c r="H2501">
+        <v>10</v>
+      </c>
+      <c r="I2501" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2501" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" t="inlineStr">
+        <is>
+          <t>KUBAIR STEEL AND POWER LLP</t>
+        </is>
+      </c>
+      <c r="B2502" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2502">
+        <v>1957708.5</v>
+      </c>
+      <c r="D2502">
+        <v>352387.58</v>
+      </c>
+      <c r="E2502">
+        <v>2310096</v>
+      </c>
+      <c r="F2502">
+        <v>221.21</v>
+      </c>
+      <c r="G2502">
+        <v>8850</v>
+      </c>
+      <c r="H2502">
+        <v>6</v>
+      </c>
+      <c r="I2502" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2502" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>Suryadev Alloys &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2503">
+        <v>1681602</v>
+      </c>
+      <c r="D2503">
+        <v>302688.36</v>
+      </c>
+      <c r="E2503">
+        <v>1984289</v>
+      </c>
+      <c r="F2503">
+        <v>215.59</v>
+      </c>
+      <c r="G2503">
+        <v>7800</v>
+      </c>
+      <c r="H2503">
+        <v>9</v>
+      </c>
+      <c r="I2503" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2503" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2504" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2504">
+        <v>486640</v>
+      </c>
+      <c r="D2504">
+        <v>24332.02</v>
+      </c>
+      <c r="F2504">
+        <v>206.08</v>
+      </c>
+      <c r="G2504">
+        <v>2361.413043478261</v>
+      </c>
+      <c r="H2504">
+        <v>11</v>
+      </c>
+      <c r="I2504" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2504" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2505" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2505">
+        <v>1728760</v>
+      </c>
+      <c r="D2505">
+        <v>311176.8</v>
+      </c>
+      <c r="E2505">
+        <v>2039938</v>
+      </c>
+      <c r="F2505">
+        <v>196.45</v>
+      </c>
+      <c r="G2505">
+        <v>8800</v>
+      </c>
+      <c r="H2505">
+        <v>5</v>
+      </c>
+      <c r="I2505" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2505" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" t="inlineStr">
+        <is>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+        </is>
+      </c>
+      <c r="B2506" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2506">
+        <v>1776792</v>
+      </c>
+      <c r="D2506">
+        <v>319822.56</v>
+      </c>
+      <c r="E2506">
+        <v>2096616</v>
+      </c>
+      <c r="F2506">
+        <v>175.92</v>
+      </c>
+      <c r="G2506">
+        <v>10100</v>
+      </c>
+      <c r="H2506">
+        <v>7</v>
+      </c>
+      <c r="I2506" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2506" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
+        </is>
+      </c>
+      <c r="B2507" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2507">
+        <v>1509279</v>
+      </c>
+      <c r="D2507">
+        <v>271670.22</v>
+      </c>
+      <c r="E2507">
+        <v>1780949</v>
+      </c>
+      <c r="F2507">
+        <v>170.54</v>
+      </c>
+      <c r="G2507">
+        <v>8850</v>
+      </c>
+      <c r="H2507">
+        <v>8</v>
+      </c>
+      <c r="I2507" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2507" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" t="inlineStr">
+        <is>
+          <t>Meenakshi Udyog India Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="B2508" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2508">
+        <v>1634002.5</v>
+      </c>
+      <c r="D2508">
+        <v>294120.45</v>
+      </c>
+      <c r="E2508">
+        <v>1928124</v>
+      </c>
+      <c r="F2508">
+        <v>167.59</v>
+      </c>
+      <c r="G2508">
+        <v>9750</v>
+      </c>
+      <c r="H2508">
+        <v>8</v>
+      </c>
+      <c r="I2508" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2508" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+        </is>
+      </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2509">
+        <v>1484144</v>
+      </c>
+      <c r="D2509">
+        <v>267145.92</v>
+      </c>
+      <c r="E2509">
+        <v>1751289</v>
+      </c>
+      <c r="F2509">
+        <v>161.32</v>
+      </c>
+      <c r="G2509">
+        <v>9200</v>
+      </c>
+      <c r="H2509">
+        <v>8</v>
+      </c>
+      <c r="I2509" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2509" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2510" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2510">
+        <v>1443682.5</v>
+      </c>
+      <c r="D2510">
+        <v>259862.85</v>
+      </c>
+      <c r="E2510">
+        <v>1703546</v>
+      </c>
+      <c r="F2510">
+        <v>143.65</v>
+      </c>
+      <c r="G2510">
+        <v>10050</v>
+      </c>
+      <c r="H2510">
+        <v>7</v>
+      </c>
+      <c r="I2510" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2510" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2511">
+        <v>1145087</v>
+      </c>
+      <c r="D2511">
+        <v>206115.68</v>
+      </c>
+      <c r="E2511">
+        <v>1351202</v>
+      </c>
+      <c r="F2511">
+        <v>132.38</v>
+      </c>
+      <c r="G2511">
+        <v>8650</v>
+      </c>
+      <c r="H2511">
+        <v>4</v>
+      </c>
+      <c r="I2511" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2511" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" t="inlineStr">
+        <is>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+        </is>
+      </c>
+      <c r="B2512" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2512">
+        <v>1124667</v>
+      </c>
+      <c r="D2512">
+        <v>202440.06</v>
+      </c>
+      <c r="E2512">
+        <v>1327108</v>
+      </c>
+      <c r="F2512">
+        <v>131.54</v>
+      </c>
+      <c r="G2512">
+        <v>8550</v>
+      </c>
+      <c r="H2512">
+        <v>6</v>
+      </c>
+      <c r="I2512" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2512" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2513">
+        <v>392938</v>
+      </c>
+      <c r="D2513">
+        <v>70728.84</v>
+      </c>
+      <c r="E2513">
+        <v>463666</v>
+      </c>
+      <c r="F2513">
+        <v>115.57</v>
+      </c>
+      <c r="G2513">
+        <v>3400</v>
+      </c>
+      <c r="H2513">
+        <v>3</v>
+      </c>
+      <c r="I2513" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2513" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" t="inlineStr">
+        <is>
+          <t>Adishakti Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2514" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2514">
+        <v>988487.5</v>
+      </c>
+      <c r="D2514">
+        <v>205425.68</v>
+      </c>
+      <c r="E2514">
+        <v>1346679</v>
+      </c>
+      <c r="F2514">
+        <v>112.97</v>
+      </c>
+      <c r="G2514">
+        <v>8750</v>
+      </c>
+      <c r="H2514">
+        <v>4</v>
+      </c>
+      <c r="I2514" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2514" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2515">
+        <v>960654</v>
+      </c>
+      <c r="D2515">
+        <v>186830.64</v>
+      </c>
+      <c r="E2515">
+        <v>1224779</v>
+      </c>
+      <c r="F2515">
+        <v>110.42</v>
+      </c>
+      <c r="G2515">
+        <v>8700</v>
+      </c>
+      <c r="H2515">
+        <v>4</v>
+      </c>
+      <c r="I2515" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2515" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" t="inlineStr">
+        <is>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2516" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2516">
+        <v>735866</v>
+      </c>
+      <c r="D2516">
+        <v>132455.88</v>
+      </c>
+      <c r="E2516">
+        <v>868322</v>
+      </c>
+      <c r="F2516">
+        <v>105.88</v>
+      </c>
+      <c r="G2516">
+        <v>6949.999999999999</v>
+      </c>
+      <c r="H2516">
+        <v>3</v>
+      </c>
+      <c r="I2516" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2516" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>Arun Vyapar Udyog Private Limited</t>
+        </is>
+      </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2517">
+        <v>934856</v>
+      </c>
+      <c r="D2517">
+        <v>168274.08</v>
+      </c>
+      <c r="E2517">
+        <v>1103130</v>
+      </c>
+      <c r="F2517">
+        <v>92.56</v>
+      </c>
+      <c r="G2517">
+        <v>10100</v>
+      </c>
+      <c r="H2517">
+        <v>3</v>
+      </c>
+      <c r="I2517" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2517" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+        </is>
+      </c>
+      <c r="B2518" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2518">
+        <v>787160</v>
+      </c>
+      <c r="D2518">
+        <v>141688.8</v>
+      </c>
+      <c r="E2518">
+        <v>928849</v>
+      </c>
+      <c r="F2518">
+        <v>89.44999999999999</v>
+      </c>
+      <c r="G2518">
+        <v>8800.000000000002</v>
+      </c>
+      <c r="H2518">
+        <v>2</v>
+      </c>
+      <c r="I2518" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2518" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>Prakash Ferrous Industries Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2519">
+        <v>674444</v>
+      </c>
+      <c r="D2519">
+        <v>121399.92</v>
+      </c>
+      <c r="E2519">
+        <v>795844</v>
+      </c>
+      <c r="F2519">
+        <v>65.48</v>
+      </c>
+      <c r="G2519">
+        <v>10300</v>
+      </c>
+      <c r="H2519">
+        <v>2</v>
+      </c>
+      <c r="I2519" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2519" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" t="inlineStr">
+        <is>
+          <t>KANNAPPAN IRON AND STEEL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2520">
+        <v>696891</v>
+      </c>
+      <c r="D2520">
+        <v>125440.38</v>
+      </c>
+      <c r="E2520">
+        <v>822331</v>
+      </c>
+      <c r="F2520">
+        <v>65.13</v>
+      </c>
+      <c r="G2520">
+        <v>10700</v>
+      </c>
+      <c r="H2520">
+        <v>3</v>
+      </c>
+      <c r="I2520" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2520" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>Mahrishi Alloys Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2521">
+        <v>276292.5</v>
+      </c>
+      <c r="D2521">
+        <v>49732.66</v>
+      </c>
+      <c r="E2521">
+        <v>326025</v>
+      </c>
+      <c r="F2521">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="G2521">
+        <v>4250</v>
+      </c>
+      <c r="H2521">
+        <v>2</v>
+      </c>
+      <c r="I2521" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2521" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" t="inlineStr">
+        <is>
+          <t>TEXCON STEELS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2522">
+        <v>555750</v>
+      </c>
+      <c r="D2522">
+        <v>100035</v>
+      </c>
+      <c r="E2522">
+        <v>655785</v>
+      </c>
+      <c r="F2522">
+        <v>65</v>
+      </c>
+      <c r="G2522">
+        <v>8550</v>
+      </c>
+      <c r="H2522">
+        <v>2</v>
+      </c>
+      <c r="I2522" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2522" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Limited</t>
+        </is>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2523">
+        <v>298770</v>
+      </c>
+      <c r="D2523">
+        <v>14938.5</v>
+      </c>
+      <c r="E2523">
+        <v>313709</v>
+      </c>
+      <c r="F2523">
+        <v>64.95</v>
+      </c>
+      <c r="G2523">
+        <v>4600</v>
+      </c>
+      <c r="H2523">
+        <v>3</v>
+      </c>
+      <c r="I2523" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2523" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" t="inlineStr">
+        <is>
+          <t>KAIRAV STEELS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2524">
+        <v>412137</v>
+      </c>
+      <c r="D2524">
+        <v>87612.66</v>
+      </c>
+      <c r="E2524">
+        <v>574350</v>
+      </c>
+      <c r="F2524">
+        <v>59.73</v>
+      </c>
+      <c r="G2524">
+        <v>6899.999999999999</v>
+      </c>
+      <c r="H2524">
+        <v>2</v>
+      </c>
+      <c r="I2524" t="inlineStr">
+        <is>
+          <t>Sunil Rathi</t>
+        </is>
+      </c>
+      <c r="J2524" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>S.R. STEEL PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>Ordinary Ramming Mass</t>
+        </is>
+      </c>
+      <c r="C2525">
+        <v>636412</v>
+      </c>
+      <c r="D2525">
+        <v>0</v>
+      </c>
+      <c r="E2525">
+        <v>636412</v>
+      </c>
+      <c r="F2525">
+        <v>56</v>
+      </c>
+      <c r="G2525">
+        <v>11364.5</v>
+      </c>
+      <c r="H2525">
+        <v>1</v>
+      </c>
+      <c r="I2525" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2525" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" t="inlineStr">
+        <is>
+          <t>Shri Tirupati Steel Cast Ltd</t>
+        </is>
+      </c>
+      <c r="B2526" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2526">
+        <v>191268</v>
+      </c>
+      <c r="D2526">
+        <v>34428.26</v>
+      </c>
+      <c r="E2526">
+        <v>225696</v>
+      </c>
+      <c r="F2526">
+        <v>55.44</v>
+      </c>
+      <c r="G2526">
+        <v>3450</v>
+      </c>
+      <c r="H2526">
+        <v>3</v>
+      </c>
+      <c r="I2526" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2526" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2527">
+        <v>437871</v>
+      </c>
+      <c r="D2527">
+        <v>78816.78</v>
+      </c>
+      <c r="E2527">
+        <v>516688</v>
+      </c>
+      <c r="F2527">
+        <v>50.33</v>
+      </c>
+      <c r="G2527">
+        <v>8700</v>
+      </c>
+      <c r="H2527">
+        <v>2</v>
+      </c>
+      <c r="I2527" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2527" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="inlineStr">
+        <is>
+          <t>Kanishk Steel Industries Ltd</t>
+        </is>
+      </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2528">
+        <v>466075</v>
+      </c>
+      <c r="D2528">
+        <v>83893.5</v>
+      </c>
+      <c r="E2528">
+        <v>549969</v>
+      </c>
+      <c r="F2528">
+        <v>45.25</v>
+      </c>
+      <c r="G2528">
+        <v>10300</v>
+      </c>
+      <c r="H2528">
+        <v>2</v>
+      </c>
+      <c r="I2528" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2528" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>GBR Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2529">
+        <v>460925</v>
+      </c>
+      <c r="D2529">
+        <v>82966.5</v>
+      </c>
+      <c r="E2529">
+        <v>543892</v>
+      </c>
+      <c r="F2529">
+        <v>44.75</v>
+      </c>
+      <c r="G2529">
+        <v>10300</v>
+      </c>
+      <c r="H2529">
+        <v>2</v>
+      </c>
+      <c r="I2529" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2529" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" t="inlineStr">
+        <is>
+          <t>Adishakti Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2530">
+        <v>152766</v>
+      </c>
+      <c r="D2530">
+        <v>0</v>
+      </c>
+      <c r="F2530">
+        <v>44.28</v>
+      </c>
+      <c r="G2530">
+        <v>3450</v>
+      </c>
+      <c r="H2530">
+        <v>2</v>
+      </c>
+      <c r="I2530" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2530" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>VRKP ISPAT PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2531">
+        <v>165702.5</v>
+      </c>
+      <c r="D2531">
+        <v>29826.45</v>
+      </c>
+      <c r="E2531">
+        <v>195529</v>
+      </c>
+      <c r="F2531">
+        <v>41.95</v>
+      </c>
+      <c r="G2531">
+        <v>3950</v>
+      </c>
+      <c r="H2531">
+        <v>2</v>
+      </c>
+      <c r="I2531" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2531" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="inlineStr">
+        <is>
+          <t>Keshree Metalurgies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2532">
+        <v>391296</v>
+      </c>
+      <c r="D2532">
+        <v>70433.28</v>
+      </c>
+      <c r="E2532">
+        <v>461729</v>
+      </c>
+      <c r="F2532">
+        <v>40.76000000000001</v>
+      </c>
+      <c r="G2532">
+        <v>9599.999999999998</v>
+      </c>
+      <c r="H2532">
+        <v>2</v>
+      </c>
+      <c r="I2532" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2532" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>Sree  Rengaraaj Steel &amp; Alloys (P) Limited</t>
+        </is>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2533">
+        <v>409555</v>
+      </c>
+      <c r="D2533">
+        <v>73719.89999999999</v>
+      </c>
+      <c r="E2533">
+        <v>483275</v>
+      </c>
+      <c r="F2533">
+        <v>40.55</v>
+      </c>
+      <c r="G2533">
+        <v>10100</v>
+      </c>
+      <c r="H2533">
+        <v>2</v>
+      </c>
+      <c r="I2533" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2533" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" t="inlineStr">
+        <is>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+        </is>
+      </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2534">
+        <v>347903</v>
+      </c>
+      <c r="D2534">
+        <v>62622.54</v>
+      </c>
+      <c r="E2534">
+        <v>410526</v>
+      </c>
+      <c r="F2534">
+        <v>40.22</v>
+      </c>
+      <c r="G2534">
+        <v>8650</v>
+      </c>
+      <c r="H2534">
+        <v>1</v>
+      </c>
+      <c r="I2534" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2534" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>Sri M.S.T. Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2535">
+        <v>346000</v>
+      </c>
+      <c r="D2535">
+        <v>62280</v>
+      </c>
+      <c r="E2535">
+        <v>408280</v>
+      </c>
+      <c r="F2535">
+        <v>40</v>
+      </c>
+      <c r="G2535">
+        <v>8650</v>
+      </c>
+      <c r="H2535">
+        <v>2</v>
+      </c>
+      <c r="I2535" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2535" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="inlineStr">
+        <is>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+        </is>
+      </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2536">
+        <v>147482</v>
+      </c>
+      <c r="D2536">
+        <v>26546.76</v>
+      </c>
+      <c r="E2536">
+        <v>174029</v>
+      </c>
+      <c r="F2536">
+        <v>39.86</v>
+      </c>
+      <c r="G2536">
+        <v>3700</v>
+      </c>
+      <c r="H2536">
+        <v>2</v>
+      </c>
+      <c r="I2536" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2536" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>BMM ISPAT LIMITED</t>
+        </is>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2537">
+        <v>300263.5</v>
+      </c>
+      <c r="D2537">
+        <v>54047.43</v>
+      </c>
+      <c r="E2537">
+        <v>354311</v>
+      </c>
+      <c r="F2537">
+        <v>39.77</v>
+      </c>
+      <c r="G2537">
+        <v>7549.999999999999</v>
+      </c>
+      <c r="H2537">
+        <v>1</v>
+      </c>
+      <c r="I2537" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2537" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="inlineStr">
+        <is>
+          <t>VMC Steel and Alloys Industry</t>
+        </is>
+      </c>
+      <c r="B2538" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2538">
+        <v>417585</v>
+      </c>
+      <c r="D2538">
+        <v>75165.3</v>
+      </c>
+      <c r="E2538">
+        <v>492751</v>
+      </c>
+      <c r="F2538">
+        <v>39.77</v>
+      </c>
+      <c r="G2538">
+        <v>10500</v>
+      </c>
+      <c r="H2538">
+        <v>2</v>
+      </c>
+      <c r="I2538" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2538" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+        </is>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2539">
+        <v>347451</v>
+      </c>
+      <c r="D2539">
+        <v>62541.18</v>
+      </c>
+      <c r="E2539">
+        <v>409992</v>
+      </c>
+      <c r="F2539">
+        <v>39.26</v>
+      </c>
+      <c r="G2539">
+        <v>8850</v>
+      </c>
+      <c r="H2539">
+        <v>1</v>
+      </c>
+      <c r="I2539" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2539" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="inlineStr">
+        <is>
+          <t>SREE PALANIANDAVAR ALLOYS AND STEELS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2540">
+        <v>246725</v>
+      </c>
+      <c r="D2540">
+        <v>44410.5</v>
+      </c>
+      <c r="E2540">
+        <v>291136</v>
+      </c>
+      <c r="F2540">
+        <v>35.5</v>
+      </c>
+      <c r="G2540">
+        <v>6950</v>
+      </c>
+      <c r="H2540">
+        <v>1</v>
+      </c>
+      <c r="I2540" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2540" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>M.A.STEELS (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2541">
+        <v>245682.5</v>
+      </c>
+      <c r="D2541">
+        <v>44222.85</v>
+      </c>
+      <c r="E2541">
+        <v>289905</v>
+      </c>
+      <c r="F2541">
+        <v>35.35</v>
+      </c>
+      <c r="G2541">
+        <v>6950</v>
+      </c>
+      <c r="H2541">
+        <v>1</v>
+      </c>
+      <c r="I2541" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2541" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="inlineStr">
+        <is>
+          <t>PARAGON STEEL DISTRIBUITORS</t>
+        </is>
+      </c>
+      <c r="B2542" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2542">
+        <v>238612</v>
+      </c>
+      <c r="D2542">
+        <v>42950.16</v>
+      </c>
+      <c r="E2542">
+        <v>281562</v>
+      </c>
+      <c r="F2542">
+        <v>35.09</v>
+      </c>
+      <c r="G2542">
+        <v>6799.999999999999</v>
+      </c>
+      <c r="H2542">
+        <v>1</v>
+      </c>
+      <c r="I2542" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2542" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>Pattambi Brothers</t>
+        </is>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2543">
+        <v>243667</v>
+      </c>
+      <c r="D2543">
+        <v>43860.06</v>
+      </c>
+      <c r="E2543">
+        <v>287527</v>
+      </c>
+      <c r="F2543">
+        <v>35.06</v>
+      </c>
+      <c r="G2543">
+        <v>6950</v>
+      </c>
+      <c r="H2543">
+        <v>1</v>
+      </c>
+      <c r="I2543" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2543" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="inlineStr">
+        <is>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+        </is>
+      </c>
+      <c r="B2544" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2544">
+        <v>142229</v>
+      </c>
+      <c r="D2544">
+        <v>25601.22</v>
+      </c>
+      <c r="E2544">
+        <v>167830</v>
+      </c>
+      <c r="F2544">
+        <v>34.69</v>
+      </c>
+      <c r="G2544">
+        <v>4100</v>
+      </c>
+      <c r="H2544">
+        <v>2</v>
+      </c>
+      <c r="I2544" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2544" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+        </is>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2545">
+        <v>260173</v>
+      </c>
+      <c r="D2545">
+        <v>46831.14</v>
+      </c>
+      <c r="E2545">
+        <v>307004</v>
+      </c>
+      <c r="F2545">
+        <v>34.46</v>
+      </c>
+      <c r="G2545">
+        <v>7550</v>
+      </c>
+      <c r="H2545">
+        <v>1</v>
+      </c>
+      <c r="I2545" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2545" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="inlineStr">
+        <is>
+          <t>RELIANCE CONCAST SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="B2546" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2546">
+        <v>108452.5</v>
+      </c>
+      <c r="D2546">
+        <v>5422.63</v>
+      </c>
+      <c r="E2546">
+        <v>113875</v>
+      </c>
+      <c r="F2546">
+        <v>33.37</v>
+      </c>
+      <c r="G2546">
+        <v>3250</v>
+      </c>
+      <c r="H2546">
+        <v>2</v>
+      </c>
+      <c r="I2546" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2546" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2547">
+        <v>176599.5</v>
+      </c>
+      <c r="D2547">
+        <v>31787.91</v>
+      </c>
+      <c r="E2547">
+        <v>208388</v>
+      </c>
+      <c r="F2547">
+        <v>25.41</v>
+      </c>
+      <c r="G2547">
+        <v>6950</v>
+      </c>
+      <c r="H2547">
+        <v>1</v>
+      </c>
+      <c r="I2547" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2547" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="inlineStr">
+        <is>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+        </is>
+      </c>
+      <c r="B2548" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2548">
+        <v>92199</v>
+      </c>
+      <c r="D2548">
+        <v>16595.82</v>
+      </c>
+      <c r="E2548">
+        <v>108795</v>
+      </c>
+      <c r="F2548">
+        <v>25.26</v>
+      </c>
+      <c r="G2548">
+        <v>3650</v>
+      </c>
+      <c r="H2548">
+        <v>1</v>
+      </c>
+      <c r="I2548" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2548" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2549">
+        <v>220937.5</v>
+      </c>
+      <c r="D2549">
+        <v>39768.76</v>
+      </c>
+      <c r="E2549">
+        <v>260706</v>
+      </c>
+      <c r="F2549">
+        <v>25.25</v>
+      </c>
+      <c r="G2549">
+        <v>8750</v>
+      </c>
+      <c r="H2549">
+        <v>1</v>
+      </c>
+      <c r="I2549" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2549" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="inlineStr">
+        <is>
+          <t>BLUE GOLD STEEL INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2550">
+        <v>220150</v>
+      </c>
+      <c r="D2550">
+        <v>39627</v>
+      </c>
+      <c r="E2550">
+        <v>259777</v>
+      </c>
+      <c r="F2550">
+        <v>25.16</v>
+      </c>
+      <c r="G2550">
+        <v>8750</v>
+      </c>
+      <c r="H2550">
+        <v>1</v>
+      </c>
+      <c r="I2550" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2550" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2551">
+        <v>184970.5</v>
+      </c>
+      <c r="D2551">
+        <v>0</v>
+      </c>
+      <c r="F2551">
+        <v>21.89</v>
+      </c>
+      <c r="G2551">
+        <v>8450</v>
+      </c>
+      <c r="H2551">
+        <v>1</v>
+      </c>
+      <c r="I2551" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2551" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2552" t="inlineStr">
+        <is>
+          <t>Tundish Ramming Mix</t>
+        </is>
+      </c>
+      <c r="C2552">
+        <v>575100</v>
+      </c>
+      <c r="D2552">
+        <v>103518</v>
+      </c>
+      <c r="E2552">
+        <v>678618</v>
+      </c>
+      <c r="F2552">
+        <v>21.3</v>
+      </c>
+      <c r="G2552">
+        <v>27000</v>
+      </c>
+      <c r="H2552">
+        <v>3</v>
+      </c>
+      <c r="I2552" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2552" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="inlineStr">
+        <is>
+          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2553">
+        <v>142695</v>
+      </c>
+      <c r="D2553">
+        <v>25685.09999999999</v>
+      </c>
+      <c r="E2553">
+        <v>168380.1</v>
+      </c>
+      <c r="F2553">
+        <v>21.14</v>
+      </c>
+      <c r="G2553">
+        <v>6750.000000000001</v>
+      </c>
+      <c r="H2553">
+        <v>2</v>
+      </c>
+      <c r="I2553" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2553" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2554" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2554">
+        <v>64896</v>
+      </c>
+      <c r="D2554">
+        <v>11681.28</v>
+      </c>
+      <c r="E2554">
+        <v>76577</v>
+      </c>
+      <c r="F2554">
+        <v>20.28</v>
+      </c>
+      <c r="G2554">
+        <v>3200</v>
+      </c>
+      <c r="H2554">
+        <v>2</v>
+      </c>
+      <c r="I2554" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2554" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2555">
+        <v>166380.5</v>
+      </c>
+      <c r="D2555">
+        <v>29948.49</v>
+      </c>
+      <c r="E2555">
+        <v>196329</v>
+      </c>
+      <c r="F2555">
+        <v>19.69</v>
+      </c>
+      <c r="G2555">
+        <v>8450</v>
+      </c>
+      <c r="H2555">
+        <v>1</v>
+      </c>
+      <c r="I2555" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2555" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" t="inlineStr">
+        <is>
+          <t>KAIRAV STEELS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2556">
+        <v>53584</v>
+      </c>
+      <c r="D2556">
+        <v>8399.52</v>
+      </c>
+      <c r="F2556">
+        <v>15.76</v>
+      </c>
+      <c r="G2556">
+        <v>3400</v>
+      </c>
+      <c r="H2556">
+        <v>3</v>
+      </c>
+      <c r="I2556" t="inlineStr">
+        <is>
+          <t>Sunil Rathi</t>
+        </is>
+      </c>
+      <c r="J2556" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="inlineStr">
+        <is>
+          <t>SRI LAXMI GANESH MINERALS UNIT - II</t>
+        </is>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2557">
+        <v>2139500</v>
+      </c>
+      <c r="D2557">
+        <v>385110</v>
+      </c>
+      <c r="E2557">
+        <v>2524610</v>
+      </c>
+      <c r="F2557">
+        <v>5.5</v>
+      </c>
+      <c r="G2557">
+        <v>389000</v>
+      </c>
+      <c r="H2557">
+        <v>1</v>
+      </c>
+      <c r="I2557" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2557" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" t="inlineStr">
+        <is>
+          <t>SRI BHAVANI CASTINGS LTD</t>
+        </is>
+      </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2558">
+        <v>36800</v>
+      </c>
+      <c r="D2558">
+        <v>6624</v>
+      </c>
+      <c r="E2558">
+        <v>43424</v>
+      </c>
+      <c r="F2558">
+        <v>4</v>
+      </c>
+      <c r="G2558">
+        <v>9200</v>
+      </c>
+      <c r="H2558">
+        <v>1</v>
+      </c>
+      <c r="I2558" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2558" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="inlineStr">
+        <is>
+          <t>SARCH ALLOY CASTINGS</t>
+        </is>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>Scrap</t>
+        </is>
+      </c>
+      <c r="C2559">
+        <v>325900</v>
+      </c>
+      <c r="D2559">
+        <v>58662</v>
+      </c>
+      <c r="E2559">
+        <v>385774</v>
+      </c>
+      <c r="F2559">
+        <v>3.02</v>
+      </c>
+      <c r="G2559">
+        <v>107913.9072847682</v>
+      </c>
+      <c r="H2559">
+        <v>2</v>
+      </c>
+      <c r="I2559" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2559" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2560" t="inlineStr">
+        <is>
+          <t>Ordinary Ramming Mass</t>
+        </is>
+      </c>
+      <c r="C2560">
+        <v>14850</v>
+      </c>
+      <c r="D2560">
+        <v>35967.7</v>
+      </c>
+      <c r="E2560">
+        <v>235788</v>
+      </c>
+      <c r="F2560">
+        <v>3</v>
+      </c>
+      <c r="G2560">
+        <v>4950</v>
+      </c>
+      <c r="H2560">
+        <v>1</v>
+      </c>
+      <c r="I2560" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2560" s="2">
+        <v>46174</v>
       </c>
     </row>
   </sheetData>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2560"/>
+  <dimension ref="A1:J2611"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -92484,22 +92484,22 @@
         </is>
       </c>
       <c r="C2435">
-        <v>4119008</v>
+        <v>1911094</v>
       </c>
       <c r="D2435">
-        <v>741421.4399999999</v>
+        <v>343996.92</v>
       </c>
       <c r="E2435">
-        <v>4860431</v>
+        <v>2255092</v>
       </c>
       <c r="F2435">
-        <v>424.64</v>
+        <v>197.02</v>
       </c>
       <c r="G2435">
         <v>9700</v>
       </c>
       <c r="H2435">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I2435" t="inlineStr">
         <is>
@@ -92513,7 +92513,7 @@
     <row r="2436">
       <c r="A2436" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+          <t>A One Ispat Private Ltd</t>
         </is>
       </c>
       <c r="B2436" t="inlineStr">
@@ -92522,22 +92522,22 @@
         </is>
       </c>
       <c r="C2436">
-        <v>2723374.5</v>
+        <v>1325537.5</v>
       </c>
       <c r="D2436">
-        <v>490207.41</v>
+        <v>238596.8</v>
       </c>
       <c r="E2436">
-        <v>3213582</v>
+        <v>1564133</v>
       </c>
       <c r="F2436">
-        <v>291.27</v>
+        <v>151.49</v>
       </c>
       <c r="G2436">
-        <v>9350</v>
+        <v>8750</v>
       </c>
       <c r="H2436">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I2436" t="inlineStr">
         <is>
@@ -92551,7 +92551,7 @@
     <row r="2437">
       <c r="A2437" t="inlineStr">
         <is>
-          <t>A One Ispat Private Ltd</t>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
         </is>
       </c>
       <c r="B2437" t="inlineStr">
@@ -92560,26 +92560,26 @@
         </is>
       </c>
       <c r="C2437">
-        <v>2201150</v>
+        <v>1272398</v>
       </c>
       <c r="D2437">
-        <v>396207.06</v>
+        <v>229031.64</v>
       </c>
       <c r="E2437">
-        <v>2597357</v>
+        <v>1501429</v>
       </c>
       <c r="F2437">
-        <v>251.56</v>
+        <v>125.98</v>
       </c>
       <c r="G2437">
-        <v>8750</v>
+        <v>10100</v>
       </c>
       <c r="H2437">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I2437" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2437" s="2">
@@ -92589,7 +92589,7 @@
     <row r="2438">
       <c r="A2438" t="inlineStr">
         <is>
-          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
         </is>
       </c>
       <c r="B2438" t="inlineStr">
@@ -92598,26 +92598,26 @@
         </is>
       </c>
       <c r="C2438">
-        <v>2182711</v>
+        <v>1092344</v>
       </c>
       <c r="D2438">
-        <v>392887.98</v>
+        <v>202686.84</v>
       </c>
       <c r="E2438">
-        <v>2575598</v>
+        <v>1328724</v>
       </c>
       <c r="F2438">
-        <v>216.11</v>
+        <v>124.13</v>
       </c>
       <c r="G2438">
-        <v>10100</v>
+        <v>8800</v>
       </c>
       <c r="H2438">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I2438" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2438" s="2">
@@ -92627,7 +92627,7 @@
     <row r="2439">
       <c r="A2439" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
         </is>
       </c>
       <c r="B2439" t="inlineStr">
@@ -92636,22 +92636,22 @@
         </is>
       </c>
       <c r="C2439">
-        <v>1846504</v>
+        <v>1106479</v>
       </c>
       <c r="D2439">
-        <v>354011.04</v>
+        <v>199166.22</v>
       </c>
       <c r="E2439">
-        <v>2320738</v>
+        <v>1305646</v>
       </c>
       <c r="F2439">
-        <v>209.83</v>
+        <v>118.34</v>
       </c>
       <c r="G2439">
-        <v>8800</v>
+        <v>9350</v>
       </c>
       <c r="H2439">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2439" t="inlineStr">
         <is>
@@ -92665,7 +92665,7 @@
     <row r="2440">
       <c r="A2440" t="inlineStr">
         <is>
-          <t>Adishakti Smelters Private Limited</t>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2440" t="inlineStr">
@@ -92674,22 +92674,22 @@
         </is>
       </c>
       <c r="C2440">
-        <v>1822100</v>
+        <v>1056960</v>
       </c>
       <c r="D2440">
-        <v>340273.86</v>
+        <v>190252.8</v>
       </c>
       <c r="E2440">
-        <v>2230685</v>
+        <v>1247212</v>
       </c>
       <c r="F2440">
-        <v>208.24</v>
+        <v>117.44</v>
       </c>
       <c r="G2440">
-        <v>8750</v>
+        <v>9000</v>
       </c>
       <c r="H2440">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I2440" t="inlineStr">
         <is>
@@ -92703,7 +92703,7 @@
     <row r="2441">
       <c r="A2441" t="inlineStr">
         <is>
-          <t>Minera Steel &amp; Power Pvt Ltd</t>
+          <t>Meenakshi Udyog India Pvt Ltd.</t>
         </is>
       </c>
       <c r="B2441" t="inlineStr">
@@ -92712,26 +92712,26 @@
         </is>
       </c>
       <c r="C2441">
-        <v>1787400</v>
+        <v>1123687.5</v>
       </c>
       <c r="D2441">
-        <v>321732</v>
+        <v>202263.75</v>
       </c>
       <c r="E2441">
-        <v>2109131</v>
+        <v>1325952</v>
       </c>
       <c r="F2441">
-        <v>198.6</v>
+        <v>115.25</v>
       </c>
       <c r="G2441">
-        <v>9000</v>
+        <v>9750</v>
       </c>
       <c r="H2441">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I2441" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2441" s="2">
@@ -92741,31 +92741,31 @@
     <row r="2442">
       <c r="A2442" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+          <t>KUBAIR STEEL AND POWER LLP</t>
         </is>
       </c>
       <c r="B2442" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2442">
-        <v>659702</v>
+        <v>989285</v>
       </c>
       <c r="D2442">
-        <v>97106.04000000001</v>
+        <v>178071.3</v>
       </c>
       <c r="E2442">
-        <v>778449.3199999999</v>
+        <v>1167358</v>
       </c>
       <c r="F2442">
-        <v>194.03</v>
+        <v>112.03</v>
       </c>
       <c r="G2442">
-        <v>3400</v>
+        <v>8830.536463447292</v>
       </c>
       <c r="H2442">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I2442" t="inlineStr">
         <is>
@@ -92779,31 +92779,31 @@
     <row r="2443">
       <c r="A2443" t="inlineStr">
         <is>
-          <t>TEXCON STEELS LIMITED</t>
+          <t>S.R. STEEL PVT LTD</t>
         </is>
       </c>
       <c r="B2443" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Ordinary Ramming Mass</t>
         </is>
       </c>
       <c r="C2443">
-        <v>1521301.5</v>
+        <v>13328</v>
       </c>
       <c r="D2443">
-        <v>273834.27</v>
+        <v>0</v>
       </c>
       <c r="E2443">
-        <v>1795135</v>
+        <v>13328</v>
       </c>
       <c r="F2443">
-        <v>177.93</v>
+        <v>112</v>
       </c>
       <c r="G2443">
-        <v>8550</v>
+        <v>119</v>
       </c>
       <c r="H2443">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2443" t="inlineStr">
         <is>
@@ -92817,7 +92817,7 @@
     <row r="2444">
       <c r="A2444" t="inlineStr">
         <is>
-          <t>Prakash Ferrous Industries Pvt Ltd</t>
+          <t>Adishakti Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2444" t="inlineStr">
@@ -92826,26 +92826,26 @@
         </is>
       </c>
       <c r="C2444">
-        <v>1825984</v>
+        <v>971950</v>
       </c>
       <c r="D2444">
-        <v>328677.12</v>
+        <v>174951.04</v>
       </c>
       <c r="E2444">
-        <v>2154661</v>
+        <v>1146902</v>
       </c>
       <c r="F2444">
-        <v>177.28</v>
+        <v>111.08</v>
       </c>
       <c r="G2444">
-        <v>10300</v>
+        <v>8749.999999999998</v>
       </c>
       <c r="H2444">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2444" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2444" s="2">
@@ -92855,31 +92855,31 @@
     <row r="2445">
       <c r="A2445" t="inlineStr">
         <is>
-          <t>Arun Vyapar Udyog Private Limited</t>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
         </is>
       </c>
       <c r="B2445" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2445">
-        <v>1784973</v>
+        <v>329154</v>
       </c>
       <c r="D2445">
-        <v>321295.14</v>
+        <v>53182.8</v>
       </c>
       <c r="E2445">
-        <v>2106269</v>
+        <v>388401.92</v>
       </c>
       <c r="F2445">
-        <v>176.73</v>
+        <v>96.81</v>
       </c>
       <c r="G2445">
-        <v>10100</v>
+        <v>3400</v>
       </c>
       <c r="H2445">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I2445" t="inlineStr">
         <is>
@@ -92893,31 +92893,31 @@
     <row r="2446">
       <c r="A2446" t="inlineStr">
         <is>
-          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
         </is>
       </c>
       <c r="B2446" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Quartz Powder</t>
         </is>
       </c>
       <c r="C2446">
-        <v>1417150.5</v>
+        <v>165644.5</v>
       </c>
       <c r="D2446">
-        <v>255087.09</v>
+        <v>8282.225</v>
       </c>
       <c r="E2446">
-        <v>1672237</v>
+        <v>173926.725</v>
       </c>
       <c r="F2446">
-        <v>160.13</v>
+        <v>85.75</v>
       </c>
       <c r="G2446">
-        <v>8850</v>
+        <v>1931.714285714286</v>
       </c>
       <c r="H2446">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I2446" t="inlineStr">
         <is>
@@ -92931,7 +92931,7 @@
     <row r="2447">
       <c r="A2447" t="inlineStr">
         <is>
-          <t>RDTMT Steels India Pvt Ltd</t>
+          <t>Arun Vyapar Udyog Private Limited</t>
         </is>
       </c>
       <c r="B2447" t="inlineStr">
@@ -92940,22 +92940,22 @@
         </is>
       </c>
       <c r="C2447">
-        <v>1355801</v>
+        <v>860722</v>
       </c>
       <c r="D2447">
-        <v>244044.2</v>
+        <v>154929.96</v>
       </c>
       <c r="E2447">
-        <v>1599845</v>
+        <v>1015652</v>
       </c>
       <c r="F2447">
-        <v>156.74</v>
+        <v>85.22</v>
       </c>
       <c r="G2447">
-        <v>8650</v>
+        <v>10100</v>
       </c>
       <c r="H2447">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2447" t="inlineStr">
         <is>
@@ -92969,7 +92969,7 @@
     <row r="2448">
       <c r="A2448" t="inlineStr">
         <is>
-          <t>Meenakshi Udyog India Pvt Ltd.</t>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
         </is>
       </c>
       <c r="B2448" t="inlineStr">
@@ -92978,26 +92978,26 @@
         </is>
       </c>
       <c r="C2448">
-        <v>1517490</v>
+        <v>714609</v>
       </c>
       <c r="D2448">
-        <v>273148.2</v>
+        <v>128629.62</v>
       </c>
       <c r="E2448">
-        <v>1790639</v>
+        <v>843239</v>
       </c>
       <c r="F2448">
-        <v>155.64</v>
+        <v>83.58</v>
       </c>
       <c r="G2448">
-        <v>9750</v>
+        <v>8550</v>
       </c>
       <c r="H2448">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I2448" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2448" s="2">
@@ -93007,31 +93007,31 @@
     <row r="2449">
       <c r="A2449" t="inlineStr">
         <is>
-          <t>Mahrishi Alloys Pvt. Ltd.</t>
+          <t>BMM ISPAT LIMITED</t>
         </is>
       </c>
       <c r="B2449" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2449">
-        <v>629689</v>
+        <v>616231</v>
       </c>
       <c r="D2449">
-        <v>113344.04</v>
+        <v>110921.58</v>
       </c>
       <c r="E2449">
-        <v>743033</v>
+        <v>727153</v>
       </c>
       <c r="F2449">
-        <v>151.58</v>
+        <v>81.62</v>
       </c>
       <c r="G2449">
-        <v>4154.16941549017</v>
+        <v>7550</v>
       </c>
       <c r="H2449">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2449" t="inlineStr">
         <is>
@@ -93054,22 +93054,22 @@
         </is>
       </c>
       <c r="C2450">
-        <v>1289103</v>
+        <v>676536</v>
       </c>
       <c r="D2450">
-        <v>249517.44</v>
+        <v>130065.12</v>
       </c>
       <c r="E2450">
-        <v>1635725</v>
+        <v>852649</v>
       </c>
       <c r="F2450">
-        <v>150.95</v>
+        <v>80.53999999999999</v>
       </c>
       <c r="G2450">
-        <v>8539.933752898311</v>
+        <v>8400</v>
       </c>
       <c r="H2450">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I2450" t="inlineStr">
         <is>
@@ -93083,7 +93083,7 @@
     <row r="2451">
       <c r="A2451" t="inlineStr">
         <is>
-          <t>KUBAIR STEEL AND POWER LLP</t>
+          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
         </is>
       </c>
       <c r="B2451" t="inlineStr">
@@ -93092,22 +93092,22 @@
         </is>
       </c>
       <c r="C2451">
-        <v>1293017</v>
+        <v>667201.5</v>
       </c>
       <c r="D2451">
-        <v>232743.06</v>
+        <v>120096.27</v>
       </c>
       <c r="E2451">
-        <v>1525762</v>
+        <v>787298</v>
       </c>
       <c r="F2451">
-        <v>146.35</v>
+        <v>75.39</v>
       </c>
       <c r="G2451">
-        <v>8835.100785787496</v>
+        <v>8850</v>
       </c>
       <c r="H2451">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2451" t="inlineStr">
         <is>
@@ -93121,31 +93121,31 @@
     <row r="2452">
       <c r="A2452" t="inlineStr">
         <is>
-          <t>Mahrishi Meltchems Pvt Ltd</t>
+          <t>RDTMT Steels India Pvt Ltd</t>
         </is>
       </c>
       <c r="B2452" t="inlineStr">
         <is>
-          <t>Quartz Powder</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2452">
-        <v>267538.5</v>
+        <v>650307</v>
       </c>
       <c r="D2452">
-        <v>13376.945</v>
+        <v>117055.26</v>
       </c>
       <c r="E2452">
-        <v>280915.725</v>
+        <v>767362</v>
       </c>
       <c r="F2452">
-        <v>138.84</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G2452">
-        <v>1926.955488331893</v>
+        <v>8650</v>
       </c>
       <c r="H2452">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I2452" t="inlineStr">
         <is>
@@ -93159,7 +93159,7 @@
     <row r="2453">
       <c r="A2453" t="inlineStr">
         <is>
-          <t>Kanishk Steel Industries Ltd</t>
+          <t>Mahrishi Alloys Pvt. Ltd.</t>
         </is>
       </c>
       <c r="B2453" t="inlineStr">
@@ -93168,26 +93168,26 @@
         </is>
       </c>
       <c r="C2453">
-        <v>1391530</v>
+        <v>294151.5</v>
       </c>
       <c r="D2453">
-        <v>250475.4</v>
+        <v>52947.28</v>
       </c>
       <c r="E2453">
-        <v>1642006</v>
+        <v>347099</v>
       </c>
       <c r="F2453">
-        <v>135.1</v>
+        <v>72.63</v>
       </c>
       <c r="G2453">
-        <v>10300</v>
+        <v>4050</v>
       </c>
       <c r="H2453">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2453" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2453" s="2">
@@ -93197,7 +93197,7 @@
     <row r="2454">
       <c r="A2454" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+          <t>TEXCON STEELS LIMITED</t>
         </is>
       </c>
       <c r="B2454" t="inlineStr">
@@ -93206,22 +93206,22 @@
         </is>
       </c>
       <c r="C2454">
-        <v>1083632</v>
+        <v>608247</v>
       </c>
       <c r="D2454">
-        <v>195053.76</v>
+        <v>109484.46</v>
       </c>
       <c r="E2454">
-        <v>1278685</v>
+        <v>717731</v>
       </c>
       <c r="F2454">
-        <v>123.14</v>
+        <v>71.14</v>
       </c>
       <c r="G2454">
-        <v>8800.000000000002</v>
+        <v>8550</v>
       </c>
       <c r="H2454">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2454" t="inlineStr">
         <is>
@@ -93235,31 +93235,31 @@
     <row r="2455">
       <c r="A2455" t="inlineStr">
         <is>
-          <t>BMM ISPAT LIMITED</t>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
         </is>
       </c>
       <c r="B2455" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2455">
-        <v>913625.5</v>
+        <v>611424</v>
       </c>
       <c r="D2455">
-        <v>164452.59</v>
+        <v>110056.32</v>
       </c>
       <c r="E2455">
-        <v>1078079</v>
+        <v>721480</v>
       </c>
       <c r="F2455">
-        <v>121.01</v>
+        <v>69.47999999999999</v>
       </c>
       <c r="G2455">
-        <v>7550</v>
+        <v>8800.000000000002</v>
       </c>
       <c r="H2455">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2455" t="inlineStr">
         <is>
@@ -93273,35 +93273,35 @@
     <row r="2456">
       <c r="A2456" t="inlineStr">
         <is>
-          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2456" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2456">
-        <v>1018048.5</v>
+        <v>468013</v>
       </c>
       <c r="D2456">
-        <v>183248.73</v>
+        <v>84242.34</v>
       </c>
       <c r="E2456">
-        <v>1201298</v>
+        <v>552256</v>
       </c>
       <c r="F2456">
-        <v>119.07</v>
+        <v>67.34</v>
       </c>
       <c r="G2456">
-        <v>8550</v>
+        <v>6950</v>
       </c>
       <c r="H2456">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2456" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2456" s="2">
@@ -93311,31 +93311,31 @@
     <row r="2457">
       <c r="A2457" t="inlineStr">
         <is>
-          <t>S.R. STEEL PVT LTD</t>
+          <t>RELIANCE CONCAST SOLUTIONS</t>
         </is>
       </c>
       <c r="B2457" t="inlineStr">
         <is>
-          <t>Ordinary Ramming Mass</t>
+          <t>Quartz Powder</t>
         </is>
       </c>
       <c r="C2457">
-        <v>1279488</v>
+        <v>182544</v>
       </c>
       <c r="D2457">
-        <v>11709.6</v>
+        <v>9127.200000000001</v>
       </c>
       <c r="E2457">
-        <v>1279488</v>
+        <v>191671</v>
       </c>
       <c r="F2457">
-        <v>112</v>
+        <v>61.35</v>
       </c>
       <c r="G2457">
-        <v>11424</v>
+        <v>2975.452322738387</v>
       </c>
       <c r="H2457">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2457" t="inlineStr">
         <is>
@@ -93349,35 +93349,35 @@
     <row r="2458">
       <c r="A2458" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>Shyam Ferrous Ltd.</t>
         </is>
       </c>
       <c r="B2458" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2458">
-        <v>485100</v>
+        <v>512662.5</v>
       </c>
       <c r="D2458">
-        <v>87318</v>
+        <v>92279.25999999999</v>
       </c>
       <c r="E2458">
-        <v>572418</v>
+        <v>604943</v>
       </c>
       <c r="F2458">
-        <v>110.25</v>
+        <v>58.59</v>
       </c>
       <c r="G2458">
-        <v>4400</v>
+        <v>8750</v>
       </c>
       <c r="H2458">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2458" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2458" s="2">
@@ -93387,31 +93387,31 @@
     <row r="2459">
       <c r="A2459" t="inlineStr">
         <is>
-          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+          <t>Shri Tirupati Steel Cast Ltd</t>
         </is>
       </c>
       <c r="B2459" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2459">
-        <v>975384</v>
+        <v>191095.5</v>
       </c>
       <c r="D2459">
-        <v>175569.12</v>
+        <v>34397.22</v>
       </c>
       <c r="E2459">
-        <v>1150954</v>
+        <v>225493</v>
       </c>
       <c r="F2459">
-        <v>106.02</v>
+        <v>55.39</v>
       </c>
       <c r="G2459">
-        <v>9200</v>
+        <v>3450</v>
       </c>
       <c r="H2459">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2459" t="inlineStr">
         <is>
@@ -93425,35 +93425,35 @@
     <row r="2460">
       <c r="A2460" t="inlineStr">
         <is>
-          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2460" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2460">
-        <v>715433</v>
+        <v>476612.5</v>
       </c>
       <c r="D2460">
-        <v>128777.94</v>
+        <v>91627.66</v>
       </c>
       <c r="E2460">
-        <v>844212</v>
+        <v>600670</v>
       </c>
       <c r="F2460">
-        <v>102.94</v>
+        <v>54.47</v>
       </c>
       <c r="G2460">
-        <v>6950</v>
+        <v>8750</v>
       </c>
       <c r="H2460">
         <v>3</v>
       </c>
       <c r="I2460" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2460" s="2">
@@ -93463,7 +93463,7 @@
     <row r="2461">
       <c r="A2461" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2461" t="inlineStr">
@@ -93472,26 +93472,26 @@
         </is>
       </c>
       <c r="C2461">
-        <v>1016859</v>
+        <v>443700</v>
       </c>
       <c r="D2461">
-        <v>183034.62</v>
+        <v>79866</v>
       </c>
       <c r="E2461">
-        <v>1199895</v>
+        <v>523566</v>
       </c>
       <c r="F2461">
-        <v>101.18</v>
+        <v>51</v>
       </c>
       <c r="G2461">
-        <v>10050</v>
+        <v>8700</v>
       </c>
       <c r="H2461">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2461" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2461" s="2">
@@ -93501,7 +93501,7 @@
     <row r="2462">
       <c r="A2462" t="inlineStr">
         <is>
-          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+          <t>Prakash Ferrous Industries Pvt Ltd</t>
         </is>
       </c>
       <c r="B2462" t="inlineStr">
@@ -93510,26 +93510,26 @@
         </is>
       </c>
       <c r="C2462">
-        <v>835440</v>
+        <v>465148</v>
       </c>
       <c r="D2462">
-        <v>150379.22</v>
+        <v>83726.64</v>
       </c>
       <c r="E2462">
-        <v>985819</v>
+        <v>548875</v>
       </c>
       <c r="F2462">
-        <v>94.40000000000001</v>
+        <v>45.16</v>
       </c>
       <c r="G2462">
-        <v>8850</v>
+        <v>10300</v>
       </c>
       <c r="H2462">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2462" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2462" s="2">
@@ -93539,7 +93539,7 @@
     <row r="2463">
       <c r="A2463" t="inlineStr">
         <is>
-          <t>Keshree Metalurgies Pvt Ltd</t>
+          <t>Kanishk Steel Industries Ltd</t>
         </is>
       </c>
       <c r="B2463" t="inlineStr">
@@ -93548,26 +93548,26 @@
         </is>
       </c>
       <c r="C2463">
-        <v>811968</v>
+        <v>462470</v>
       </c>
       <c r="D2463">
-        <v>146154.24</v>
+        <v>83244.60000000001</v>
       </c>
       <c r="E2463">
-        <v>958123</v>
+        <v>545715</v>
       </c>
       <c r="F2463">
-        <v>84.58</v>
+        <v>44.9</v>
       </c>
       <c r="G2463">
-        <v>9600</v>
+        <v>10300</v>
       </c>
       <c r="H2463">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2463" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2463" s="2">
@@ -93577,7 +93577,7 @@
     <row r="2464">
       <c r="A2464" t="inlineStr">
         <is>
-          <t>ADRI STEEL PRIVATE LIMITED</t>
+          <t>GBR Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2464" t="inlineStr">
@@ -93586,26 +93586,26 @@
         </is>
       </c>
       <c r="C2464">
-        <v>690550</v>
+        <v>439295</v>
       </c>
       <c r="D2464">
-        <v>130136.42</v>
+        <v>79073.10000000001</v>
       </c>
       <c r="E2464">
-        <v>853116</v>
+        <v>518368</v>
       </c>
       <c r="F2464">
-        <v>78.92</v>
+        <v>42.65</v>
       </c>
       <c r="G2464">
-        <v>8750</v>
+        <v>10300</v>
       </c>
       <c r="H2464">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2464" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2464" s="2">
@@ -93615,28 +93615,28 @@
     <row r="2465">
       <c r="A2465" t="inlineStr">
         <is>
-          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2465" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2465">
-        <v>678592.5</v>
+        <v>271012.5</v>
       </c>
       <c r="D2465">
-        <v>122146.65</v>
+        <v>48782.25</v>
       </c>
       <c r="E2465">
-        <v>800740</v>
+        <v>319794</v>
       </c>
       <c r="F2465">
-        <v>78.45</v>
+        <v>40.15000000000001</v>
       </c>
       <c r="G2465">
-        <v>8650</v>
+        <v>6749.999999999999</v>
       </c>
       <c r="H2465">
         <v>2</v>
@@ -93653,7 +93653,7 @@
     <row r="2466">
       <c r="A2466" t="inlineStr">
         <is>
-          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+          <t>Keshree Metalurgies Pvt Ltd</t>
         </is>
       </c>
       <c r="B2466" t="inlineStr">
@@ -93662,26 +93662,26 @@
         </is>
       </c>
       <c r="C2466">
-        <v>678861</v>
+        <v>384000</v>
       </c>
       <c r="D2466">
-        <v>122194.98</v>
+        <v>69120</v>
       </c>
       <c r="E2466">
-        <v>801056</v>
+        <v>453120</v>
       </c>
       <c r="F2466">
-        <v>78.03</v>
+        <v>40</v>
       </c>
       <c r="G2466">
-        <v>8700</v>
+        <v>9600</v>
       </c>
       <c r="H2466">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2466" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2466" s="2">
@@ -93691,7 +93691,7 @@
     <row r="2467">
       <c r="A2467" t="inlineStr">
         <is>
-          <t>Shri Tirupati Steel Cast Ltd</t>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
         </is>
       </c>
       <c r="B2467" t="inlineStr">
@@ -93700,26 +93700,26 @@
         </is>
       </c>
       <c r="C2467">
-        <v>264063</v>
+        <v>134274</v>
       </c>
       <c r="D2467">
-        <v>47531.38</v>
+        <v>24169.32</v>
       </c>
       <c r="E2467">
-        <v>311595</v>
+        <v>158443</v>
       </c>
       <c r="F2467">
-        <v>76.53999999999999</v>
+        <v>38.92</v>
       </c>
       <c r="G2467">
         <v>3450</v>
       </c>
       <c r="H2467">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2467" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2467" s="2">
@@ -93729,35 +93729,35 @@
     <row r="2468">
       <c r="A2468" t="inlineStr">
         <is>
-          <t>RELIANCE CONCAST SOLUTIONS</t>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
         </is>
       </c>
       <c r="B2468" t="inlineStr">
         <is>
-          <t>Quartz Powder</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2468">
-        <v>182544</v>
+        <v>327056.5</v>
       </c>
       <c r="D2468">
-        <v>9127.200000000001</v>
+        <v>58870.17</v>
       </c>
       <c r="E2468">
-        <v>191671</v>
+        <v>385927</v>
       </c>
       <c r="F2468">
-        <v>61.35</v>
+        <v>37.81</v>
       </c>
       <c r="G2468">
-        <v>2975.452322738387</v>
+        <v>8650</v>
       </c>
       <c r="H2468">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2468" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2468" s="2">
@@ -93767,7 +93767,7 @@
     <row r="2469">
       <c r="A2469" t="inlineStr">
         <is>
-          <t>Shyam Ferrous Ltd.</t>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
         </is>
       </c>
       <c r="B2469" t="inlineStr">
@@ -93776,26 +93776,26 @@
         </is>
       </c>
       <c r="C2469">
-        <v>512662.5</v>
+        <v>327980</v>
       </c>
       <c r="D2469">
-        <v>92279.25999999999</v>
+        <v>59036.4</v>
       </c>
       <c r="E2469">
-        <v>604943</v>
+        <v>387017</v>
       </c>
       <c r="F2469">
-        <v>58.59</v>
+        <v>35.65</v>
       </c>
       <c r="G2469">
-        <v>8750</v>
+        <v>9200</v>
       </c>
       <c r="H2469">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2469" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2469" s="2">
@@ -93805,35 +93805,35 @@
     <row r="2470">
       <c r="A2470" t="inlineStr">
         <is>
-          <t>RDTMT Steels India Pvt Ltd</t>
+          <t>VMC Steel and Alloys Industry</t>
         </is>
       </c>
       <c r="B2470" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2470">
-        <v>169571</v>
+        <v>368445</v>
       </c>
       <c r="D2470">
-        <v>30522.78</v>
+        <v>66320.10000000001</v>
       </c>
       <c r="E2470">
-        <v>200093</v>
+        <v>434765</v>
       </c>
       <c r="F2470">
-        <v>45.83000000000001</v>
+        <v>35.09</v>
       </c>
       <c r="G2470">
-        <v>3700</v>
+        <v>10500</v>
       </c>
       <c r="H2470">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2470" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2470" s="2">
@@ -93843,28 +93843,28 @@
     <row r="2471">
       <c r="A2471" t="inlineStr">
         <is>
-          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+          <t>PARAGON STEEL DISTRIBUITORS</t>
         </is>
       </c>
       <c r="B2471" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2471">
-        <v>162615</v>
+        <v>238000</v>
       </c>
       <c r="D2471">
-        <v>29270.7</v>
+        <v>42840</v>
       </c>
       <c r="E2471">
-        <v>191886</v>
+        <v>280840</v>
       </c>
       <c r="F2471">
-        <v>43.95</v>
+        <v>35</v>
       </c>
       <c r="G2471">
-        <v>3700</v>
+        <v>6800</v>
       </c>
       <c r="H2471">
         <v>2</v>
@@ -93881,7 +93881,7 @@
     <row r="2472">
       <c r="A2472" t="inlineStr">
         <is>
-          <t>GBR Metals Pvt Ltd</t>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
         </is>
       </c>
       <c r="B2472" t="inlineStr">
@@ -93890,26 +93890,26 @@
         </is>
       </c>
       <c r="C2472">
-        <v>439295</v>
+        <v>306298.5</v>
       </c>
       <c r="D2472">
-        <v>79073.10000000001</v>
+        <v>55133.74</v>
       </c>
       <c r="E2472">
-        <v>518368</v>
+        <v>361432</v>
       </c>
       <c r="F2472">
-        <v>42.65</v>
+        <v>34.61</v>
       </c>
       <c r="G2472">
-        <v>10300</v>
+        <v>8850</v>
       </c>
       <c r="H2472">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2472" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2472" s="2">
@@ -93919,35 +93919,35 @@
     <row r="2473">
       <c r="A2473" t="inlineStr">
         <is>
-          <t>KRISHNA STEEL ROLLING MILLS</t>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
         </is>
       </c>
       <c r="B2473" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2473">
-        <v>286160</v>
+        <v>141655</v>
       </c>
       <c r="D2473">
-        <v>66912.84</v>
+        <v>25497.9</v>
       </c>
       <c r="E2473">
-        <v>438651</v>
+        <v>167153</v>
       </c>
       <c r="F2473">
-        <v>40.88</v>
+        <v>34.55</v>
       </c>
       <c r="G2473">
-        <v>7000.000000000001</v>
+        <v>4100</v>
       </c>
       <c r="H2473">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2473" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2473" s="2">
@@ -93957,35 +93957,35 @@
     <row r="2474">
       <c r="A2474" t="inlineStr">
         <is>
-          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
+          <t>Sri M.S.T. Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2474" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2474">
-        <v>271012.5</v>
+        <v>264430.5</v>
       </c>
       <c r="D2474">
-        <v>48782.25</v>
+        <v>47597.49</v>
       </c>
       <c r="E2474">
-        <v>319794</v>
+        <v>312028</v>
       </c>
       <c r="F2474">
-        <v>40.15000000000001</v>
+        <v>30.57</v>
       </c>
       <c r="G2474">
-        <v>6749.999999999999</v>
+        <v>8650</v>
       </c>
       <c r="H2474">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2474" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2474" s="2">
@@ -93995,35 +93995,35 @@
     <row r="2475">
       <c r="A2475" t="inlineStr">
         <is>
-          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2475" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2475">
-        <v>134274</v>
+        <v>306324</v>
       </c>
       <c r="D2475">
-        <v>24169.32</v>
+        <v>55138.32</v>
       </c>
       <c r="E2475">
-        <v>158443</v>
+        <v>361463</v>
       </c>
       <c r="F2475">
-        <v>38.92</v>
+        <v>30.48</v>
       </c>
       <c r="G2475">
-        <v>3450</v>
+        <v>10050</v>
       </c>
       <c r="H2475">
         <v>1</v>
       </c>
       <c r="I2475" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2475" s="2">
@@ -94033,35 +94033,35 @@
     <row r="2476">
       <c r="A2476" t="inlineStr">
         <is>
-          <t>SREE PALANIANDAVAR ALLOYS AND STEELS PVT LTD</t>
+          <t>Meenakshi Steels</t>
         </is>
       </c>
       <c r="B2476" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2476">
-        <v>244779</v>
+        <v>315420</v>
       </c>
       <c r="D2476">
-        <v>44060.22</v>
+        <v>56775.6</v>
       </c>
       <c r="E2476">
-        <v>288839</v>
+        <v>372196</v>
       </c>
       <c r="F2476">
-        <v>35.22</v>
+        <v>30.04</v>
       </c>
       <c r="G2476">
-        <v>6950</v>
+        <v>10500</v>
       </c>
       <c r="H2476">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2476" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2476" s="2">
@@ -94071,35 +94071,35 @@
     <row r="2477">
       <c r="A2477" t="inlineStr">
         <is>
-          <t>VGK STEELS</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2477" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2477">
-        <v>307737.5</v>
+        <v>131208</v>
       </c>
       <c r="D2477">
-        <v>55392.75</v>
+        <v>23617.44</v>
       </c>
       <c r="E2477">
-        <v>363130</v>
+        <v>154825</v>
       </c>
       <c r="F2477">
-        <v>35.17</v>
+        <v>29.82</v>
       </c>
       <c r="G2477">
-        <v>8750</v>
+        <v>4400</v>
       </c>
       <c r="H2477">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2477" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2477" s="2">
@@ -94109,7 +94109,7 @@
     <row r="2478">
       <c r="A2478" t="inlineStr">
         <is>
-          <t>VMC Steel and Alloys Industry</t>
+          <t>BLUE GOLD STEEL INDUSTRIES</t>
         </is>
       </c>
       <c r="B2478" t="inlineStr">
@@ -94118,26 +94118,26 @@
         </is>
       </c>
       <c r="C2478">
-        <v>368445</v>
+        <v>228112.5</v>
       </c>
       <c r="D2478">
-        <v>66320.10000000001</v>
+        <v>41060.26</v>
       </c>
       <c r="E2478">
-        <v>434765</v>
+        <v>269173</v>
       </c>
       <c r="F2478">
-        <v>35.09</v>
+        <v>26.07</v>
       </c>
       <c r="G2478">
-        <v>10500</v>
+        <v>8750</v>
       </c>
       <c r="H2478">
         <v>1</v>
       </c>
       <c r="I2478" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2478" s="2">
@@ -94147,7 +94147,7 @@
     <row r="2479">
       <c r="A2479" t="inlineStr">
         <is>
-          <t>PARAGON STEEL DISTRIBUITORS</t>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
         </is>
       </c>
       <c r="B2479" t="inlineStr">
@@ -94156,26 +94156,26 @@
         </is>
       </c>
       <c r="C2479">
-        <v>238000</v>
+        <v>171948</v>
       </c>
       <c r="D2479">
-        <v>42840</v>
+        <v>30950.64</v>
       </c>
       <c r="E2479">
-        <v>280840</v>
+        <v>202899</v>
       </c>
       <c r="F2479">
-        <v>35</v>
+        <v>24.92</v>
       </c>
       <c r="G2479">
-        <v>6800</v>
+        <v>6899.999999999999</v>
       </c>
       <c r="H2479">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2479" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2479" s="2">
@@ -94185,7 +94185,7 @@
     <row r="2480">
       <c r="A2480" t="inlineStr">
         <is>
-          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+          <t>BLUE GOLD STEEL INDUSTRIES</t>
         </is>
       </c>
       <c r="B2480" t="inlineStr">
@@ -94194,26 +94194,26 @@
         </is>
       </c>
       <c r="C2480">
-        <v>141655</v>
+        <v>65895</v>
       </c>
       <c r="D2480">
-        <v>25497.9</v>
+        <v>11861.1</v>
       </c>
       <c r="E2480">
-        <v>167153</v>
+        <v>77756</v>
       </c>
       <c r="F2480">
-        <v>34.55</v>
+        <v>19.1</v>
       </c>
       <c r="G2480">
-        <v>4100</v>
+        <v>3450</v>
       </c>
       <c r="H2480">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2480" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2480" s="2">
@@ -94223,35 +94223,35 @@
     <row r="2481">
       <c r="A2481" t="inlineStr">
         <is>
-          <t>Sri M.S.T. Smelters Private Limited</t>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
         </is>
       </c>
       <c r="B2481" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2481">
-        <v>264430.5</v>
+        <v>69301</v>
       </c>
       <c r="D2481">
-        <v>47597.49</v>
+        <v>12474.18</v>
       </c>
       <c r="E2481">
-        <v>312028</v>
+        <v>81775</v>
       </c>
       <c r="F2481">
-        <v>30.57</v>
+        <v>18.73</v>
       </c>
       <c r="G2481">
-        <v>8650</v>
+        <v>3700</v>
       </c>
       <c r="H2481">
         <v>1</v>
       </c>
       <c r="I2481" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2481" s="2">
@@ -94261,35 +94261,35 @@
     <row r="2482">
       <c r="A2482" t="inlineStr">
         <is>
-          <t>Meenakshi Steels</t>
+          <t>KRISHNA STEEL ROLLING MILLS</t>
         </is>
       </c>
       <c r="B2482" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2482">
-        <v>315420</v>
+        <v>60758</v>
       </c>
       <c r="D2482">
-        <v>56775.6</v>
+        <v>0</v>
       </c>
       <c r="E2482">
-        <v>372196</v>
+        <v>71694.44</v>
       </c>
       <c r="F2482">
-        <v>30.04</v>
+        <v>17.87</v>
       </c>
       <c r="G2482">
-        <v>10500</v>
+        <v>3400</v>
       </c>
       <c r="H2482">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2482" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2482" s="2">
@@ -94299,7 +94299,7 @@
     <row r="2483">
       <c r="A2483" t="inlineStr">
         <is>
-          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+          <t>PRINCE ALLOYS (P) LTD</t>
         </is>
       </c>
       <c r="B2483" t="inlineStr">
@@ -94308,22 +94308,22 @@
         </is>
       </c>
       <c r="C2483">
-        <v>203292.5</v>
+        <v>124127</v>
       </c>
       <c r="D2483">
-        <v>30950.64</v>
+        <v>22342.86</v>
       </c>
       <c r="E2483">
-        <v>239885.51</v>
+        <v>146470</v>
       </c>
       <c r="F2483">
-        <v>29.43</v>
+        <v>17.86</v>
       </c>
       <c r="G2483">
-        <v>6907.662249405369</v>
+        <v>6950</v>
       </c>
       <c r="H2483">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2483" t="inlineStr">
         <is>
@@ -94337,35 +94337,35 @@
     <row r="2484">
       <c r="A2484" t="inlineStr">
         <is>
-          <t>BLUE GOLD STEEL INDUSTRIES</t>
+          <t>PRINCE ROLLINGS  (P) LTD</t>
         </is>
       </c>
       <c r="B2484" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2484">
-        <v>228112.5</v>
+        <v>123710</v>
       </c>
       <c r="D2484">
-        <v>41060.26</v>
+        <v>22267.8</v>
       </c>
       <c r="E2484">
-        <v>269173</v>
+        <v>145978</v>
       </c>
       <c r="F2484">
-        <v>26.07</v>
+        <v>17.8</v>
       </c>
       <c r="G2484">
-        <v>8750</v>
+        <v>6950</v>
       </c>
       <c r="H2484">
         <v>1</v>
       </c>
       <c r="I2484" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2484" s="2">
@@ -94375,35 +94375,35 @@
     <row r="2485">
       <c r="A2485" t="inlineStr">
         <is>
-          <t>KUBAIR STEEL AND POWER LLP</t>
+          <t>KRISHNA STEEL ROLLING MILLS</t>
         </is>
       </c>
       <c r="B2485" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2485">
-        <v>92016.5</v>
+        <v>124110</v>
       </c>
       <c r="D2485">
-        <v>16562.98</v>
+        <v>33276.24</v>
       </c>
       <c r="E2485">
-        <v>108579</v>
+        <v>218144</v>
       </c>
       <c r="F2485">
-        <v>25.21</v>
+        <v>17.73</v>
       </c>
       <c r="G2485">
-        <v>3650</v>
+        <v>7000</v>
       </c>
       <c r="H2485">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2485" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2485" s="2">
@@ -94413,35 +94413,35 @@
     <row r="2486">
       <c r="A2486" t="inlineStr">
         <is>
-          <t>KRISHNA STEEL ROLLING MILLS</t>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2486" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2486">
-        <v>85578</v>
+        <v>105820.5</v>
       </c>
       <c r="D2486">
-        <v>0</v>
+        <v>13210.3</v>
       </c>
       <c r="E2486">
-        <v>100982.04</v>
+        <v>124868.4</v>
       </c>
       <c r="F2486">
-        <v>25.17</v>
+        <v>15.01</v>
       </c>
       <c r="G2486">
-        <v>3400</v>
+        <v>7050</v>
       </c>
       <c r="H2486">
         <v>2</v>
       </c>
       <c r="I2486" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2486" s="2">
@@ -94451,28 +94451,28 @@
     <row r="2487">
       <c r="A2487" t="inlineStr">
         <is>
-          <t>SNAM ALLOYS PRIVATE LIMITED</t>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2487" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2487">
-        <v>145000</v>
+        <v>46048</v>
       </c>
       <c r="D2487">
-        <v>26100</v>
+        <v>0</v>
       </c>
       <c r="E2487">
-        <v>171100</v>
+        <v>54336.64</v>
       </c>
       <c r="F2487">
-        <v>20</v>
+        <v>14.39</v>
       </c>
       <c r="G2487">
-        <v>7250</v>
+        <v>3200</v>
       </c>
       <c r="H2487">
         <v>1</v>
@@ -94489,7 +94489,7 @@
     <row r="2488">
       <c r="A2488" t="inlineStr">
         <is>
-          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+          <t>RDTMT Steels India Pvt Ltd</t>
         </is>
       </c>
       <c r="B2488" t="inlineStr">
@@ -94498,26 +94498,26 @@
         </is>
       </c>
       <c r="C2488">
-        <v>65802</v>
+        <v>37074</v>
       </c>
       <c r="D2488">
-        <v>17486.37</v>
+        <v>6673.32</v>
       </c>
       <c r="E2488">
-        <v>114633</v>
+        <v>43747</v>
       </c>
       <c r="F2488">
-        <v>19.94</v>
+        <v>10.02</v>
       </c>
       <c r="G2488">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="H2488">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2488" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2488" s="2">
@@ -94527,35 +94527,35 @@
     <row r="2489">
       <c r="A2489" t="inlineStr">
         <is>
-          <t>Adishakti Smelters Private Limited</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2489" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Tundish Ramming Mix</t>
         </is>
       </c>
       <c r="C2489">
-        <v>68310</v>
+        <v>252450</v>
       </c>
       <c r="D2489">
-        <v>0</v>
+        <v>45441</v>
       </c>
       <c r="E2489">
-        <v>80605.8</v>
+        <v>297891</v>
       </c>
       <c r="F2489">
-        <v>19.8</v>
+        <v>9.35</v>
       </c>
       <c r="G2489">
-        <v>3450</v>
+        <v>27000</v>
       </c>
       <c r="H2489">
         <v>1</v>
       </c>
       <c r="I2489" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2489" s="2">
@@ -94565,145 +94565,145 @@
     <row r="2490">
       <c r="A2490" t="inlineStr">
         <is>
-          <t>BLUE GOLD STEEL INDUSTRIES</t>
+          <t>Pushpit Steels Private Limited</t>
         </is>
       </c>
       <c r="B2490" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2490">
-        <v>65895</v>
+        <v>3109044</v>
       </c>
       <c r="D2490">
-        <v>11861.1</v>
+        <v>559627.92</v>
       </c>
       <c r="E2490">
-        <v>77756</v>
+        <v>3668672</v>
       </c>
       <c r="F2490">
-        <v>19.1</v>
+        <v>320.52</v>
       </c>
       <c r="G2490">
-        <v>3450</v>
+        <v>9700</v>
       </c>
       <c r="H2490">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I2490" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2490" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="2491">
       <c r="A2491" t="inlineStr">
         <is>
-          <t>PRINCE ALLOYS (P) LTD</t>
+          <t>A One Ispat Private Ltd</t>
         </is>
       </c>
       <c r="B2491" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2491">
-        <v>124127</v>
+        <v>2788100</v>
       </c>
       <c r="D2491">
-        <v>22342.86</v>
+        <v>501858.02</v>
       </c>
       <c r="E2491">
-        <v>146470</v>
+        <v>3289959</v>
       </c>
       <c r="F2491">
-        <v>17.86</v>
+        <v>318.64</v>
       </c>
       <c r="G2491">
-        <v>6950</v>
+        <v>8750</v>
       </c>
       <c r="H2491">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I2491" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2491" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="2492">
       <c r="A2492" t="inlineStr">
         <is>
-          <t>PRINCE ROLLINGS  (P) LTD</t>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2492" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2492">
-        <v>123710</v>
+        <v>2024190</v>
       </c>
       <c r="D2492">
-        <v>22267.8</v>
+        <v>364354.2</v>
       </c>
       <c r="E2492">
-        <v>145978</v>
+        <v>2388544</v>
       </c>
       <c r="F2492">
-        <v>17.8</v>
+        <v>224.91</v>
       </c>
       <c r="G2492">
-        <v>6950</v>
+        <v>9000</v>
       </c>
       <c r="H2492">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2492" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2492" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="2493">
       <c r="A2493" t="inlineStr">
         <is>
-          <t>ADRI STEEL PRIVATE LIMITED</t>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
         </is>
       </c>
       <c r="B2493" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2493">
-        <v>105820.5</v>
+        <v>2087200.5</v>
       </c>
       <c r="D2493">
-        <v>13210.3</v>
+        <v>375696.09</v>
       </c>
       <c r="E2493">
-        <v>124868.4</v>
+        <v>2462897</v>
       </c>
       <c r="F2493">
-        <v>15.01</v>
+        <v>223.23</v>
       </c>
       <c r="G2493">
-        <v>7050</v>
+        <v>9350</v>
       </c>
       <c r="H2493">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2493" t="inlineStr">
         <is>
@@ -94711,37 +94711,37 @@
         </is>
       </c>
       <c r="J2493" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="2494">
       <c r="A2494" t="inlineStr">
         <is>
-          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+          <t>KUBAIR STEEL AND POWER LLP</t>
         </is>
       </c>
       <c r="B2494" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2494">
-        <v>46048</v>
+        <v>1957708.5</v>
       </c>
       <c r="D2494">
-        <v>0</v>
+        <v>352387.58</v>
       </c>
       <c r="E2494">
-        <v>54336.64</v>
+        <v>2310096</v>
       </c>
       <c r="F2494">
-        <v>14.39</v>
+        <v>221.21</v>
       </c>
       <c r="G2494">
-        <v>3200</v>
+        <v>8850</v>
       </c>
       <c r="H2494">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2494" t="inlineStr">
         <is>
@@ -94749,37 +94749,37 @@
         </is>
       </c>
       <c r="J2494" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="2495">
       <c r="A2495" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>Suryadev Alloys &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2495" t="inlineStr">
         <is>
-          <t>Tundish Ramming Mix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2495">
-        <v>252450</v>
+        <v>1681602</v>
       </c>
       <c r="D2495">
-        <v>45441</v>
+        <v>302688.36</v>
       </c>
       <c r="E2495">
-        <v>297891</v>
+        <v>1984289</v>
       </c>
       <c r="F2495">
-        <v>9.35</v>
+        <v>215.59</v>
       </c>
       <c r="G2495">
-        <v>27000</v>
+        <v>7800</v>
       </c>
       <c r="H2495">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I2495" t="inlineStr">
         <is>
@@ -94787,7 +94787,7 @@
         </is>
       </c>
       <c r="J2495" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="2496">
@@ -94796,23 +94796,25 @@
           <t>Mahrishi Meltchems Pvt Ltd</t>
         </is>
       </c>
+      <c r="B2496" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
       <c r="C2496">
-        <v>825000</v>
+        <v>486640</v>
       </c>
       <c r="D2496">
-        <v>148500</v>
-      </c>
-      <c r="E2496">
-        <v>973500</v>
+        <v>24332.02</v>
       </c>
       <c r="F2496">
-        <v>5</v>
+        <v>206.08</v>
       </c>
       <c r="G2496">
-        <v>165000</v>
+        <v>2361.413043478261</v>
       </c>
       <c r="H2496">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I2496" t="inlineStr">
         <is>
@@ -94820,32 +94822,37 @@
         </is>
       </c>
       <c r="J2496" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="2497">
       <c r="A2497" t="inlineStr">
         <is>
-          <t>Mahrishi Meltchems Pvt Ltd</t>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2497">
-        <v>696600</v>
+        <v>1728760</v>
       </c>
       <c r="D2497">
-        <v>125388</v>
+        <v>311176.8</v>
       </c>
       <c r="E2497">
-        <v>821988</v>
+        <v>2039938</v>
       </c>
       <c r="F2497">
-        <v>1.8</v>
+        <v>196.45</v>
       </c>
       <c r="G2497">
-        <v>387000</v>
+        <v>8800</v>
       </c>
       <c r="H2497">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2497" t="inlineStr">
         <is>
@@ -94853,13 +94860,13 @@
         </is>
       </c>
       <c r="J2497" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="2498">
       <c r="A2498" t="inlineStr">
         <is>
-          <t>Pushpit Steels Private Limited</t>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
         </is>
       </c>
       <c r="B2498" t="inlineStr">
@@ -94868,22 +94875,22 @@
         </is>
       </c>
       <c r="C2498">
-        <v>3109044</v>
+        <v>1776792</v>
       </c>
       <c r="D2498">
-        <v>559627.92</v>
+        <v>319822.56</v>
       </c>
       <c r="E2498">
-        <v>3668672</v>
+        <v>2096616</v>
       </c>
       <c r="F2498">
-        <v>320.52</v>
+        <v>175.92</v>
       </c>
       <c r="G2498">
-        <v>9700</v>
+        <v>10100</v>
       </c>
       <c r="H2498">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I2498" t="inlineStr">
         <is>
@@ -94897,7 +94904,7 @@
     <row r="2499">
       <c r="A2499" t="inlineStr">
         <is>
-          <t>A One Ispat Private Ltd</t>
+          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
         </is>
       </c>
       <c r="B2499" t="inlineStr">
@@ -94906,22 +94913,22 @@
         </is>
       </c>
       <c r="C2499">
-        <v>2788100</v>
+        <v>1509279</v>
       </c>
       <c r="D2499">
-        <v>501858.02</v>
+        <v>271670.22</v>
       </c>
       <c r="E2499">
-        <v>3289959</v>
+        <v>1780949</v>
       </c>
       <c r="F2499">
-        <v>318.64</v>
+        <v>170.54</v>
       </c>
       <c r="G2499">
-        <v>8750</v>
+        <v>8850</v>
       </c>
       <c r="H2499">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2499" t="inlineStr">
         <is>
@@ -94935,7 +94942,7 @@
     <row r="2500">
       <c r="A2500" t="inlineStr">
         <is>
-          <t>Minera Steel &amp; Power Pvt Ltd</t>
+          <t>Meenakshi Udyog India Pvt Ltd.</t>
         </is>
       </c>
       <c r="B2500" t="inlineStr">
@@ -94944,26 +94951,26 @@
         </is>
       </c>
       <c r="C2500">
-        <v>2024190</v>
+        <v>1634002.5</v>
       </c>
       <c r="D2500">
-        <v>364354.2</v>
+        <v>294120.45</v>
       </c>
       <c r="E2500">
-        <v>2388544</v>
+        <v>1928124</v>
       </c>
       <c r="F2500">
-        <v>224.91</v>
+        <v>167.59</v>
       </c>
       <c r="G2500">
-        <v>9000</v>
+        <v>9750</v>
       </c>
       <c r="H2500">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2500" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2500" s="2">
@@ -94973,7 +94980,7 @@
     <row r="2501">
       <c r="A2501" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
         </is>
       </c>
       <c r="B2501" t="inlineStr">
@@ -94982,22 +94989,22 @@
         </is>
       </c>
       <c r="C2501">
-        <v>2087200.5</v>
+        <v>1484144</v>
       </c>
       <c r="D2501">
-        <v>375696.09</v>
+        <v>267145.92</v>
       </c>
       <c r="E2501">
-        <v>2462897</v>
+        <v>1751289</v>
       </c>
       <c r="F2501">
-        <v>223.23</v>
+        <v>161.32</v>
       </c>
       <c r="G2501">
-        <v>9350</v>
+        <v>9200</v>
       </c>
       <c r="H2501">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2501" t="inlineStr">
         <is>
@@ -95011,7 +95018,7 @@
     <row r="2502">
       <c r="A2502" t="inlineStr">
         <is>
-          <t>KUBAIR STEEL AND POWER LLP</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2502" t="inlineStr">
@@ -95020,26 +95027,26 @@
         </is>
       </c>
       <c r="C2502">
-        <v>1957708.5</v>
+        <v>1443682.5</v>
       </c>
       <c r="D2502">
-        <v>352387.58</v>
+        <v>259862.85</v>
       </c>
       <c r="E2502">
-        <v>2310096</v>
+        <v>1703546</v>
       </c>
       <c r="F2502">
-        <v>221.21</v>
+        <v>143.65</v>
       </c>
       <c r="G2502">
-        <v>8850</v>
+        <v>10050</v>
       </c>
       <c r="H2502">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2502" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2502" s="2">
@@ -95049,35 +95056,35 @@
     <row r="2503">
       <c r="A2503" t="inlineStr">
         <is>
-          <t>Suryadev Alloys &amp; Power Pvt Ltd</t>
+          <t>RDTMT Steels India Pvt Ltd</t>
         </is>
       </c>
       <c r="B2503" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2503">
-        <v>1681602</v>
+        <v>1145087</v>
       </c>
       <c r="D2503">
-        <v>302688.36</v>
+        <v>206115.68</v>
       </c>
       <c r="E2503">
-        <v>1984289</v>
+        <v>1351202</v>
       </c>
       <c r="F2503">
-        <v>215.59</v>
+        <v>132.38</v>
       </c>
       <c r="G2503">
-        <v>7800</v>
+        <v>8650</v>
       </c>
       <c r="H2503">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I2503" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2503" s="2">
@@ -95087,28 +95094,31 @@
     <row r="2504">
       <c r="A2504" t="inlineStr">
         <is>
-          <t>Mahrishi Meltchems Pvt Ltd</t>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
         </is>
       </c>
       <c r="B2504" t="inlineStr">
         <is>
-          <t>Quartz Powder</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2504">
-        <v>486640</v>
+        <v>1124667</v>
       </c>
       <c r="D2504">
-        <v>24332.02</v>
+        <v>202440.06</v>
+      </c>
+      <c r="E2504">
+        <v>1327108</v>
       </c>
       <c r="F2504">
-        <v>206.08</v>
+        <v>131.54</v>
       </c>
       <c r="G2504">
-        <v>2361.413043478261</v>
+        <v>8550</v>
       </c>
       <c r="H2504">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I2504" t="inlineStr">
         <is>
@@ -95127,26 +95137,26 @@
       </c>
       <c r="B2505" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2505">
-        <v>1728760</v>
+        <v>392938</v>
       </c>
       <c r="D2505">
-        <v>311176.8</v>
+        <v>70728.84</v>
       </c>
       <c r="E2505">
-        <v>2039938</v>
+        <v>463666</v>
       </c>
       <c r="F2505">
-        <v>196.45</v>
+        <v>115.57</v>
       </c>
       <c r="G2505">
-        <v>8800</v>
+        <v>3400</v>
       </c>
       <c r="H2505">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I2505" t="inlineStr">
         <is>
@@ -95160,7 +95170,7 @@
     <row r="2506">
       <c r="A2506" t="inlineStr">
         <is>
-          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+          <t>Adishakti Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2506" t="inlineStr">
@@ -95169,26 +95179,26 @@
         </is>
       </c>
       <c r="C2506">
-        <v>1776792</v>
+        <v>988487.5</v>
       </c>
       <c r="D2506">
-        <v>319822.56</v>
+        <v>205425.68</v>
       </c>
       <c r="E2506">
-        <v>2096616</v>
+        <v>1346679</v>
       </c>
       <c r="F2506">
-        <v>175.92</v>
+        <v>112.97</v>
       </c>
       <c r="G2506">
-        <v>10100</v>
+        <v>8750</v>
       </c>
       <c r="H2506">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I2506" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2506" s="2">
@@ -95198,7 +95208,7 @@
     <row r="2507">
       <c r="A2507" t="inlineStr">
         <is>
-          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2507" t="inlineStr">
@@ -95207,22 +95217,22 @@
         </is>
       </c>
       <c r="C2507">
-        <v>1509279</v>
+        <v>960654</v>
       </c>
       <c r="D2507">
-        <v>271670.22</v>
+        <v>186830.64</v>
       </c>
       <c r="E2507">
-        <v>1780949</v>
+        <v>1224779</v>
       </c>
       <c r="F2507">
-        <v>170.54</v>
+        <v>110.42</v>
       </c>
       <c r="G2507">
-        <v>8850</v>
+        <v>8700</v>
       </c>
       <c r="H2507">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I2507" t="inlineStr">
         <is>
@@ -95236,35 +95246,35 @@
     <row r="2508">
       <c r="A2508" t="inlineStr">
         <is>
-          <t>Meenakshi Udyog India Pvt Ltd.</t>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2508" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2508">
-        <v>1634002.5</v>
+        <v>735866</v>
       </c>
       <c r="D2508">
-        <v>294120.45</v>
+        <v>132455.88</v>
       </c>
       <c r="E2508">
-        <v>1928124</v>
+        <v>868322</v>
       </c>
       <c r="F2508">
-        <v>167.59</v>
+        <v>105.88</v>
       </c>
       <c r="G2508">
-        <v>9750</v>
+        <v>6949.999999999999</v>
       </c>
       <c r="H2508">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I2508" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2508" s="2">
@@ -95274,7 +95284,7 @@
     <row r="2509">
       <c r="A2509" t="inlineStr">
         <is>
-          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+          <t>Arun Vyapar Udyog Private Limited</t>
         </is>
       </c>
       <c r="B2509" t="inlineStr">
@@ -95283,22 +95293,22 @@
         </is>
       </c>
       <c r="C2509">
-        <v>1484144</v>
+        <v>934856</v>
       </c>
       <c r="D2509">
-        <v>267145.92</v>
+        <v>168274.08</v>
       </c>
       <c r="E2509">
-        <v>1751289</v>
+        <v>1103130</v>
       </c>
       <c r="F2509">
-        <v>161.32</v>
+        <v>92.56</v>
       </c>
       <c r="G2509">
-        <v>9200</v>
+        <v>10100</v>
       </c>
       <c r="H2509">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I2509" t="inlineStr">
         <is>
@@ -95312,7 +95322,7 @@
     <row r="2510">
       <c r="A2510" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
         </is>
       </c>
       <c r="B2510" t="inlineStr">
@@ -95321,26 +95331,26 @@
         </is>
       </c>
       <c r="C2510">
-        <v>1443682.5</v>
+        <v>787160</v>
       </c>
       <c r="D2510">
-        <v>259862.85</v>
+        <v>141688.8</v>
       </c>
       <c r="E2510">
-        <v>1703546</v>
+        <v>928849</v>
       </c>
       <c r="F2510">
-        <v>143.65</v>
+        <v>89.44999999999999</v>
       </c>
       <c r="G2510">
-        <v>10050</v>
+        <v>8800.000000000002</v>
       </c>
       <c r="H2510">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I2510" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2510" s="2">
@@ -95350,7 +95360,7 @@
     <row r="2511">
       <c r="A2511" t="inlineStr">
         <is>
-          <t>RDTMT Steels India Pvt Ltd</t>
+          <t>Prakash Ferrous Industries Pvt Ltd</t>
         </is>
       </c>
       <c r="B2511" t="inlineStr">
@@ -95359,26 +95369,26 @@
         </is>
       </c>
       <c r="C2511">
-        <v>1145087</v>
+        <v>674444</v>
       </c>
       <c r="D2511">
-        <v>206115.68</v>
+        <v>121399.92</v>
       </c>
       <c r="E2511">
-        <v>1351202</v>
+        <v>795844</v>
       </c>
       <c r="F2511">
-        <v>132.38</v>
+        <v>65.48</v>
       </c>
       <c r="G2511">
-        <v>8650</v>
+        <v>10300</v>
       </c>
       <c r="H2511">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2511" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2511" s="2">
@@ -95388,7 +95398,7 @@
     <row r="2512">
       <c r="A2512" t="inlineStr">
         <is>
-          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+          <t>KANNAPPAN IRON AND STEEL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="B2512" t="inlineStr">
@@ -95397,22 +95407,22 @@
         </is>
       </c>
       <c r="C2512">
-        <v>1124667</v>
+        <v>696891</v>
       </c>
       <c r="D2512">
-        <v>202440.06</v>
+        <v>125440.38</v>
       </c>
       <c r="E2512">
-        <v>1327108</v>
+        <v>822331</v>
       </c>
       <c r="F2512">
-        <v>131.54</v>
+        <v>65.13</v>
       </c>
       <c r="G2512">
-        <v>8550</v>
+        <v>10700</v>
       </c>
       <c r="H2512">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2512" t="inlineStr">
         <is>
@@ -95426,31 +95436,31 @@
     <row r="2513">
       <c r="A2513" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+          <t>Mahrishi Alloys Pvt. Ltd.</t>
         </is>
       </c>
       <c r="B2513" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2513">
-        <v>392938</v>
+        <v>276292.5</v>
       </c>
       <c r="D2513">
-        <v>70728.84</v>
+        <v>49732.66</v>
       </c>
       <c r="E2513">
-        <v>463666</v>
+        <v>326025</v>
       </c>
       <c r="F2513">
-        <v>115.57</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="G2513">
-        <v>3400</v>
+        <v>4250</v>
       </c>
       <c r="H2513">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2513" t="inlineStr">
         <is>
@@ -95464,7 +95474,7 @@
     <row r="2514">
       <c r="A2514" t="inlineStr">
         <is>
-          <t>Adishakti Smelters Private Limited</t>
+          <t>TEXCON STEELS LIMITED</t>
         </is>
       </c>
       <c r="B2514" t="inlineStr">
@@ -95473,22 +95483,22 @@
         </is>
       </c>
       <c r="C2514">
-        <v>988487.5</v>
+        <v>555750</v>
       </c>
       <c r="D2514">
-        <v>205425.68</v>
+        <v>100035</v>
       </c>
       <c r="E2514">
-        <v>1346679</v>
+        <v>655785</v>
       </c>
       <c r="F2514">
-        <v>112.97</v>
+        <v>65</v>
       </c>
       <c r="G2514">
-        <v>8750</v>
+        <v>8550</v>
       </c>
       <c r="H2514">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2514" t="inlineStr">
         <is>
@@ -95502,31 +95512,31 @@
     <row r="2515">
       <c r="A2515" t="inlineStr">
         <is>
-          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+          <t>Bharat Heavy Electricals Limited</t>
         </is>
       </c>
       <c r="B2515" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Quartz Powder</t>
         </is>
       </c>
       <c r="C2515">
-        <v>960654</v>
+        <v>298770</v>
       </c>
       <c r="D2515">
-        <v>186830.64</v>
+        <v>14938.5</v>
       </c>
       <c r="E2515">
-        <v>1224779</v>
+        <v>313709</v>
       </c>
       <c r="F2515">
-        <v>110.42</v>
+        <v>64.95</v>
       </c>
       <c r="G2515">
-        <v>8700</v>
+        <v>4600</v>
       </c>
       <c r="H2515">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2515" t="inlineStr">
         <is>
@@ -95540,7 +95550,7 @@
     <row r="2516">
       <c r="A2516" t="inlineStr">
         <is>
-          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+          <t>KAIRAV STEELS PVT LTD</t>
         </is>
       </c>
       <c r="B2516" t="inlineStr">
@@ -95549,26 +95559,26 @@
         </is>
       </c>
       <c r="C2516">
-        <v>735866</v>
+        <v>412137</v>
       </c>
       <c r="D2516">
-        <v>132455.88</v>
+        <v>87612.66</v>
       </c>
       <c r="E2516">
-        <v>868322</v>
+        <v>574350</v>
       </c>
       <c r="F2516">
-        <v>105.88</v>
+        <v>59.73</v>
       </c>
       <c r="G2516">
-        <v>6949.999999999999</v>
+        <v>6899.999999999999</v>
       </c>
       <c r="H2516">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2516" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Sunil Rathi</t>
         </is>
       </c>
       <c r="J2516" s="2">
@@ -95578,31 +95588,31 @@
     <row r="2517">
       <c r="A2517" t="inlineStr">
         <is>
-          <t>Arun Vyapar Udyog Private Limited</t>
+          <t>S.R. STEEL PVT LTD</t>
         </is>
       </c>
       <c r="B2517" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Ordinary Ramming Mass</t>
         </is>
       </c>
       <c r="C2517">
-        <v>934856</v>
+        <v>636412</v>
       </c>
       <c r="D2517">
-        <v>168274.08</v>
+        <v>0</v>
       </c>
       <c r="E2517">
-        <v>1103130</v>
+        <v>636412</v>
       </c>
       <c r="F2517">
-        <v>92.56</v>
+        <v>56</v>
       </c>
       <c r="G2517">
-        <v>10100</v>
+        <v>11364.5</v>
       </c>
       <c r="H2517">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2517" t="inlineStr">
         <is>
@@ -95616,31 +95626,31 @@
     <row r="2518">
       <c r="A2518" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+          <t>Shri Tirupati Steel Cast Ltd</t>
         </is>
       </c>
       <c r="B2518" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2518">
-        <v>787160</v>
+        <v>191268</v>
       </c>
       <c r="D2518">
-        <v>141688.8</v>
+        <v>34428.26</v>
       </c>
       <c r="E2518">
-        <v>928849</v>
+        <v>225696</v>
       </c>
       <c r="F2518">
-        <v>89.44999999999999</v>
+        <v>55.44</v>
       </c>
       <c r="G2518">
-        <v>8800.000000000002</v>
+        <v>3450</v>
       </c>
       <c r="H2518">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2518" t="inlineStr">
         <is>
@@ -95654,7 +95664,7 @@
     <row r="2519">
       <c r="A2519" t="inlineStr">
         <is>
-          <t>Prakash Ferrous Industries Pvt Ltd</t>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2519" t="inlineStr">
@@ -95663,26 +95673,26 @@
         </is>
       </c>
       <c r="C2519">
-        <v>674444</v>
+        <v>437871</v>
       </c>
       <c r="D2519">
-        <v>121399.92</v>
+        <v>78816.78</v>
       </c>
       <c r="E2519">
-        <v>795844</v>
+        <v>516688</v>
       </c>
       <c r="F2519">
-        <v>65.48</v>
+        <v>50.33</v>
       </c>
       <c r="G2519">
-        <v>10300</v>
+        <v>8700</v>
       </c>
       <c r="H2519">
         <v>2</v>
       </c>
       <c r="I2519" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2519" s="2">
@@ -95692,7 +95702,7 @@
     <row r="2520">
       <c r="A2520" t="inlineStr">
         <is>
-          <t>KANNAPPAN IRON AND STEEL COMPANY LIMITED</t>
+          <t>Kanishk Steel Industries Ltd</t>
         </is>
       </c>
       <c r="B2520" t="inlineStr">
@@ -95701,26 +95711,26 @@
         </is>
       </c>
       <c r="C2520">
-        <v>696891</v>
+        <v>466075</v>
       </c>
       <c r="D2520">
-        <v>125440.38</v>
+        <v>83893.5</v>
       </c>
       <c r="E2520">
-        <v>822331</v>
+        <v>549969</v>
       </c>
       <c r="F2520">
-        <v>65.13</v>
+        <v>45.25</v>
       </c>
       <c r="G2520">
-        <v>10700</v>
+        <v>10300</v>
       </c>
       <c r="H2520">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2520" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2520" s="2">
@@ -95730,7 +95740,7 @@
     <row r="2521">
       <c r="A2521" t="inlineStr">
         <is>
-          <t>Mahrishi Alloys Pvt. Ltd.</t>
+          <t>GBR Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2521" t="inlineStr">
@@ -95739,26 +95749,26 @@
         </is>
       </c>
       <c r="C2521">
-        <v>276292.5</v>
+        <v>460925</v>
       </c>
       <c r="D2521">
-        <v>49732.66</v>
+        <v>82966.5</v>
       </c>
       <c r="E2521">
-        <v>326025</v>
+        <v>543892</v>
       </c>
       <c r="F2521">
-        <v>65.01000000000001</v>
+        <v>44.75</v>
       </c>
       <c r="G2521">
-        <v>4250</v>
+        <v>10300</v>
       </c>
       <c r="H2521">
         <v>2</v>
       </c>
       <c r="I2521" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2521" s="2">
@@ -95768,28 +95778,25 @@
     <row r="2522">
       <c r="A2522" t="inlineStr">
         <is>
-          <t>TEXCON STEELS LIMITED</t>
+          <t>Adishakti Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2522" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2522">
-        <v>555750</v>
+        <v>152766</v>
       </c>
       <c r="D2522">
-        <v>100035</v>
-      </c>
-      <c r="E2522">
-        <v>655785</v>
+        <v>0</v>
       </c>
       <c r="F2522">
-        <v>65</v>
+        <v>44.28</v>
       </c>
       <c r="G2522">
-        <v>8550</v>
+        <v>3450</v>
       </c>
       <c r="H2522">
         <v>2</v>
@@ -95806,31 +95813,31 @@
     <row r="2523">
       <c r="A2523" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Limited</t>
+          <t>VRKP ISPAT PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2523" t="inlineStr">
         <is>
-          <t>Quartz Powder</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2523">
-        <v>298770</v>
+        <v>165702.5</v>
       </c>
       <c r="D2523">
-        <v>14938.5</v>
+        <v>29826.45</v>
       </c>
       <c r="E2523">
-        <v>313709</v>
+        <v>195529</v>
       </c>
       <c r="F2523">
-        <v>64.95</v>
+        <v>41.95</v>
       </c>
       <c r="G2523">
-        <v>4600</v>
+        <v>3950</v>
       </c>
       <c r="H2523">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2523" t="inlineStr">
         <is>
@@ -95844,35 +95851,35 @@
     <row r="2524">
       <c r="A2524" t="inlineStr">
         <is>
-          <t>KAIRAV STEELS PVT LTD</t>
+          <t>Keshree Metalurgies Pvt Ltd</t>
         </is>
       </c>
       <c r="B2524" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2524">
-        <v>412137</v>
+        <v>391296</v>
       </c>
       <c r="D2524">
-        <v>87612.66</v>
+        <v>70433.28</v>
       </c>
       <c r="E2524">
-        <v>574350</v>
+        <v>461729</v>
       </c>
       <c r="F2524">
-        <v>59.73</v>
+        <v>40.76000000000001</v>
       </c>
       <c r="G2524">
-        <v>6899.999999999999</v>
+        <v>9599.999999999998</v>
       </c>
       <c r="H2524">
         <v>2</v>
       </c>
       <c r="I2524" t="inlineStr">
         <is>
-          <t>Sunil Rathi</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2524" s="2">
@@ -95882,31 +95889,31 @@
     <row r="2525">
       <c r="A2525" t="inlineStr">
         <is>
-          <t>S.R. STEEL PVT LTD</t>
+          <t>Sree  Rengaraaj Steel &amp; Alloys (P) Limited</t>
         </is>
       </c>
       <c r="B2525" t="inlineStr">
         <is>
-          <t>Ordinary Ramming Mass</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2525">
-        <v>636412</v>
+        <v>409555</v>
       </c>
       <c r="D2525">
-        <v>0</v>
+        <v>73719.89999999999</v>
       </c>
       <c r="E2525">
-        <v>636412</v>
+        <v>483275</v>
       </c>
       <c r="F2525">
-        <v>56</v>
+        <v>40.55</v>
       </c>
       <c r="G2525">
-        <v>11364.5</v>
+        <v>10100</v>
       </c>
       <c r="H2525">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2525" t="inlineStr">
         <is>
@@ -95920,35 +95927,35 @@
     <row r="2526">
       <c r="A2526" t="inlineStr">
         <is>
-          <t>Shri Tirupati Steel Cast Ltd</t>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
         </is>
       </c>
       <c r="B2526" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2526">
-        <v>191268</v>
+        <v>347903</v>
       </c>
       <c r="D2526">
-        <v>34428.26</v>
+        <v>62622.54</v>
       </c>
       <c r="E2526">
-        <v>225696</v>
+        <v>410526</v>
       </c>
       <c r="F2526">
-        <v>55.44</v>
+        <v>40.22</v>
       </c>
       <c r="G2526">
-        <v>3450</v>
+        <v>8650</v>
       </c>
       <c r="H2526">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2526" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2526" s="2">
@@ -95958,7 +95965,7 @@
     <row r="2527">
       <c r="A2527" t="inlineStr">
         <is>
-          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+          <t>Sri M.S.T. Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2527" t="inlineStr">
@@ -95967,19 +95974,19 @@
         </is>
       </c>
       <c r="C2527">
-        <v>437871</v>
+        <v>346000</v>
       </c>
       <c r="D2527">
-        <v>78816.78</v>
+        <v>62280</v>
       </c>
       <c r="E2527">
-        <v>516688</v>
+        <v>408280</v>
       </c>
       <c r="F2527">
-        <v>50.33</v>
+        <v>40</v>
       </c>
       <c r="G2527">
-        <v>8700</v>
+        <v>8650</v>
       </c>
       <c r="H2527">
         <v>2</v>
@@ -95996,35 +96003,35 @@
     <row r="2528">
       <c r="A2528" t="inlineStr">
         <is>
-          <t>Kanishk Steel Industries Ltd</t>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
         </is>
       </c>
       <c r="B2528" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2528">
-        <v>466075</v>
+        <v>147482</v>
       </c>
       <c r="D2528">
-        <v>83893.5</v>
+        <v>26546.76</v>
       </c>
       <c r="E2528">
-        <v>549969</v>
+        <v>174029</v>
       </c>
       <c r="F2528">
-        <v>45.25</v>
+        <v>39.86</v>
       </c>
       <c r="G2528">
-        <v>10300</v>
+        <v>3700</v>
       </c>
       <c r="H2528">
         <v>2</v>
       </c>
       <c r="I2528" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2528" s="2">
@@ -96034,35 +96041,35 @@
     <row r="2529">
       <c r="A2529" t="inlineStr">
         <is>
-          <t>GBR Metals Pvt Ltd</t>
+          <t>BMM ISPAT LIMITED</t>
         </is>
       </c>
       <c r="B2529" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2529">
-        <v>460925</v>
+        <v>300263.5</v>
       </c>
       <c r="D2529">
-        <v>82966.5</v>
+        <v>54047.43</v>
       </c>
       <c r="E2529">
-        <v>543892</v>
+        <v>354311</v>
       </c>
       <c r="F2529">
-        <v>44.75</v>
+        <v>39.77</v>
       </c>
       <c r="G2529">
-        <v>10300</v>
+        <v>7549.999999999999</v>
       </c>
       <c r="H2529">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2529" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2529" s="2">
@@ -96072,32 +96079,35 @@
     <row r="2530">
       <c r="A2530" t="inlineStr">
         <is>
-          <t>Adishakti Smelters Private Limited</t>
+          <t>VMC Steel and Alloys Industry</t>
         </is>
       </c>
       <c r="B2530" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2530">
-        <v>152766</v>
+        <v>417585</v>
       </c>
       <c r="D2530">
-        <v>0</v>
+        <v>75165.3</v>
+      </c>
+      <c r="E2530">
+        <v>492751</v>
       </c>
       <c r="F2530">
-        <v>44.28</v>
+        <v>39.77</v>
       </c>
       <c r="G2530">
-        <v>3450</v>
+        <v>10500</v>
       </c>
       <c r="H2530">
         <v>2</v>
       </c>
       <c r="I2530" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2530" s="2">
@@ -96107,31 +96117,31 @@
     <row r="2531">
       <c r="A2531" t="inlineStr">
         <is>
-          <t>VRKP ISPAT PRIVATE LIMITED</t>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
         </is>
       </c>
       <c r="B2531" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2531">
-        <v>165702.5</v>
+        <v>347451</v>
       </c>
       <c r="D2531">
-        <v>29826.45</v>
+        <v>62541.18</v>
       </c>
       <c r="E2531">
-        <v>195529</v>
+        <v>409992</v>
       </c>
       <c r="F2531">
-        <v>41.95</v>
+        <v>39.26</v>
       </c>
       <c r="G2531">
-        <v>3950</v>
+        <v>8850</v>
       </c>
       <c r="H2531">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2531" t="inlineStr">
         <is>
@@ -96145,35 +96155,35 @@
     <row r="2532">
       <c r="A2532" t="inlineStr">
         <is>
-          <t>Keshree Metalurgies Pvt Ltd</t>
+          <t>SREE PALANIANDAVAR ALLOYS AND STEELS PVT LTD</t>
         </is>
       </c>
       <c r="B2532" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2532">
-        <v>391296</v>
+        <v>246725</v>
       </c>
       <c r="D2532">
-        <v>70433.28</v>
+        <v>44410.5</v>
       </c>
       <c r="E2532">
-        <v>461729</v>
+        <v>291136</v>
       </c>
       <c r="F2532">
-        <v>40.76000000000001</v>
+        <v>35.5</v>
       </c>
       <c r="G2532">
-        <v>9599.999999999998</v>
+        <v>6950</v>
       </c>
       <c r="H2532">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2532" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2532" s="2">
@@ -96183,35 +96193,35 @@
     <row r="2533">
       <c r="A2533" t="inlineStr">
         <is>
-          <t>Sree  Rengaraaj Steel &amp; Alloys (P) Limited</t>
+          <t>M.A.STEELS (P) LTD</t>
         </is>
       </c>
       <c r="B2533" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2533">
-        <v>409555</v>
+        <v>245682.5</v>
       </c>
       <c r="D2533">
-        <v>73719.89999999999</v>
+        <v>44222.85</v>
       </c>
       <c r="E2533">
-        <v>483275</v>
+        <v>289905</v>
       </c>
       <c r="F2533">
-        <v>40.55</v>
+        <v>35.35</v>
       </c>
       <c r="G2533">
-        <v>10100</v>
+        <v>6950</v>
       </c>
       <c r="H2533">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2533" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2533" s="2">
@@ -96221,35 +96231,35 @@
     <row r="2534">
       <c r="A2534" t="inlineStr">
         <is>
-          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+          <t>PARAGON STEEL DISTRIBUITORS</t>
         </is>
       </c>
       <c r="B2534" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2534">
-        <v>347903</v>
+        <v>238612</v>
       </c>
       <c r="D2534">
-        <v>62622.54</v>
+        <v>42950.16</v>
       </c>
       <c r="E2534">
-        <v>410526</v>
+        <v>281562</v>
       </c>
       <c r="F2534">
-        <v>40.22</v>
+        <v>35.09</v>
       </c>
       <c r="G2534">
-        <v>8650</v>
+        <v>6799.999999999999</v>
       </c>
       <c r="H2534">
         <v>1</v>
       </c>
       <c r="I2534" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2534" s="2">
@@ -96259,31 +96269,31 @@
     <row r="2535">
       <c r="A2535" t="inlineStr">
         <is>
-          <t>Sri M.S.T. Smelters Private Limited</t>
+          <t>Pattambi Brothers</t>
         </is>
       </c>
       <c r="B2535" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2535">
-        <v>346000</v>
+        <v>243667</v>
       </c>
       <c r="D2535">
-        <v>62280</v>
+        <v>43860.06</v>
       </c>
       <c r="E2535">
-        <v>408280</v>
+        <v>287527</v>
       </c>
       <c r="F2535">
-        <v>40</v>
+        <v>35.06</v>
       </c>
       <c r="G2535">
-        <v>8650</v>
+        <v>6950</v>
       </c>
       <c r="H2535">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2535" t="inlineStr">
         <is>
@@ -96297,7 +96307,7 @@
     <row r="2536">
       <c r="A2536" t="inlineStr">
         <is>
-          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
         </is>
       </c>
       <c r="B2536" t="inlineStr">
@@ -96306,19 +96316,19 @@
         </is>
       </c>
       <c r="C2536">
-        <v>147482</v>
+        <v>142229</v>
       </c>
       <c r="D2536">
-        <v>26546.76</v>
+        <v>25601.22</v>
       </c>
       <c r="E2536">
-        <v>174029</v>
+        <v>167830</v>
       </c>
       <c r="F2536">
-        <v>39.86</v>
+        <v>34.69</v>
       </c>
       <c r="G2536">
-        <v>3700</v>
+        <v>4100</v>
       </c>
       <c r="H2536">
         <v>2</v>
@@ -96335,7 +96345,7 @@
     <row r="2537">
       <c r="A2537" t="inlineStr">
         <is>
-          <t>BMM ISPAT LIMITED</t>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
         </is>
       </c>
       <c r="B2537" t="inlineStr">
@@ -96344,19 +96354,19 @@
         </is>
       </c>
       <c r="C2537">
-        <v>300263.5</v>
+        <v>260173</v>
       </c>
       <c r="D2537">
-        <v>54047.43</v>
+        <v>46831.14</v>
       </c>
       <c r="E2537">
-        <v>354311</v>
+        <v>307004</v>
       </c>
       <c r="F2537">
-        <v>39.77</v>
+        <v>34.46</v>
       </c>
       <c r="G2537">
-        <v>7549.999999999999</v>
+        <v>7550</v>
       </c>
       <c r="H2537">
         <v>1</v>
@@ -96373,35 +96383,35 @@
     <row r="2538">
       <c r="A2538" t="inlineStr">
         <is>
-          <t>VMC Steel and Alloys Industry</t>
+          <t>RELIANCE CONCAST SOLUTIONS</t>
         </is>
       </c>
       <c r="B2538" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Quartz Powder</t>
         </is>
       </c>
       <c r="C2538">
-        <v>417585</v>
+        <v>108452.5</v>
       </c>
       <c r="D2538">
-        <v>75165.3</v>
+        <v>5422.63</v>
       </c>
       <c r="E2538">
-        <v>492751</v>
+        <v>113875</v>
       </c>
       <c r="F2538">
-        <v>39.77</v>
+        <v>33.37</v>
       </c>
       <c r="G2538">
-        <v>10500</v>
+        <v>3250</v>
       </c>
       <c r="H2538">
         <v>2</v>
       </c>
       <c r="I2538" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2538" s="2">
@@ -96411,35 +96421,35 @@
     <row r="2539">
       <c r="A2539" t="inlineStr">
         <is>
-          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
         </is>
       </c>
       <c r="B2539" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2539">
-        <v>347451</v>
+        <v>176599.5</v>
       </c>
       <c r="D2539">
-        <v>62541.18</v>
+        <v>31787.91</v>
       </c>
       <c r="E2539">
-        <v>409992</v>
+        <v>208388</v>
       </c>
       <c r="F2539">
-        <v>39.26</v>
+        <v>25.41</v>
       </c>
       <c r="G2539">
-        <v>8850</v>
+        <v>6950</v>
       </c>
       <c r="H2539">
         <v>1</v>
       </c>
       <c r="I2539" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2539" s="2">
@@ -96449,35 +96459,35 @@
     <row r="2540">
       <c r="A2540" t="inlineStr">
         <is>
-          <t>SREE PALANIANDAVAR ALLOYS AND STEELS PVT LTD</t>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
         </is>
       </c>
       <c r="B2540" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2540">
-        <v>246725</v>
+        <v>92199</v>
       </c>
       <c r="D2540">
-        <v>44410.5</v>
+        <v>16595.82</v>
       </c>
       <c r="E2540">
-        <v>291136</v>
+        <v>108795</v>
       </c>
       <c r="F2540">
-        <v>35.5</v>
+        <v>25.26</v>
       </c>
       <c r="G2540">
-        <v>6950</v>
+        <v>3650</v>
       </c>
       <c r="H2540">
         <v>1</v>
       </c>
       <c r="I2540" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2540" s="2">
@@ -96487,35 +96497,35 @@
     <row r="2541">
       <c r="A2541" t="inlineStr">
         <is>
-          <t>M.A.STEELS (P) LTD</t>
+          <t>ADRI STEEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2541" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2541">
-        <v>245682.5</v>
+        <v>220937.5</v>
       </c>
       <c r="D2541">
-        <v>44222.85</v>
+        <v>39768.76</v>
       </c>
       <c r="E2541">
-        <v>289905</v>
+        <v>260706</v>
       </c>
       <c r="F2541">
-        <v>35.35</v>
+        <v>25.25</v>
       </c>
       <c r="G2541">
-        <v>6950</v>
+        <v>8750</v>
       </c>
       <c r="H2541">
         <v>1</v>
       </c>
       <c r="I2541" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2541" s="2">
@@ -96525,35 +96535,35 @@
     <row r="2542">
       <c r="A2542" t="inlineStr">
         <is>
-          <t>PARAGON STEEL DISTRIBUITORS</t>
+          <t>BLUE GOLD STEEL INDUSTRIES</t>
         </is>
       </c>
       <c r="B2542" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2542">
-        <v>238612</v>
+        <v>220150</v>
       </c>
       <c r="D2542">
-        <v>42950.16</v>
+        <v>39627</v>
       </c>
       <c r="E2542">
-        <v>281562</v>
+        <v>259777</v>
       </c>
       <c r="F2542">
-        <v>35.09</v>
+        <v>25.16</v>
       </c>
       <c r="G2542">
-        <v>6799.999999999999</v>
+        <v>8750</v>
       </c>
       <c r="H2542">
         <v>1</v>
       </c>
       <c r="I2542" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2542" s="2">
@@ -96563,7 +96573,7 @@
     <row r="2543">
       <c r="A2543" t="inlineStr">
         <is>
-          <t>Pattambi Brothers</t>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2543" t="inlineStr">
@@ -96572,26 +96582,23 @@
         </is>
       </c>
       <c r="C2543">
-        <v>243667</v>
+        <v>184970.5</v>
       </c>
       <c r="D2543">
-        <v>43860.06</v>
-      </c>
-      <c r="E2543">
-        <v>287527</v>
+        <v>0</v>
       </c>
       <c r="F2543">
-        <v>35.06</v>
+        <v>21.89</v>
       </c>
       <c r="G2543">
-        <v>6950</v>
+        <v>8450</v>
       </c>
       <c r="H2543">
         <v>1</v>
       </c>
       <c r="I2543" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2543" s="2">
@@ -96601,35 +96608,35 @@
     <row r="2544">
       <c r="A2544" t="inlineStr">
         <is>
-          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2544" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Tundish Ramming Mix</t>
         </is>
       </c>
       <c r="C2544">
-        <v>142229</v>
+        <v>575100</v>
       </c>
       <c r="D2544">
-        <v>25601.22</v>
+        <v>103518</v>
       </c>
       <c r="E2544">
-        <v>167830</v>
+        <v>678618</v>
       </c>
       <c r="F2544">
-        <v>34.69</v>
+        <v>21.3</v>
       </c>
       <c r="G2544">
-        <v>4100</v>
+        <v>27000</v>
       </c>
       <c r="H2544">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2544" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2544" s="2">
@@ -96639,7 +96646,7 @@
     <row r="2545">
       <c r="A2545" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2545" t="inlineStr">
@@ -96648,26 +96655,26 @@
         </is>
       </c>
       <c r="C2545">
-        <v>260173</v>
+        <v>142695</v>
       </c>
       <c r="D2545">
-        <v>46831.14</v>
+        <v>25685.09999999999</v>
       </c>
       <c r="E2545">
-        <v>307004</v>
+        <v>168380.1</v>
       </c>
       <c r="F2545">
-        <v>34.46</v>
+        <v>21.14</v>
       </c>
       <c r="G2545">
-        <v>7550</v>
+        <v>6750.000000000001</v>
       </c>
       <c r="H2545">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2545" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2545" s="2">
@@ -96677,28 +96684,28 @@
     <row r="2546">
       <c r="A2546" t="inlineStr">
         <is>
-          <t>RELIANCE CONCAST SOLUTIONS</t>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2546" t="inlineStr">
         <is>
-          <t>Quartz Powder</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2546">
-        <v>108452.5</v>
+        <v>64896</v>
       </c>
       <c r="D2546">
-        <v>5422.63</v>
+        <v>11681.28</v>
       </c>
       <c r="E2546">
-        <v>113875</v>
+        <v>76577</v>
       </c>
       <c r="F2546">
-        <v>33.37</v>
+        <v>20.28</v>
       </c>
       <c r="G2546">
-        <v>3250</v>
+        <v>3200</v>
       </c>
       <c r="H2546">
         <v>2</v>
@@ -96715,7 +96722,7 @@
     <row r="2547">
       <c r="A2547" t="inlineStr">
         <is>
-          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+          <t>SNAM ALLOYS PVT LTD</t>
         </is>
       </c>
       <c r="B2547" t="inlineStr">
@@ -96724,26 +96731,26 @@
         </is>
       </c>
       <c r="C2547">
-        <v>176599.5</v>
+        <v>166380.5</v>
       </c>
       <c r="D2547">
-        <v>31787.91</v>
+        <v>29948.49</v>
       </c>
       <c r="E2547">
-        <v>208388</v>
+        <v>196329</v>
       </c>
       <c r="F2547">
-        <v>25.41</v>
+        <v>19.69</v>
       </c>
       <c r="G2547">
-        <v>6950</v>
+        <v>8450</v>
       </c>
       <c r="H2547">
         <v>1</v>
       </c>
       <c r="I2547" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2547" s="2">
@@ -96753,7 +96760,7 @@
     <row r="2548">
       <c r="A2548" t="inlineStr">
         <is>
-          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+          <t>KAIRAV STEELS PVT LTD</t>
         </is>
       </c>
       <c r="B2548" t="inlineStr">
@@ -96762,26 +96769,23 @@
         </is>
       </c>
       <c r="C2548">
-        <v>92199</v>
+        <v>53584</v>
       </c>
       <c r="D2548">
-        <v>16595.82</v>
-      </c>
-      <c r="E2548">
-        <v>108795</v>
+        <v>8399.52</v>
       </c>
       <c r="F2548">
-        <v>25.26</v>
+        <v>15.76</v>
       </c>
       <c r="G2548">
-        <v>3650</v>
+        <v>3400</v>
       </c>
       <c r="H2548">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2548" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Sunil Rathi</t>
         </is>
       </c>
       <c r="J2548" s="2">
@@ -96791,7 +96795,7 @@
     <row r="2549">
       <c r="A2549" t="inlineStr">
         <is>
-          <t>ADRI STEEL PRIVATE LIMITED</t>
+          <t>SRI LAXMI GANESH MINERALS UNIT - II</t>
         </is>
       </c>
       <c r="B2549" t="inlineStr">
@@ -96800,19 +96804,19 @@
         </is>
       </c>
       <c r="C2549">
-        <v>220937.5</v>
+        <v>2139500</v>
       </c>
       <c r="D2549">
-        <v>39768.76</v>
+        <v>385110</v>
       </c>
       <c r="E2549">
-        <v>260706</v>
+        <v>2524610</v>
       </c>
       <c r="F2549">
-        <v>25.25</v>
+        <v>5.5</v>
       </c>
       <c r="G2549">
-        <v>8750</v>
+        <v>389000</v>
       </c>
       <c r="H2549">
         <v>1</v>
@@ -96829,7 +96833,7 @@
     <row r="2550">
       <c r="A2550" t="inlineStr">
         <is>
-          <t>BLUE GOLD STEEL INDUSTRIES</t>
+          <t>SRI BHAVANI CASTINGS LTD</t>
         </is>
       </c>
       <c r="B2550" t="inlineStr">
@@ -96838,26 +96842,26 @@
         </is>
       </c>
       <c r="C2550">
-        <v>220150</v>
+        <v>36800</v>
       </c>
       <c r="D2550">
-        <v>39627</v>
+        <v>6624</v>
       </c>
       <c r="E2550">
-        <v>259777</v>
+        <v>43424</v>
       </c>
       <c r="F2550">
-        <v>25.16</v>
+        <v>4</v>
       </c>
       <c r="G2550">
-        <v>8750</v>
+        <v>9200</v>
       </c>
       <c r="H2550">
         <v>1</v>
       </c>
       <c r="I2550" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2550" s="2">
@@ -96867,28 +96871,31 @@
     <row r="2551">
       <c r="A2551" t="inlineStr">
         <is>
-          <t>SNAM ALLOYS PRIVATE LIMITED</t>
+          <t>SARCH ALLOY CASTINGS</t>
         </is>
       </c>
       <c r="B2551" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Scrap</t>
         </is>
       </c>
       <c r="C2551">
-        <v>184970.5</v>
+        <v>325900</v>
       </c>
       <c r="D2551">
-        <v>0</v>
+        <v>58662</v>
+      </c>
+      <c r="E2551">
+        <v>385774</v>
       </c>
       <c r="F2551">
-        <v>21.89</v>
+        <v>3.02</v>
       </c>
       <c r="G2551">
-        <v>8450</v>
+        <v>107913.9072847682</v>
       </c>
       <c r="H2551">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2551" t="inlineStr">
         <is>
@@ -96902,35 +96909,35 @@
     <row r="2552">
       <c r="A2552" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2552" t="inlineStr">
         <is>
-          <t>Tundish Ramming Mix</t>
+          <t>Ordinary Ramming Mass</t>
         </is>
       </c>
       <c r="C2552">
-        <v>575100</v>
+        <v>14850</v>
       </c>
       <c r="D2552">
-        <v>103518</v>
+        <v>35967.7</v>
       </c>
       <c r="E2552">
-        <v>678618</v>
+        <v>235788</v>
       </c>
       <c r="F2552">
-        <v>21.3</v>
+        <v>3</v>
       </c>
       <c r="G2552">
-        <v>27000</v>
+        <v>4950</v>
       </c>
       <c r="H2552">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2552" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2552" s="2">
@@ -96940,69 +96947,69 @@
     <row r="2553">
       <c r="A2553" t="inlineStr">
         <is>
-          <t>ILC IRON &amp; STEEL PRIVATE LIMITED</t>
+          <t>A One Ispat Private Ltd</t>
         </is>
       </c>
       <c r="B2553" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2553">
-        <v>142695</v>
+        <v>2997837.5</v>
       </c>
       <c r="D2553">
-        <v>25685.09999999999</v>
+        <v>539610.8200000001</v>
       </c>
       <c r="E2553">
-        <v>168380.1</v>
+        <v>3537450</v>
       </c>
       <c r="F2553">
-        <v>21.14</v>
+        <v>342.61</v>
       </c>
       <c r="G2553">
-        <v>6750.000000000001</v>
+        <v>8750.000000000002</v>
       </c>
       <c r="H2553">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2553" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2553" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2554">
       <c r="A2554" t="inlineStr">
         <is>
-          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
         </is>
       </c>
       <c r="B2554" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2554">
-        <v>64896</v>
+        <v>2459237</v>
       </c>
       <c r="D2554">
-        <v>11681.28</v>
+        <v>442662.66</v>
       </c>
       <c r="E2554">
-        <v>76577</v>
+        <v>2901900</v>
       </c>
       <c r="F2554">
-        <v>20.28</v>
+        <v>263.02</v>
       </c>
       <c r="G2554">
-        <v>3200</v>
+        <v>9350</v>
       </c>
       <c r="H2554">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I2554" t="inlineStr">
         <is>
@@ -97010,86 +97017,89 @@
         </is>
       </c>
       <c r="J2554" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2555">
       <c r="A2555" t="inlineStr">
         <is>
-          <t>SNAM ALLOYS PVT LTD</t>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
         </is>
       </c>
       <c r="B2555" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2555">
-        <v>166380.5</v>
+        <v>1710536</v>
       </c>
       <c r="D2555">
-        <v>29948.49</v>
+        <v>307896.48</v>
       </c>
       <c r="E2555">
-        <v>196329</v>
+        <v>2018433</v>
       </c>
       <c r="F2555">
-        <v>19.69</v>
+        <v>169.36</v>
       </c>
       <c r="G2555">
-        <v>8450</v>
+        <v>10100</v>
       </c>
       <c r="H2555">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2555" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2555" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2556">
       <c r="A2556" t="inlineStr">
         <is>
-          <t>KAIRAV STEELS PVT LTD</t>
+          <t>Pushpit Steels Private Limited</t>
         </is>
       </c>
       <c r="B2556" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2556">
-        <v>53584</v>
+        <v>1492151</v>
       </c>
       <c r="D2556">
-        <v>8399.52</v>
+        <v>268587.18</v>
+      </c>
+      <c r="E2556">
+        <v>1760737</v>
       </c>
       <c r="F2556">
-        <v>15.76</v>
+        <v>153.83</v>
       </c>
       <c r="G2556">
-        <v>3400</v>
+        <v>9700</v>
       </c>
       <c r="H2556">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I2556" t="inlineStr">
         <is>
-          <t>Sunil Rathi</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2556" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2557">
       <c r="A2557" t="inlineStr">
         <is>
-          <t>SRI LAXMI GANESH MINERALS UNIT - II</t>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2557" t="inlineStr">
@@ -97098,22 +97108,22 @@
         </is>
       </c>
       <c r="C2557">
-        <v>2139500</v>
+        <v>1258716</v>
       </c>
       <c r="D2557">
-        <v>385110</v>
+        <v>244798.56</v>
       </c>
       <c r="E2557">
-        <v>2524610</v>
+        <v>1604792</v>
       </c>
       <c r="F2557">
-        <v>5.5</v>
+        <v>144.68</v>
       </c>
       <c r="G2557">
-        <v>389000</v>
+        <v>8700</v>
       </c>
       <c r="H2557">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2557" t="inlineStr">
         <is>
@@ -97121,13 +97131,13 @@
         </is>
       </c>
       <c r="J2557" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2558">
       <c r="A2558" t="inlineStr">
         <is>
-          <t>SRI BHAVANI CASTINGS LTD</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2558" t="inlineStr">
@@ -97136,60 +97146,60 @@
         </is>
       </c>
       <c r="C2558">
-        <v>36800</v>
+        <v>1322781</v>
       </c>
       <c r="D2558">
-        <v>6624</v>
+        <v>238100.58</v>
       </c>
       <c r="E2558">
-        <v>43424</v>
+        <v>1560881</v>
       </c>
       <c r="F2558">
-        <v>4</v>
+        <v>131.62</v>
       </c>
       <c r="G2558">
-        <v>9200</v>
+        <v>10050</v>
       </c>
       <c r="H2558">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2558" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2558" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2559">
       <c r="A2559" t="inlineStr">
         <is>
-          <t>SARCH ALLOY CASTINGS</t>
+          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
         </is>
       </c>
       <c r="B2559" t="inlineStr">
         <is>
-          <t>Scrap</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2559">
-        <v>325900</v>
+        <v>1071381</v>
       </c>
       <c r="D2559">
-        <v>58662</v>
+        <v>192848.58</v>
       </c>
       <c r="E2559">
-        <v>385774</v>
+        <v>1264230</v>
       </c>
       <c r="F2559">
-        <v>3.02</v>
+        <v>121.06</v>
       </c>
       <c r="G2559">
-        <v>107913.9072847682</v>
+        <v>8850</v>
       </c>
       <c r="H2559">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2559" t="inlineStr">
         <is>
@@ -97197,45 +97207,1960 @@
         </is>
       </c>
       <c r="J2559" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2560">
       <c r="A2560" t="inlineStr">
         <is>
-          <t>SNAM ALLOYS PRIVATE LIMITED</t>
+          <t>Adishakti Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2560" t="inlineStr">
         <is>
-          <t>Ordinary Ramming Mass</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2560">
-        <v>14850</v>
+        <v>1040112.5</v>
       </c>
       <c r="D2560">
-        <v>35967.7</v>
+        <v>210954.92</v>
       </c>
       <c r="E2560">
-        <v>235788</v>
+        <v>1382926</v>
       </c>
       <c r="F2560">
+        <v>118.87</v>
+      </c>
+      <c r="G2560">
+        <v>8750</v>
+      </c>
+      <c r="H2560">
+        <v>5</v>
+      </c>
+      <c r="I2560" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2560" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="inlineStr">
+        <is>
+          <t>Arun Vyapar Udyog Private Limited</t>
+        </is>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2561">
+        <v>1170590</v>
+      </c>
+      <c r="D2561">
+        <v>210706.2</v>
+      </c>
+      <c r="E2561">
+        <v>1381296</v>
+      </c>
+      <c r="F2561">
+        <v>115.9</v>
+      </c>
+      <c r="G2561">
+        <v>10100</v>
+      </c>
+      <c r="H2561">
+        <v>5</v>
+      </c>
+      <c r="I2561" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2561" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2562">
+        <v>381412</v>
+      </c>
+      <c r="D2562">
+        <v>68654.16</v>
+      </c>
+      <c r="E2562">
+        <v>450066</v>
+      </c>
+      <c r="F2562">
+        <v>112.18</v>
+      </c>
+      <c r="G2562">
+        <v>3400</v>
+      </c>
+      <c r="H2562">
         <v>3</v>
       </c>
-      <c r="G2560">
+      <c r="I2562" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2562" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2563">
+        <v>967243</v>
+      </c>
+      <c r="D2563">
+        <v>174103.76</v>
+      </c>
+      <c r="E2563">
+        <v>1141347</v>
+      </c>
+      <c r="F2563">
+        <v>111.82</v>
+      </c>
+      <c r="G2563">
+        <v>8650</v>
+      </c>
+      <c r="H2563">
+        <v>3</v>
+      </c>
+      <c r="I2563" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2563" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" t="inlineStr">
+        <is>
+          <t>Meenakshi Udyog India Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2564">
+        <v>1089075</v>
+      </c>
+      <c r="D2564">
+        <v>196033.5</v>
+      </c>
+      <c r="E2564">
+        <v>1285109</v>
+      </c>
+      <c r="F2564">
+        <v>111.7</v>
+      </c>
+      <c r="G2564">
+        <v>9750</v>
+      </c>
+      <c r="H2564">
+        <v>6</v>
+      </c>
+      <c r="I2564" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2564" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="inlineStr">
+        <is>
+          <t>KUBAIR STEEL AND POWER LLP</t>
+        </is>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2565">
+        <v>964561.5</v>
+      </c>
+      <c r="D2565">
+        <v>173621.08</v>
+      </c>
+      <c r="E2565">
+        <v>1138183</v>
+      </c>
+      <c r="F2565">
+        <v>108.99</v>
+      </c>
+      <c r="G2565">
+        <v>8850</v>
+      </c>
+      <c r="H2565">
+        <v>3</v>
+      </c>
+      <c r="I2565" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2565" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2566" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2566">
+        <v>453640</v>
+      </c>
+      <c r="D2566">
+        <v>81655.2</v>
+      </c>
+      <c r="E2566">
+        <v>535296</v>
+      </c>
+      <c r="F2566">
+        <v>103.1</v>
+      </c>
+      <c r="G2566">
+        <v>4400</v>
+      </c>
+      <c r="H2566">
+        <v>5</v>
+      </c>
+      <c r="I2566" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2566" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="inlineStr">
+        <is>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+        </is>
+      </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2567">
+        <v>810660</v>
+      </c>
+      <c r="D2567">
+        <v>145918.84</v>
+      </c>
+      <c r="E2567">
+        <v>956579</v>
+      </c>
+      <c r="F2567">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="G2567">
+        <v>8850</v>
+      </c>
+      <c r="H2567">
+        <v>4</v>
+      </c>
+      <c r="I2567" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2567" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+        </is>
+      </c>
+      <c r="B2568" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2568">
+        <v>794200</v>
+      </c>
+      <c r="D2568">
+        <v>142956</v>
+      </c>
+      <c r="E2568">
+        <v>937156</v>
+      </c>
+      <c r="F2568">
+        <v>90.25</v>
+      </c>
+      <c r="G2568">
+        <v>8800</v>
+      </c>
+      <c r="H2568">
+        <v>2</v>
+      </c>
+      <c r="I2568" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2568" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" t="inlineStr">
+        <is>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+        </is>
+      </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2569">
+        <v>785664</v>
+      </c>
+      <c r="D2569">
+        <v>141419.52</v>
+      </c>
+      <c r="E2569">
+        <v>927083</v>
+      </c>
+      <c r="F2569">
+        <v>89.28</v>
+      </c>
+      <c r="G2569">
+        <v>8800</v>
+      </c>
+      <c r="H2569">
+        <v>2</v>
+      </c>
+      <c r="I2569" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2569" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" t="inlineStr">
+        <is>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+        </is>
+      </c>
+      <c r="B2570" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2570">
+        <v>743640.5</v>
+      </c>
+      <c r="D2570">
+        <v>133855.29</v>
+      </c>
+      <c r="E2570">
+        <v>877496</v>
+      </c>
+      <c r="F2570">
+        <v>85.97</v>
+      </c>
+      <c r="G2570">
+        <v>8650</v>
+      </c>
+      <c r="H2570">
+        <v>2</v>
+      </c>
+      <c r="I2570" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2570" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="inlineStr">
+        <is>
+          <t>Shri Tirupati Steel Cast Ltd</t>
+        </is>
+      </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2571">
+        <v>284590.5</v>
+      </c>
+      <c r="D2571">
+        <v>51226.32</v>
+      </c>
+      <c r="E2571">
+        <v>335816</v>
+      </c>
+      <c r="F2571">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="G2571">
+        <v>3450</v>
+      </c>
+      <c r="H2571">
+        <v>5</v>
+      </c>
+      <c r="I2571" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2571" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" t="inlineStr">
+        <is>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+        </is>
+      </c>
+      <c r="B2572" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2572">
+        <v>696910.5</v>
+      </c>
+      <c r="D2572">
+        <v>125443.89</v>
+      </c>
+      <c r="E2572">
+        <v>822355</v>
+      </c>
+      <c r="F2572">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="G2572">
+        <v>8550</v>
+      </c>
+      <c r="H2572">
+        <v>4</v>
+      </c>
+      <c r="I2572" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2572" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="inlineStr">
+        <is>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2573">
+        <v>503887</v>
+      </c>
+      <c r="D2573">
+        <v>90699.66</v>
+      </c>
+      <c r="E2573">
+        <v>594587</v>
+      </c>
+      <c r="F2573">
+        <v>70.97</v>
+      </c>
+      <c r="G2573">
+        <v>7100</v>
+      </c>
+      <c r="H2573">
+        <v>2</v>
+      </c>
+      <c r="I2573" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2573" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" t="inlineStr">
+        <is>
+          <t>E RAMAMURTHY MINERALS AND METALS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2574" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2574">
+        <v>546880.5</v>
+      </c>
+      <c r="D2574">
+        <v>98438.48999999999</v>
+      </c>
+      <c r="E2574">
+        <v>645319</v>
+      </c>
+      <c r="F2574">
+        <v>68.78999999999999</v>
+      </c>
+      <c r="G2574">
+        <v>7950.000000000001</v>
+      </c>
+      <c r="H2574">
+        <v>2</v>
+      </c>
+      <c r="I2574" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2574" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="inlineStr">
+        <is>
+          <t>TEXCON STEELS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2575">
+        <v>565069.5</v>
+      </c>
+      <c r="D2575">
+        <v>101712.51</v>
+      </c>
+      <c r="E2575">
+        <v>666783</v>
+      </c>
+      <c r="F2575">
+        <v>66.09</v>
+      </c>
+      <c r="G2575">
+        <v>8550</v>
+      </c>
+      <c r="H2575">
+        <v>2</v>
+      </c>
+      <c r="I2575" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2575" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="inlineStr">
+        <is>
+          <t>KAIRAV STEELS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2576" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2576">
+        <v>414483</v>
+      </c>
+      <c r="D2576">
+        <v>100002.02</v>
+      </c>
+      <c r="E2576">
+        <v>655569</v>
+      </c>
+      <c r="F2576">
+        <v>60.07</v>
+      </c>
+      <c r="G2576">
+        <v>6900</v>
+      </c>
+      <c r="H2576">
+        <v>3</v>
+      </c>
+      <c r="I2576" t="inlineStr">
+        <is>
+          <t>Sunil Rathi</t>
+        </is>
+      </c>
+      <c r="J2576" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="inlineStr">
+        <is>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2577">
+        <v>429345</v>
+      </c>
+      <c r="D2577">
+        <v>78585.66</v>
+      </c>
+      <c r="E2577">
+        <v>515173</v>
+      </c>
+      <c r="F2577">
+        <v>49.35</v>
+      </c>
+      <c r="G2577">
+        <v>8700</v>
+      </c>
+      <c r="H2577">
+        <v>2</v>
+      </c>
+      <c r="I2577" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2577" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" t="inlineStr">
+        <is>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2578" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2578">
+        <v>402120</v>
+      </c>
+      <c r="D2578">
+        <v>72381.60000000001</v>
+      </c>
+      <c r="E2578">
+        <v>474502</v>
+      </c>
+      <c r="F2578">
+        <v>44.68000000000001</v>
+      </c>
+      <c r="G2578">
+        <v>8999.999999999998</v>
+      </c>
+      <c r="H2578">
+        <v>2</v>
+      </c>
+      <c r="I2578" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2578" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="inlineStr">
+        <is>
+          <t>Keshree Metalurgies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2579">
+        <v>402240</v>
+      </c>
+      <c r="D2579">
+        <v>72403.2</v>
+      </c>
+      <c r="E2579">
+        <v>474644</v>
+      </c>
+      <c r="F2579">
+        <v>41.9</v>
+      </c>
+      <c r="G2579">
+        <v>9600</v>
+      </c>
+      <c r="H2579">
+        <v>2</v>
+      </c>
+      <c r="I2579" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2579" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" t="inlineStr">
+        <is>
+          <t>Sri M.S.T. Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2580" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2580">
+        <v>346951.5</v>
+      </c>
+      <c r="D2580">
+        <v>62451.27</v>
+      </c>
+      <c r="E2580">
+        <v>409403</v>
+      </c>
+      <c r="F2580">
+        <v>40.11</v>
+      </c>
+      <c r="G2580">
+        <v>8650</v>
+      </c>
+      <c r="H2580">
+        <v>2</v>
+      </c>
+      <c r="I2580" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2580" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" t="inlineStr">
+        <is>
+          <t>INDUS TMT INDUSTRIES LTD.</t>
+        </is>
+      </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2581">
+        <v>388291</v>
+      </c>
+      <c r="D2581">
+        <v>69892.38</v>
+      </c>
+      <c r="E2581">
+        <v>458184</v>
+      </c>
+      <c r="F2581">
+        <v>40.03</v>
+      </c>
+      <c r="G2581">
+        <v>9700</v>
+      </c>
+      <c r="H2581">
+        <v>2</v>
+      </c>
+      <c r="I2581" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2581" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" t="inlineStr">
+        <is>
+          <t>Mahrishi Alloys Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B2582" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2582">
+        <v>168895</v>
+      </c>
+      <c r="D2582">
+        <v>30401.1</v>
+      </c>
+      <c r="E2582">
+        <v>199296</v>
+      </c>
+      <c r="F2582">
+        <v>39.74</v>
+      </c>
+      <c r="G2582">
+        <v>4250</v>
+      </c>
+      <c r="H2582">
+        <v>1</v>
+      </c>
+      <c r="I2582" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2582" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" t="inlineStr">
+        <is>
+          <t>Adishakti Smelters Private Limited</t>
+        </is>
+      </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2583">
+        <v>131859</v>
+      </c>
+      <c r="D2583">
+        <v>0</v>
+      </c>
+      <c r="F2583">
+        <v>38.22</v>
+      </c>
+      <c r="G2583">
+        <v>3450</v>
+      </c>
+      <c r="H2583">
+        <v>3</v>
+      </c>
+      <c r="I2583" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2583" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" t="inlineStr">
+        <is>
+          <t>M.A.STEELS (P) LTD</t>
+        </is>
+      </c>
+      <c r="B2584" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2584">
+        <v>246169</v>
+      </c>
+      <c r="D2584">
+        <v>44310.42</v>
+      </c>
+      <c r="E2584">
+        <v>290479</v>
+      </c>
+      <c r="F2584">
+        <v>35.42</v>
+      </c>
+      <c r="G2584">
+        <v>6950</v>
+      </c>
+      <c r="H2584">
+        <v>2</v>
+      </c>
+      <c r="I2584" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2584" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" t="inlineStr">
+        <is>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2585" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2585">
+        <v>113088</v>
+      </c>
+      <c r="D2585">
+        <v>24808.68</v>
+      </c>
+      <c r="E2585">
+        <v>162635</v>
+      </c>
+      <c r="F2585">
+        <v>35.34</v>
+      </c>
+      <c r="G2585">
+        <v>3200</v>
+      </c>
+      <c r="H2585">
+        <v>1</v>
+      </c>
+      <c r="I2585" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2585" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" t="inlineStr">
+        <is>
+          <t>MINAR ISPAT PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B2586" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2586">
+        <v>244709.5</v>
+      </c>
+      <c r="D2586">
+        <v>44047.71000000001</v>
+      </c>
+      <c r="E2586">
+        <v>288757</v>
+      </c>
+      <c r="F2586">
+        <v>35.21</v>
+      </c>
+      <c r="G2586">
+        <v>6950</v>
+      </c>
+      <c r="H2586">
+        <v>2</v>
+      </c>
+      <c r="I2586" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2586" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" t="inlineStr">
+        <is>
+          <t>VGK STEELS</t>
+        </is>
+      </c>
+      <c r="B2587" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2587">
+        <v>307562.5</v>
+      </c>
+      <c r="D2587">
+        <v>65484.45</v>
+      </c>
+      <c r="E2587">
+        <v>429287</v>
+      </c>
+      <c r="F2587">
+        <v>35.15</v>
+      </c>
+      <c r="G2587">
+        <v>8750</v>
+      </c>
+      <c r="H2587">
+        <v>1</v>
+      </c>
+      <c r="I2587" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2587" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" t="inlineStr">
+        <is>
+          <t>UDHAYAN STEELS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2588" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2588">
+        <v>249494</v>
+      </c>
+      <c r="D2588">
+        <v>44908.92</v>
+      </c>
+      <c r="E2588">
+        <v>294403</v>
+      </c>
+      <c r="F2588">
+        <v>35.14</v>
+      </c>
+      <c r="G2588">
+        <v>7100</v>
+      </c>
+      <c r="H2588">
+        <v>1</v>
+      </c>
+      <c r="I2588" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2588" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" t="inlineStr">
+        <is>
+          <t>Kannappan Alloys and Steel Company Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2589" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2589">
+        <v>371636</v>
+      </c>
+      <c r="D2589">
+        <v>66894.48</v>
+      </c>
+      <c r="E2589">
+        <v>438531</v>
+      </c>
+      <c r="F2589">
+        <v>35.06</v>
+      </c>
+      <c r="G2589">
+        <v>10600</v>
+      </c>
+      <c r="H2589">
+        <v>2</v>
+      </c>
+      <c r="I2589" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2589" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" t="inlineStr">
+        <is>
+          <t>KUBAIR STEEL AND POWER LLP</t>
+        </is>
+      </c>
+      <c r="B2590" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2590">
+        <v>127567.5</v>
+      </c>
+      <c r="D2590">
+        <v>22962.16</v>
+      </c>
+      <c r="E2590">
+        <v>150530</v>
+      </c>
+      <c r="F2590">
+        <v>34.95</v>
+      </c>
+      <c r="G2590">
+        <v>3650</v>
+      </c>
+      <c r="H2590">
+        <v>1</v>
+      </c>
+      <c r="I2590" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2590" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" t="inlineStr">
+        <is>
+          <t>PARAGON STEEL DISTRIBUITORS</t>
+        </is>
+      </c>
+      <c r="B2591" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2591">
+        <v>237456</v>
+      </c>
+      <c r="D2591">
+        <v>42742.08</v>
+      </c>
+      <c r="E2591">
+        <v>280198</v>
+      </c>
+      <c r="F2591">
+        <v>34.92</v>
+      </c>
+      <c r="G2591">
+        <v>6800</v>
+      </c>
+      <c r="H2591">
+        <v>2</v>
+      </c>
+      <c r="I2591" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2591" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" t="inlineStr">
+        <is>
+          <t>Sree  Rengaraaj Steel &amp; Alloys (P) Limited</t>
+        </is>
+      </c>
+      <c r="B2592" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2592">
+        <v>177837</v>
+      </c>
+      <c r="D2592">
+        <v>32010.66</v>
+      </c>
+      <c r="E2592">
+        <v>209848</v>
+      </c>
+      <c r="F2592">
+        <v>34.87</v>
+      </c>
+      <c r="G2592">
+        <v>5100</v>
+      </c>
+      <c r="H2592">
+        <v>1</v>
+      </c>
+      <c r="I2592" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2592" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" t="inlineStr">
+        <is>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+        </is>
+      </c>
+      <c r="B2593" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2593">
+        <v>320712</v>
+      </c>
+      <c r="D2593">
+        <v>57728.16</v>
+      </c>
+      <c r="E2593">
+        <v>378440</v>
+      </c>
+      <c r="F2593">
+        <v>34.86</v>
+      </c>
+      <c r="G2593">
+        <v>9200</v>
+      </c>
+      <c r="H2593">
+        <v>2</v>
+      </c>
+      <c r="I2593" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2593" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" t="inlineStr">
+        <is>
+          <t>KANNAPPAN IRON AND STEEL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B2594" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2594">
+        <v>372574</v>
+      </c>
+      <c r="D2594">
+        <v>67107.87</v>
+      </c>
+      <c r="E2594">
+        <v>439929</v>
+      </c>
+      <c r="F2594">
+        <v>34.82</v>
+      </c>
+      <c r="G2594">
+        <v>10700</v>
+      </c>
+      <c r="H2594">
+        <v>1</v>
+      </c>
+      <c r="I2594" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2594" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" t="inlineStr">
+        <is>
+          <t>RDTMT Steels India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2595" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2595">
+        <v>125948</v>
+      </c>
+      <c r="D2595">
+        <v>22670.64</v>
+      </c>
+      <c r="E2595">
+        <v>148619</v>
+      </c>
+      <c r="F2595">
+        <v>34.04</v>
+      </c>
+      <c r="G2595">
+        <v>3700</v>
+      </c>
+      <c r="H2595">
+        <v>1</v>
+      </c>
+      <c r="I2595" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2595" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" t="inlineStr">
+        <is>
+          <t>Pattambi Brothers</t>
+        </is>
+      </c>
+      <c r="B2596" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2596">
+        <v>231713</v>
+      </c>
+      <c r="D2596">
+        <v>41708.34</v>
+      </c>
+      <c r="E2596">
+        <v>273421</v>
+      </c>
+      <c r="F2596">
+        <v>33.34</v>
+      </c>
+      <c r="G2596">
+        <v>6949.999999999999</v>
+      </c>
+      <c r="H2596">
+        <v>2</v>
+      </c>
+      <c r="I2596" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2596" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" t="inlineStr">
+        <is>
+          <t>KUTTIPPULAN IRON AND STEEL COMPANY PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2597" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2597">
+        <v>216492.5</v>
+      </c>
+      <c r="D2597">
+        <v>38968.65</v>
+      </c>
+      <c r="E2597">
+        <v>255461</v>
+      </c>
+      <c r="F2597">
+        <v>31.15</v>
+      </c>
+      <c r="G2597">
+        <v>6950</v>
+      </c>
+      <c r="H2597">
+        <v>1</v>
+      </c>
+      <c r="I2597" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2597" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2598" t="inlineStr">
+        <is>
+          <t>Quartz Powder</t>
+        </is>
+      </c>
+      <c r="C2598">
+        <v>60681.5</v>
+      </c>
+      <c r="D2598">
+        <v>3034.08</v>
+      </c>
+      <c r="E2598">
+        <v>63716</v>
+      </c>
+      <c r="F2598">
+        <v>20.57</v>
+      </c>
+      <c r="G2598">
+        <v>2950</v>
+      </c>
+      <c r="H2598">
+        <v>1</v>
+      </c>
+      <c r="I2598" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2598" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" t="inlineStr">
+        <is>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2599" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2599">
+        <v>66165</v>
+      </c>
+      <c r="D2599">
+        <v>0</v>
+      </c>
+      <c r="F2599">
+        <v>20.05</v>
+      </c>
+      <c r="G2599">
+        <v>3300</v>
+      </c>
+      <c r="H2599">
+        <v>1</v>
+      </c>
+      <c r="I2599" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2599" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" t="inlineStr">
+        <is>
+          <t>BEEPATH CASTINGS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2600" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2600">
+        <v>123480</v>
+      </c>
+      <c r="D2600">
+        <v>22226.4</v>
+      </c>
+      <c r="E2600">
+        <v>145706</v>
+      </c>
+      <c r="F2600">
+        <v>17.64</v>
+      </c>
+      <c r="G2600">
+        <v>7000</v>
+      </c>
+      <c r="H2600">
+        <v>1</v>
+      </c>
+      <c r="I2600" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2600" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" t="inlineStr">
+        <is>
+          <t>KRISHNA STEEL ROLLING MILLS</t>
+        </is>
+      </c>
+      <c r="B2601" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2601">
+        <v>123410</v>
+      </c>
+      <c r="D2601">
+        <v>22213.8</v>
+      </c>
+      <c r="E2601">
+        <v>145624</v>
+      </c>
+      <c r="F2601">
+        <v>17.63</v>
+      </c>
+      <c r="G2601">
+        <v>7000</v>
+      </c>
+      <c r="H2601">
+        <v>1</v>
+      </c>
+      <c r="I2601" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2601" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" t="inlineStr">
+        <is>
+          <t>Pulkit Metals Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2602" t="inlineStr">
+        <is>
+          <t>Tundish Ramming Mix</t>
+        </is>
+      </c>
+      <c r="C2602">
+        <v>418500</v>
+      </c>
+      <c r="D2602">
+        <v>75330</v>
+      </c>
+      <c r="E2602">
+        <v>493830</v>
+      </c>
+      <c r="F2602">
+        <v>15.5</v>
+      </c>
+      <c r="G2602">
+        <v>27000</v>
+      </c>
+      <c r="H2602">
+        <v>2</v>
+      </c>
+      <c r="I2602" t="inlineStr">
+        <is>
+          <t>Abhijit Maloo</t>
+        </is>
+      </c>
+      <c r="J2602" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2603">
+      <c r="A2603" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2603" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2603">
+        <v>100893</v>
+      </c>
+      <c r="D2603">
+        <v>24406.65</v>
+      </c>
+      <c r="E2603">
+        <v>159999</v>
+      </c>
+      <c r="F2603">
+        <v>11.94</v>
+      </c>
+      <c r="G2603">
+        <v>8450</v>
+      </c>
+      <c r="H2603">
+        <v>1</v>
+      </c>
+      <c r="I2603" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2603" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2604">
+      <c r="A2604" t="inlineStr">
+        <is>
+          <t>E RAMAMURTHY MINERALS AND METALS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2604" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2604">
+        <v>44795</v>
+      </c>
+      <c r="D2604">
+        <v>8063.1</v>
+      </c>
+      <c r="E2604">
+        <v>52858</v>
+      </c>
+      <c r="F2604">
+        <v>10.54</v>
+      </c>
+      <c r="G2604">
+        <v>4250</v>
+      </c>
+      <c r="H2604">
+        <v>2</v>
+      </c>
+      <c r="I2604" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2604" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="inlineStr">
+        <is>
+          <t>KAIRAV STEELS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2605" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2605">
+        <v>35768</v>
+      </c>
+      <c r="D2605">
+        <v>5439.17</v>
+      </c>
+      <c r="F2605">
+        <v>10.52</v>
+      </c>
+      <c r="G2605">
+        <v>3400</v>
+      </c>
+      <c r="H2605">
+        <v>2</v>
+      </c>
+      <c r="I2605" t="inlineStr">
+        <is>
+          <t>Sunil Rathi</t>
+        </is>
+      </c>
+      <c r="J2605" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PVT LTD</t>
+        </is>
+      </c>
+      <c r="C2606">
+        <v>34699.5</v>
+      </c>
+      <c r="D2606">
+        <v>0</v>
+      </c>
+      <c r="F2606">
+        <v>7.01</v>
+      </c>
+      <c r="G2606">
         <v>4950</v>
       </c>
-      <c r="H2560">
+      <c r="H2606">
         <v>1</v>
       </c>
-      <c r="I2560" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="J2560" s="2">
-        <v>46174</v>
+      <c r="I2606" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2606" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2607">
+      <c r="A2607" t="inlineStr">
+        <is>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2607" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2607">
+        <v>35880</v>
+      </c>
+      <c r="D2607">
+        <v>18368.1</v>
+      </c>
+      <c r="E2607">
+        <v>120413</v>
+      </c>
+      <c r="F2607">
+        <v>5.2</v>
+      </c>
+      <c r="G2607">
+        <v>6900</v>
+      </c>
+      <c r="H2607">
+        <v>1</v>
+      </c>
+      <c r="I2607" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2607" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" t="inlineStr">
+        <is>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2608" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2608">
+        <v>28897</v>
+      </c>
+      <c r="D2608">
+        <v>3897.9</v>
+      </c>
+      <c r="F2608">
+        <v>4.07</v>
+      </c>
+      <c r="G2608">
+        <v>7099.999999999999</v>
+      </c>
+      <c r="H2608">
+        <v>2</v>
+      </c>
+      <c r="I2608" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2608" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="inlineStr">
+        <is>
+          <t>Speed International India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2609" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2609">
+        <v>900000</v>
+      </c>
+      <c r="D2609">
+        <v>162000</v>
+      </c>
+      <c r="E2609">
+        <v>1062000</v>
+      </c>
+      <c r="F2609">
+        <v>2.5</v>
+      </c>
+      <c r="G2609">
+        <v>360000</v>
+      </c>
+      <c r="H2609">
+        <v>1</v>
+      </c>
+      <c r="I2609" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2609" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2610">
+      <c r="A2610" t="inlineStr">
+        <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2610" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2610">
+        <v>330000</v>
+      </c>
+      <c r="D2610">
+        <v>59400</v>
+      </c>
+      <c r="E2610">
+        <v>389400</v>
+      </c>
+      <c r="F2610">
+        <v>2</v>
+      </c>
+      <c r="G2610">
+        <v>165000</v>
+      </c>
+      <c r="H2610">
+        <v>1</v>
+      </c>
+      <c r="I2610" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2610" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2611">
+      <c r="A2611" t="inlineStr">
+        <is>
+          <t>KANNAPPAN IRON AND STEEL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>Nali Top</t>
+        </is>
+      </c>
+      <c r="C2611">
+        <v>247.5</v>
+      </c>
+      <c r="D2611">
+        <v>0</v>
+      </c>
+      <c r="F2611">
+        <v>0.05</v>
+      </c>
+      <c r="G2611">
+        <v>4950</v>
+      </c>
+      <c r="H2611">
+        <v>1</v>
+      </c>
+      <c r="I2611" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2611" s="2">
+        <v>46204</v>
       </c>
     </row>
   </sheetData>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -98101,6 +98101,9 @@
       <c r="D2583">
         <v>0</v>
       </c>
+      <c r="E2583">
+        <v>155593.62</v>
+      </c>
       <c r="F2583">
         <v>38.22</v>
       </c>
@@ -98706,6 +98709,9 @@
       <c r="D2599">
         <v>0</v>
       </c>
+      <c r="E2599">
+        <v>78074.7</v>
+      </c>
       <c r="F2599">
         <v>20.05</v>
       </c>
@@ -98931,6 +98937,9 @@
       <c r="D2605">
         <v>5439.17</v>
       </c>
+      <c r="E2605">
+        <v>55075.08</v>
+      </c>
       <c r="F2605">
         <v>10.52</v>
       </c>
@@ -98955,12 +98964,20 @@
           <t>SNAM ALLOYS PVT LTD</t>
         </is>
       </c>
+      <c r="B2606" t="inlineStr">
+        <is>
+          <t>Ordinary Ramming Mass</t>
+        </is>
+      </c>
       <c r="C2606">
         <v>34699.5</v>
       </c>
       <c r="D2606">
         <v>0</v>
       </c>
+      <c r="E2606">
+        <v>40945.41</v>
+      </c>
       <c r="F2606">
         <v>7.01</v>
       </c>
@@ -99034,6 +99051,9 @@
       <c r="D2608">
         <v>3897.9</v>
       </c>
+      <c r="E2608">
+        <v>34098.56</v>
+      </c>
       <c r="F2608">
         <v>4.07</v>
       </c>
@@ -99144,6 +99164,9 @@
       </c>
       <c r="D2611">
         <v>0</v>
+      </c>
+      <c r="E2611">
+        <v>292.05</v>
       </c>
       <c r="F2611">
         <v>0.05</v>

--- a/src/customers.xlsx
+++ b/src/customers.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2611"/>
+  <dimension ref="A1:J2617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -96947,7 +96947,7 @@
     <row r="2553">
       <c r="A2553" t="inlineStr">
         <is>
-          <t>A One Ispat Private Ltd</t>
+          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
         </is>
       </c>
       <c r="B2553" t="inlineStr">
@@ -96956,22 +96956,22 @@
         </is>
       </c>
       <c r="C2553">
-        <v>2997837.5</v>
+        <v>3685583</v>
       </c>
       <c r="D2553">
-        <v>539610.8200000001</v>
+        <v>663404.9400000001</v>
       </c>
       <c r="E2553">
-        <v>3537450</v>
+        <v>4348988</v>
       </c>
       <c r="F2553">
-        <v>342.61</v>
+        <v>394.18</v>
       </c>
       <c r="G2553">
-        <v>8750.000000000002</v>
+        <v>9350</v>
       </c>
       <c r="H2553">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I2553" t="inlineStr">
         <is>
@@ -96985,7 +96985,7 @@
     <row r="2554">
       <c r="A2554" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-BALLARY</t>
+          <t>A One Ispat Private Ltd</t>
         </is>
       </c>
       <c r="B2554" t="inlineStr">
@@ -96994,22 +96994,22 @@
         </is>
       </c>
       <c r="C2554">
-        <v>2459237</v>
+        <v>3318700</v>
       </c>
       <c r="D2554">
-        <v>442662.66</v>
+        <v>597366.0800000001</v>
       </c>
       <c r="E2554">
-        <v>2901900</v>
+        <v>3916068</v>
       </c>
       <c r="F2554">
-        <v>263.02</v>
+        <v>379.28</v>
       </c>
       <c r="G2554">
-        <v>9350</v>
+        <v>8750</v>
       </c>
       <c r="H2554">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2554" t="inlineStr">
         <is>
@@ -97023,7 +97023,7 @@
     <row r="2555">
       <c r="A2555" t="inlineStr">
         <is>
-          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
+          <t>Pushpit Steels Private Limited</t>
         </is>
       </c>
       <c r="B2555" t="inlineStr">
@@ -97032,22 +97032,22 @@
         </is>
       </c>
       <c r="C2555">
-        <v>1710536</v>
+        <v>3301104</v>
       </c>
       <c r="D2555">
-        <v>307896.48</v>
+        <v>594198.72</v>
       </c>
       <c r="E2555">
-        <v>2018433</v>
+        <v>3895302</v>
       </c>
       <c r="F2555">
-        <v>169.36</v>
+        <v>340.32</v>
       </c>
       <c r="G2555">
-        <v>10100</v>
+        <v>9700.000000000002</v>
       </c>
       <c r="H2555">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I2555" t="inlineStr">
         <is>
@@ -97061,7 +97061,7 @@
     <row r="2556">
       <c r="A2556" t="inlineStr">
         <is>
-          <t>Pushpit Steels Private Limited</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2556" t="inlineStr">
@@ -97070,22 +97070,22 @@
         </is>
       </c>
       <c r="C2556">
-        <v>1492151</v>
+        <v>2174820</v>
       </c>
       <c r="D2556">
-        <v>268587.18</v>
+        <v>391467.6</v>
       </c>
       <c r="E2556">
-        <v>1760737</v>
+        <v>2566287</v>
       </c>
       <c r="F2556">
-        <v>153.83</v>
+        <v>216.4</v>
       </c>
       <c r="G2556">
-        <v>9700</v>
+        <v>10050</v>
       </c>
       <c r="H2556">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I2556" t="inlineStr">
         <is>
@@ -97099,7 +97099,7 @@
     <row r="2557">
       <c r="A2557" t="inlineStr">
         <is>
-          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+          <t>M S METALS &amp; STEELS PRIVATE LIMITED - TN - Unit 1</t>
         </is>
       </c>
       <c r="B2557" t="inlineStr">
@@ -97108,26 +97108,26 @@
         </is>
       </c>
       <c r="C2557">
-        <v>1258716</v>
+        <v>2116960</v>
       </c>
       <c r="D2557">
-        <v>244798.56</v>
+        <v>381052.8</v>
       </c>
       <c r="E2557">
-        <v>1604792</v>
+        <v>2498013</v>
       </c>
       <c r="F2557">
-        <v>144.68</v>
+        <v>209.6</v>
       </c>
       <c r="G2557">
-        <v>8700</v>
+        <v>10100</v>
       </c>
       <c r="H2557">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2557" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2557" s="2">
@@ -97137,7 +97137,7 @@
     <row r="2558">
       <c r="A2558" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>Adishakti Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2558" t="inlineStr">
@@ -97146,26 +97146,26 @@
         </is>
       </c>
       <c r="C2558">
-        <v>1322781</v>
+        <v>1702662.5</v>
       </c>
       <c r="D2558">
-        <v>238100.58</v>
+        <v>330213.92</v>
       </c>
       <c r="E2558">
-        <v>1560881</v>
+        <v>2164736</v>
       </c>
       <c r="F2558">
-        <v>131.62</v>
+        <v>194.59</v>
       </c>
       <c r="G2558">
-        <v>10050</v>
+        <v>8750</v>
       </c>
       <c r="H2558">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2558" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2558" s="2">
@@ -97175,7 +97175,7 @@
     <row r="2559">
       <c r="A2559" t="inlineStr">
         <is>
-          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
+          <t>KUBAIR STEEL AND POWER LLP</t>
         </is>
       </c>
       <c r="B2559" t="inlineStr">
@@ -97184,22 +97184,22 @@
         </is>
       </c>
       <c r="C2559">
-        <v>1071381</v>
+        <v>1628842.5</v>
       </c>
       <c r="D2559">
-        <v>192848.58</v>
+        <v>293191.66</v>
       </c>
       <c r="E2559">
-        <v>1264230</v>
+        <v>1922035</v>
       </c>
       <c r="F2559">
-        <v>121.06</v>
+        <v>184.05</v>
       </c>
       <c r="G2559">
         <v>8850</v>
       </c>
       <c r="H2559">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2559" t="inlineStr">
         <is>
@@ -97213,7 +97213,7 @@
     <row r="2560">
       <c r="A2560" t="inlineStr">
         <is>
-          <t>Adishakti Smelters Private Limited</t>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2560" t="inlineStr">
@@ -97222,22 +97222,22 @@
         </is>
       </c>
       <c r="C2560">
-        <v>1040112.5</v>
+        <v>1566783</v>
       </c>
       <c r="D2560">
-        <v>210954.92</v>
+        <v>304712.28</v>
       </c>
       <c r="E2560">
-        <v>1382926</v>
+        <v>1997560</v>
       </c>
       <c r="F2560">
-        <v>118.87</v>
+        <v>180.09</v>
       </c>
       <c r="G2560">
-        <v>8750</v>
+        <v>8700</v>
       </c>
       <c r="H2560">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I2560" t="inlineStr">
         <is>
@@ -97251,7 +97251,7 @@
     <row r="2561">
       <c r="A2561" t="inlineStr">
         <is>
-          <t>Arun Vyapar Udyog Private Limited</t>
+          <t>PRIMEGOLD STEEL AND POWER LIMITED</t>
         </is>
       </c>
       <c r="B2561" t="inlineStr">
@@ -97260,22 +97260,22 @@
         </is>
       </c>
       <c r="C2561">
-        <v>1170590</v>
+        <v>1424761.5</v>
       </c>
       <c r="D2561">
-        <v>210706.2</v>
+        <v>256457.07</v>
       </c>
       <c r="E2561">
-        <v>1381296</v>
+        <v>1681219</v>
       </c>
       <c r="F2561">
-        <v>115.9</v>
+        <v>160.99</v>
       </c>
       <c r="G2561">
-        <v>10100</v>
+        <v>8850</v>
       </c>
       <c r="H2561">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I2561" t="inlineStr">
         <is>
@@ -97289,31 +97289,31 @@
     <row r="2562">
       <c r="A2562" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+          <t>Arun Vyapar Udyog Private Limited</t>
         </is>
       </c>
       <c r="B2562" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2562">
-        <v>381412</v>
+        <v>1575903</v>
       </c>
       <c r="D2562">
-        <v>68654.16</v>
+        <v>283662.54</v>
       </c>
       <c r="E2562">
-        <v>450066</v>
+        <v>1859565</v>
       </c>
       <c r="F2562">
-        <v>112.18</v>
+        <v>156.03</v>
       </c>
       <c r="G2562">
-        <v>3400</v>
+        <v>10100</v>
       </c>
       <c r="H2562">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I2562" t="inlineStr">
         <is>
@@ -97327,7 +97327,7 @@
     <row r="2563">
       <c r="A2563" t="inlineStr">
         <is>
-          <t>RDTMT Steels India Pvt Ltd</t>
+          <t>Meenakshi Udyog India Pvt Ltd.</t>
         </is>
       </c>
       <c r="B2563" t="inlineStr">
@@ -97336,26 +97336,26 @@
         </is>
       </c>
       <c r="C2563">
-        <v>967243</v>
+        <v>1479952.5</v>
       </c>
       <c r="D2563">
-        <v>174103.76</v>
+        <v>266391.45</v>
       </c>
       <c r="E2563">
-        <v>1141347</v>
+        <v>1746345</v>
       </c>
       <c r="F2563">
-        <v>111.82</v>
+        <v>151.79</v>
       </c>
       <c r="G2563">
-        <v>8650</v>
+        <v>9750</v>
       </c>
       <c r="H2563">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I2563" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2563" s="2">
@@ -97365,7 +97365,7 @@
     <row r="2564">
       <c r="A2564" t="inlineStr">
         <is>
-          <t>Meenakshi Udyog India Pvt Ltd.</t>
+          <t>RDTMT Steels India Pvt Ltd</t>
         </is>
       </c>
       <c r="B2564" t="inlineStr">
@@ -97374,26 +97374,26 @@
         </is>
       </c>
       <c r="C2564">
-        <v>1089075</v>
+        <v>1310561.5</v>
       </c>
       <c r="D2564">
-        <v>196033.5</v>
+        <v>235901.1</v>
       </c>
       <c r="E2564">
-        <v>1285109</v>
+        <v>1546463</v>
       </c>
       <c r="F2564">
-        <v>111.7</v>
+        <v>151.51</v>
       </c>
       <c r="G2564">
-        <v>9750</v>
+        <v>8650</v>
       </c>
       <c r="H2564">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I2564" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2564" s="2">
@@ -97403,31 +97403,31 @@
     <row r="2565">
       <c r="A2565" t="inlineStr">
         <is>
-          <t>KUBAIR STEEL AND POWER LLP</t>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
         </is>
       </c>
       <c r="B2565" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2565">
-        <v>964561.5</v>
+        <v>492762</v>
       </c>
       <c r="D2565">
-        <v>173621.08</v>
+        <v>88697.16</v>
       </c>
       <c r="E2565">
-        <v>1138183</v>
+        <v>581459</v>
       </c>
       <c r="F2565">
-        <v>108.99</v>
+        <v>144.93</v>
       </c>
       <c r="G2565">
-        <v>8850</v>
+        <v>3400</v>
       </c>
       <c r="H2565">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2565" t="inlineStr">
         <is>
@@ -97441,35 +97441,35 @@
     <row r="2566">
       <c r="A2566" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2566" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2566">
-        <v>453640</v>
+        <v>997905</v>
       </c>
       <c r="D2566">
-        <v>81655.2</v>
+        <v>179622.9</v>
       </c>
       <c r="E2566">
-        <v>535296</v>
+        <v>1177528</v>
       </c>
       <c r="F2566">
-        <v>103.1</v>
+        <v>140.55</v>
       </c>
       <c r="G2566">
-        <v>4400</v>
+        <v>7099.999999999999</v>
       </c>
       <c r="H2566">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2566" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2566" s="2">
@@ -97479,7 +97479,7 @@
     <row r="2567">
       <c r="A2567" t="inlineStr">
         <is>
-          <t>Jai Hind Rolling Mills India Pvt Limited</t>
+          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
         </is>
       </c>
       <c r="B2567" t="inlineStr">
@@ -97488,26 +97488,26 @@
         </is>
       </c>
       <c r="C2567">
-        <v>810660</v>
+        <v>1127614</v>
       </c>
       <c r="D2567">
-        <v>145918.84</v>
+        <v>202970.52</v>
       </c>
       <c r="E2567">
-        <v>956579</v>
+        <v>1330585</v>
       </c>
       <c r="F2567">
-        <v>91.59999999999999</v>
+        <v>130.36</v>
       </c>
       <c r="G2567">
-        <v>8850</v>
+        <v>8650</v>
       </c>
       <c r="H2567">
         <v>4</v>
       </c>
       <c r="I2567" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Shresth Maheshwari</t>
         </is>
       </c>
       <c r="J2567" s="2">
@@ -97517,7 +97517,7 @@
     <row r="2568">
       <c r="A2568" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
+          <t>A ONE STEELS INDIA LIMITED-GBD</t>
         </is>
       </c>
       <c r="B2568" t="inlineStr">
@@ -97526,22 +97526,22 @@
         </is>
       </c>
       <c r="C2568">
-        <v>794200</v>
+        <v>1141448</v>
       </c>
       <c r="D2568">
-        <v>142956</v>
+        <v>205460.64</v>
       </c>
       <c r="E2568">
-        <v>937156</v>
+        <v>1346908</v>
       </c>
       <c r="F2568">
-        <v>90.25</v>
+        <v>129.71</v>
       </c>
       <c r="G2568">
         <v>8800</v>
       </c>
       <c r="H2568">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2568" t="inlineStr">
         <is>
@@ -97555,31 +97555,31 @@
     <row r="2569">
       <c r="A2569" t="inlineStr">
         <is>
-          <t>A ONE STEELS INDIA LIMITED-GBD</t>
+          <t>Shri Tirupati Steel Cast Ltd</t>
         </is>
       </c>
       <c r="B2569" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2569">
-        <v>785664</v>
+        <v>406065</v>
       </c>
       <c r="D2569">
-        <v>141419.52</v>
+        <v>73091.74000000001</v>
       </c>
       <c r="E2569">
-        <v>927083</v>
+        <v>479156</v>
       </c>
       <c r="F2569">
-        <v>89.28</v>
+        <v>117.7</v>
       </c>
       <c r="G2569">
-        <v>8800</v>
+        <v>3450</v>
       </c>
       <c r="H2569">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I2569" t="inlineStr">
         <is>
@@ -97593,7 +97593,7 @@
     <row r="2570">
       <c r="A2570" t="inlineStr">
         <is>
-          <t>S K STEEL TECH PRIVATE LIMITED_x000D_</t>
+          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
         </is>
       </c>
       <c r="B2570" t="inlineStr">
@@ -97602,26 +97602,26 @@
         </is>
       </c>
       <c r="C2570">
-        <v>743640.5</v>
+        <v>961124</v>
       </c>
       <c r="D2570">
-        <v>133855.29</v>
+        <v>173002.32</v>
       </c>
       <c r="E2570">
-        <v>877496</v>
+        <v>1134126</v>
       </c>
       <c r="F2570">
-        <v>85.97</v>
+        <v>104.47</v>
       </c>
       <c r="G2570">
-        <v>8650</v>
+        <v>9200.000000000002</v>
       </c>
       <c r="H2570">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2570" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2570" s="2">
@@ -97631,7 +97631,7 @@
     <row r="2571">
       <c r="A2571" t="inlineStr">
         <is>
-          <t>Shri Tirupati Steel Cast Ltd</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2571" t="inlineStr">
@@ -97640,26 +97640,26 @@
         </is>
       </c>
       <c r="C2571">
-        <v>284590.5</v>
+        <v>453640</v>
       </c>
       <c r="D2571">
-        <v>51226.32</v>
+        <v>81655.2</v>
       </c>
       <c r="E2571">
-        <v>335816</v>
+        <v>535296</v>
       </c>
       <c r="F2571">
-        <v>82.48999999999999</v>
+        <v>103.1</v>
       </c>
       <c r="G2571">
-        <v>3450</v>
+        <v>4400</v>
       </c>
       <c r="H2571">
         <v>5</v>
       </c>
       <c r="I2571" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2571" s="2">
@@ -97669,35 +97669,35 @@
     <row r="2572">
       <c r="A2572" t="inlineStr">
         <is>
-          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
+          <t>KAIRAV STEELS PVT LTD</t>
         </is>
       </c>
       <c r="B2572" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2572">
-        <v>696910.5</v>
+        <v>690207</v>
       </c>
       <c r="D2572">
-        <v>125443.89</v>
+        <v>163442.44</v>
       </c>
       <c r="E2572">
-        <v>822355</v>
+        <v>1071456</v>
       </c>
       <c r="F2572">
-        <v>81.51000000000001</v>
+        <v>100.03</v>
       </c>
       <c r="G2572">
-        <v>8550</v>
+        <v>6900</v>
       </c>
       <c r="H2572">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2572" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Sunil Rathi</t>
         </is>
       </c>
       <c r="J2572" s="2">
@@ -97707,35 +97707,35 @@
     <row r="2573">
       <c r="A2573" t="inlineStr">
         <is>
-          <t>Prakash Sponge Iron &amp; Power Pvt Ltd</t>
+          <t>RDTMT STEELS INDIA PVT LTD-KA</t>
         </is>
       </c>
       <c r="B2573" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2573">
-        <v>503887</v>
+        <v>1077727.5</v>
       </c>
       <c r="D2573">
-        <v>90699.66</v>
+        <v>193990.95</v>
       </c>
       <c r="E2573">
-        <v>594587</v>
+        <v>1271719</v>
       </c>
       <c r="F2573">
-        <v>70.97</v>
+        <v>95.78</v>
       </c>
       <c r="G2573">
-        <v>7100</v>
+        <v>11252.1142200877</v>
       </c>
       <c r="H2573">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2573" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2573" s="2">
@@ -97745,7 +97745,7 @@
     <row r="2574">
       <c r="A2574" t="inlineStr">
         <is>
-          <t>E RAMAMURTHY MINERALS AND METALS PVT LTD</t>
+          <t>Minera Steel &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2574" t="inlineStr">
@@ -97754,22 +97754,22 @@
         </is>
       </c>
       <c r="C2574">
-        <v>546880.5</v>
+        <v>832050</v>
       </c>
       <c r="D2574">
-        <v>98438.48999999999</v>
+        <v>149769</v>
       </c>
       <c r="E2574">
-        <v>645319</v>
+        <v>981820</v>
       </c>
       <c r="F2574">
-        <v>68.78999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="G2574">
-        <v>7950.000000000001</v>
+        <v>9000</v>
       </c>
       <c r="H2574">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2574" t="inlineStr">
         <is>
@@ -97783,7 +97783,7 @@
     <row r="2575">
       <c r="A2575" t="inlineStr">
         <is>
-          <t>TEXCON STEELS LIMITED</t>
+          <t>Jai Hind Rolling Mills India Pvt Limited</t>
         </is>
       </c>
       <c r="B2575" t="inlineStr">
@@ -97792,22 +97792,22 @@
         </is>
       </c>
       <c r="C2575">
-        <v>565069.5</v>
+        <v>810660</v>
       </c>
       <c r="D2575">
-        <v>101712.51</v>
+        <v>145918.84</v>
       </c>
       <c r="E2575">
-        <v>666783</v>
+        <v>956579</v>
       </c>
       <c r="F2575">
-        <v>66.09</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="G2575">
-        <v>8550</v>
+        <v>8850</v>
       </c>
       <c r="H2575">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2575" t="inlineStr">
         <is>
@@ -97821,35 +97821,35 @@
     <row r="2576">
       <c r="A2576" t="inlineStr">
         <is>
-          <t>KAIRAV STEELS PVT LTD</t>
+          <t>A ONE STEELS INDIA LIMITED -HINDUPUR</t>
         </is>
       </c>
       <c r="B2576" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2576">
-        <v>414483</v>
+        <v>794200</v>
       </c>
       <c r="D2576">
-        <v>100002.02</v>
+        <v>142956</v>
       </c>
       <c r="E2576">
-        <v>655569</v>
+        <v>937156</v>
       </c>
       <c r="F2576">
-        <v>60.07</v>
+        <v>90.25</v>
       </c>
       <c r="G2576">
-        <v>6900</v>
+        <v>8800</v>
       </c>
       <c r="H2576">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2576" t="inlineStr">
         <is>
-          <t>Sunil Rathi</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2576" s="2">
@@ -97868,22 +97868,22 @@
         </is>
       </c>
       <c r="C2577">
-        <v>429345</v>
+        <v>647541</v>
       </c>
       <c r="D2577">
-        <v>78585.66</v>
+        <v>117860.94</v>
       </c>
       <c r="E2577">
-        <v>515173</v>
+        <v>772644</v>
       </c>
       <c r="F2577">
-        <v>49.35</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="G2577">
         <v>8700</v>
       </c>
       <c r="H2577">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2577" t="inlineStr">
         <is>
@@ -97897,31 +97897,31 @@
     <row r="2578">
       <c r="A2578" t="inlineStr">
         <is>
-          <t>Minera Steel &amp; Power Pvt Ltd</t>
+          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
         </is>
       </c>
       <c r="B2578" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2578">
-        <v>402120</v>
+        <v>232544</v>
       </c>
       <c r="D2578">
-        <v>72381.60000000001</v>
+        <v>46310.76</v>
       </c>
       <c r="E2578">
-        <v>474502</v>
+        <v>303593</v>
       </c>
       <c r="F2578">
-        <v>44.68000000000001</v>
+        <v>72.67</v>
       </c>
       <c r="G2578">
-        <v>8999.999999999998</v>
+        <v>3200</v>
       </c>
       <c r="H2578">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2578" t="inlineStr">
         <is>
@@ -97935,7 +97935,7 @@
     <row r="2579">
       <c r="A2579" t="inlineStr">
         <is>
-          <t>Keshree Metalurgies Pvt Ltd</t>
+          <t>Prakash Ferrous Industries Pvt Ltd</t>
         </is>
       </c>
       <c r="B2579" t="inlineStr">
@@ -97944,26 +97944,26 @@
         </is>
       </c>
       <c r="C2579">
-        <v>402240</v>
+        <v>695310</v>
       </c>
       <c r="D2579">
-        <v>72403.2</v>
+        <v>125155.8</v>
       </c>
       <c r="E2579">
-        <v>474644</v>
+        <v>820466</v>
       </c>
       <c r="F2579">
-        <v>41.9</v>
+        <v>70.94999999999999</v>
       </c>
       <c r="G2579">
-        <v>9600</v>
+        <v>9800.000000000002</v>
       </c>
       <c r="H2579">
         <v>2</v>
       </c>
       <c r="I2579" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2579" s="2">
@@ -97973,35 +97973,35 @@
     <row r="2580">
       <c r="A2580" t="inlineStr">
         <is>
-          <t>Sri M.S.T. Smelters Private Limited</t>
+          <t>PARAGON STEEL DISTRIBUITORS</t>
         </is>
       </c>
       <c r="B2580" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2580">
-        <v>346951.5</v>
+        <v>476612</v>
       </c>
       <c r="D2580">
-        <v>62451.27</v>
+        <v>85790.16</v>
       </c>
       <c r="E2580">
-        <v>409403</v>
+        <v>562402</v>
       </c>
       <c r="F2580">
-        <v>40.11</v>
+        <v>70.09</v>
       </c>
       <c r="G2580">
-        <v>8650</v>
+        <v>6800</v>
       </c>
       <c r="H2580">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2580" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2580" s="2">
@@ -98011,28 +98011,28 @@
     <row r="2581">
       <c r="A2581" t="inlineStr">
         <is>
-          <t>INDUS TMT INDUSTRIES LTD.</t>
+          <t>UDHAYAN STEELS PVT LTD</t>
         </is>
       </c>
       <c r="B2581" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2581">
-        <v>388291</v>
+        <v>497355</v>
       </c>
       <c r="D2581">
-        <v>69892.38</v>
+        <v>89523.89999999999</v>
       </c>
       <c r="E2581">
-        <v>458184</v>
+        <v>586879</v>
       </c>
       <c r="F2581">
-        <v>40.03</v>
+        <v>70.05</v>
       </c>
       <c r="G2581">
-        <v>9700</v>
+        <v>7100</v>
       </c>
       <c r="H2581">
         <v>2</v>
@@ -98058,22 +98058,22 @@
         </is>
       </c>
       <c r="C2582">
-        <v>168895</v>
+        <v>293930</v>
       </c>
       <c r="D2582">
-        <v>30401.1</v>
+        <v>52907.39999999999</v>
       </c>
       <c r="E2582">
-        <v>199296</v>
+        <v>346837</v>
       </c>
       <c r="F2582">
-        <v>39.74</v>
+        <v>69.16</v>
       </c>
       <c r="G2582">
         <v>4250</v>
       </c>
       <c r="H2582">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2582" t="inlineStr">
         <is>
@@ -98087,31 +98087,31 @@
     <row r="2583">
       <c r="A2583" t="inlineStr">
         <is>
-          <t>Adishakti Smelters Private Limited</t>
+          <t>E RAMAMURTHY MINERALS AND METALS PVT LTD</t>
         </is>
       </c>
       <c r="B2583" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2583">
-        <v>131859</v>
+        <v>546880.5</v>
       </c>
       <c r="D2583">
-        <v>0</v>
+        <v>98438.48999999999</v>
       </c>
       <c r="E2583">
-        <v>155593.62</v>
+        <v>645319</v>
       </c>
       <c r="F2583">
-        <v>38.22</v>
+        <v>68.78999999999999</v>
       </c>
       <c r="G2583">
-        <v>3450</v>
+        <v>7950.000000000001</v>
       </c>
       <c r="H2583">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2583" t="inlineStr">
         <is>
@@ -98125,35 +98125,35 @@
     <row r="2584">
       <c r="A2584" t="inlineStr">
         <is>
-          <t>M.A.STEELS (P) LTD</t>
+          <t>TEXCON STEELS LIMITED</t>
         </is>
       </c>
       <c r="B2584" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2584">
-        <v>246169</v>
+        <v>565069.5</v>
       </c>
       <c r="D2584">
-        <v>44310.42</v>
+        <v>101712.51</v>
       </c>
       <c r="E2584">
-        <v>290479</v>
+        <v>666783</v>
       </c>
       <c r="F2584">
-        <v>35.42</v>
+        <v>66.09</v>
       </c>
       <c r="G2584">
-        <v>6950</v>
+        <v>8550</v>
       </c>
       <c r="H2584">
         <v>2</v>
       </c>
       <c r="I2584" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2584" s="2">
@@ -98163,35 +98163,35 @@
     <row r="2585">
       <c r="A2585" t="inlineStr">
         <is>
-          <t>Sugna Sponge &amp; Power Pvt Ltd</t>
+          <t>Pattambi Brothers</t>
         </is>
       </c>
       <c r="B2585" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2585">
-        <v>113088</v>
+        <v>442576</v>
       </c>
       <c r="D2585">
-        <v>24808.68</v>
+        <v>79663.67999999999</v>
       </c>
       <c r="E2585">
-        <v>162635</v>
+        <v>522239</v>
       </c>
       <c r="F2585">
-        <v>35.34</v>
+        <v>63.68</v>
       </c>
       <c r="G2585">
-        <v>3200</v>
+        <v>6950.000000000001</v>
       </c>
       <c r="H2585">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2585" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2585" s="2">
@@ -98201,35 +98201,35 @@
     <row r="2586">
       <c r="A2586" t="inlineStr">
         <is>
-          <t>MINAR ISPAT PVT. LTD</t>
+          <t>Keshree Metalurgies Pvt Ltd</t>
         </is>
       </c>
       <c r="B2586" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2586">
-        <v>244709.5</v>
+        <v>402240</v>
       </c>
       <c r="D2586">
-        <v>44047.71000000001</v>
+        <v>72403.2</v>
       </c>
       <c r="E2586">
-        <v>288757</v>
+        <v>474644</v>
       </c>
       <c r="F2586">
-        <v>35.21</v>
+        <v>41.9</v>
       </c>
       <c r="G2586">
-        <v>6950</v>
+        <v>9600</v>
       </c>
       <c r="H2586">
         <v>2</v>
       </c>
       <c r="I2586" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2586" s="2">
@@ -98239,7 +98239,7 @@
     <row r="2587">
       <c r="A2587" t="inlineStr">
         <is>
-          <t>VGK STEELS</t>
+          <t>VMC Steel and Alloys Industry</t>
         </is>
       </c>
       <c r="B2587" t="inlineStr">
@@ -98248,26 +98248,26 @@
         </is>
       </c>
       <c r="C2587">
-        <v>307562.5</v>
+        <v>426195</v>
       </c>
       <c r="D2587">
-        <v>65484.45</v>
+        <v>76715.10000000001</v>
       </c>
       <c r="E2587">
-        <v>429287</v>
+        <v>502910</v>
       </c>
       <c r="F2587">
-        <v>35.15</v>
+        <v>40.59</v>
       </c>
       <c r="G2587">
-        <v>8750</v>
+        <v>10500</v>
       </c>
       <c r="H2587">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2587" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2587" s="2">
@@ -98277,35 +98277,35 @@
     <row r="2588">
       <c r="A2588" t="inlineStr">
         <is>
-          <t>UDHAYAN STEELS PVT LTD</t>
+          <t>Sri M.S.T. Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2588" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2588">
-        <v>249494</v>
+        <v>346951.5</v>
       </c>
       <c r="D2588">
-        <v>44908.92</v>
+        <v>62451.27</v>
       </c>
       <c r="E2588">
-        <v>294403</v>
+        <v>409403</v>
       </c>
       <c r="F2588">
-        <v>35.14</v>
+        <v>40.11</v>
       </c>
       <c r="G2588">
-        <v>7100</v>
+        <v>8650</v>
       </c>
       <c r="H2588">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2588" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2588" s="2">
@@ -98315,7 +98315,7 @@
     <row r="2589">
       <c r="A2589" t="inlineStr">
         <is>
-          <t>Kannappan Alloys and Steel Company Pvt Ltd</t>
+          <t>INDUS TMT INDUSTRIES LTD.</t>
         </is>
       </c>
       <c r="B2589" t="inlineStr">
@@ -98324,19 +98324,19 @@
         </is>
       </c>
       <c r="C2589">
-        <v>371636</v>
+        <v>388291</v>
       </c>
       <c r="D2589">
-        <v>66894.48</v>
+        <v>69892.38</v>
       </c>
       <c r="E2589">
-        <v>438531</v>
+        <v>458184</v>
       </c>
       <c r="F2589">
-        <v>35.06</v>
+        <v>40.03</v>
       </c>
       <c r="G2589">
-        <v>10600</v>
+        <v>9700</v>
       </c>
       <c r="H2589">
         <v>2</v>
@@ -98353,7 +98353,7 @@
     <row r="2590">
       <c r="A2590" t="inlineStr">
         <is>
-          <t>KUBAIR STEEL AND POWER LLP</t>
+          <t>Adishakti Smelters Private Limited</t>
         </is>
       </c>
       <c r="B2590" t="inlineStr">
@@ -98362,22 +98362,22 @@
         </is>
       </c>
       <c r="C2590">
-        <v>127567.5</v>
+        <v>131859</v>
       </c>
       <c r="D2590">
-        <v>22962.16</v>
+        <v>0</v>
       </c>
       <c r="E2590">
-        <v>150530</v>
+        <v>155593.62</v>
       </c>
       <c r="F2590">
-        <v>34.95</v>
+        <v>38.22</v>
       </c>
       <c r="G2590">
-        <v>3650</v>
+        <v>3450</v>
       </c>
       <c r="H2590">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2590" t="inlineStr">
         <is>
@@ -98391,7 +98391,7 @@
     <row r="2591">
       <c r="A2591" t="inlineStr">
         <is>
-          <t>PARAGON STEEL DISTRIBUITORS</t>
+          <t>M.A.STEELS (P) LTD</t>
         </is>
       </c>
       <c r="B2591" t="inlineStr">
@@ -98400,26 +98400,26 @@
         </is>
       </c>
       <c r="C2591">
-        <v>237456</v>
+        <v>246169</v>
       </c>
       <c r="D2591">
-        <v>42742.08</v>
+        <v>44310.42</v>
       </c>
       <c r="E2591">
-        <v>280198</v>
+        <v>290479</v>
       </c>
       <c r="F2591">
-        <v>34.92</v>
+        <v>35.42</v>
       </c>
       <c r="G2591">
-        <v>6800</v>
+        <v>6950</v>
       </c>
       <c r="H2591">
         <v>2</v>
       </c>
       <c r="I2591" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2591" s="2">
@@ -98429,35 +98429,35 @@
     <row r="2592">
       <c r="A2592" t="inlineStr">
         <is>
-          <t>Sree  Rengaraaj Steel &amp; Alloys (P) Limited</t>
+          <t>MINAR ISPAT PVT. LTD</t>
         </is>
       </c>
       <c r="B2592" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2592">
-        <v>177837</v>
+        <v>244709.5</v>
       </c>
       <c r="D2592">
-        <v>32010.66</v>
+        <v>44047.71000000001</v>
       </c>
       <c r="E2592">
-        <v>209848</v>
+        <v>288757</v>
       </c>
       <c r="F2592">
-        <v>34.87</v>
+        <v>35.21</v>
       </c>
       <c r="G2592">
-        <v>5100</v>
+        <v>6950</v>
       </c>
       <c r="H2592">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2592" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2592" s="2">
@@ -98467,7 +98467,7 @@
     <row r="2593">
       <c r="A2593" t="inlineStr">
         <is>
-          <t>M S METALS AND STEELS PVT LTD (ANCHEPALYA)</t>
+          <t>VGK STEELS</t>
         </is>
       </c>
       <c r="B2593" t="inlineStr">
@@ -98476,26 +98476,26 @@
         </is>
       </c>
       <c r="C2593">
-        <v>320712</v>
+        <v>307562.5</v>
       </c>
       <c r="D2593">
-        <v>57728.16</v>
+        <v>65484.45</v>
       </c>
       <c r="E2593">
-        <v>378440</v>
+        <v>429287</v>
       </c>
       <c r="F2593">
-        <v>34.86</v>
+        <v>35.15</v>
       </c>
       <c r="G2593">
-        <v>9200</v>
+        <v>8750</v>
       </c>
       <c r="H2593">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2593" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2593" s="2">
@@ -98505,7 +98505,7 @@
     <row r="2594">
       <c r="A2594" t="inlineStr">
         <is>
-          <t>KANNAPPAN IRON AND STEEL COMPANY LIMITED</t>
+          <t>Kannappan Alloys and Steel Company Pvt Ltd</t>
         </is>
       </c>
       <c r="B2594" t="inlineStr">
@@ -98514,22 +98514,22 @@
         </is>
       </c>
       <c r="C2594">
-        <v>372574</v>
+        <v>371636</v>
       </c>
       <c r="D2594">
-        <v>67107.87</v>
+        <v>66894.48</v>
       </c>
       <c r="E2594">
-        <v>439929</v>
+        <v>438531</v>
       </c>
       <c r="F2594">
-        <v>34.82</v>
+        <v>35.06</v>
       </c>
       <c r="G2594">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="H2594">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2594" t="inlineStr">
         <is>
@@ -98543,7 +98543,7 @@
     <row r="2595">
       <c r="A2595" t="inlineStr">
         <is>
-          <t>RDTMT Steels India Pvt Ltd</t>
+          <t>KUBAIR STEEL AND POWER LLP</t>
         </is>
       </c>
       <c r="B2595" t="inlineStr">
@@ -98552,19 +98552,19 @@
         </is>
       </c>
       <c r="C2595">
-        <v>125948</v>
+        <v>127567.5</v>
       </c>
       <c r="D2595">
-        <v>22670.64</v>
+        <v>22962.16</v>
       </c>
       <c r="E2595">
-        <v>148619</v>
+        <v>150530</v>
       </c>
       <c r="F2595">
-        <v>34.04</v>
+        <v>34.95</v>
       </c>
       <c r="G2595">
-        <v>3700</v>
+        <v>3650</v>
       </c>
       <c r="H2595">
         <v>1</v>
@@ -98581,35 +98581,35 @@
     <row r="2596">
       <c r="A2596" t="inlineStr">
         <is>
-          <t>Pattambi Brothers</t>
+          <t>Sree  Rengaraaj Steel &amp; Alloys (P) Limited</t>
         </is>
       </c>
       <c r="B2596" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2596">
-        <v>231713</v>
+        <v>177837</v>
       </c>
       <c r="D2596">
-        <v>41708.34</v>
+        <v>32010.66</v>
       </c>
       <c r="E2596">
-        <v>273421</v>
+        <v>209848</v>
       </c>
       <c r="F2596">
-        <v>33.34</v>
+        <v>34.87</v>
       </c>
       <c r="G2596">
-        <v>6949.999999999999</v>
+        <v>5100</v>
       </c>
       <c r="H2596">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2596" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2596" s="2">
@@ -98619,35 +98619,35 @@
     <row r="2597">
       <c r="A2597" t="inlineStr">
         <is>
-          <t>KUTTIPPULAN IRON AND STEEL COMPANY PVT LTD</t>
+          <t>KANNAPPAN IRON AND STEEL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="B2597" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2597">
-        <v>216492.5</v>
+        <v>372574</v>
       </c>
       <c r="D2597">
-        <v>38968.65</v>
+        <v>67107.87</v>
       </c>
       <c r="E2597">
-        <v>255461</v>
+        <v>439929</v>
       </c>
       <c r="F2597">
-        <v>31.15</v>
+        <v>34.82</v>
       </c>
       <c r="G2597">
-        <v>6950</v>
+        <v>10700</v>
       </c>
       <c r="H2597">
         <v>1</v>
       </c>
       <c r="I2597" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2597" s="2">
@@ -98657,35 +98657,35 @@
     <row r="2598">
       <c r="A2598" t="inlineStr">
         <is>
-          <t>Mahrishi Meltchems Pvt Ltd</t>
+          <t>SREE PALANIANDAVAR ALLOYS AND STEELS PVT LTD</t>
         </is>
       </c>
       <c r="B2598" t="inlineStr">
         <is>
-          <t>Quartz Powder</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2598">
-        <v>60681.5</v>
+        <v>241790.5</v>
       </c>
       <c r="D2598">
-        <v>3034.08</v>
+        <v>43522.29</v>
       </c>
       <c r="E2598">
-        <v>63716</v>
+        <v>285313</v>
       </c>
       <c r="F2598">
-        <v>20.57</v>
+        <v>34.79</v>
       </c>
       <c r="G2598">
-        <v>2950</v>
+        <v>6950</v>
       </c>
       <c r="H2598">
         <v>1</v>
       </c>
       <c r="I2598" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2598" s="2">
@@ -98695,35 +98695,35 @@
     <row r="2599">
       <c r="A2599" t="inlineStr">
         <is>
-          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+          <t>RDTMT Steels India Pvt Ltd</t>
         </is>
       </c>
       <c r="B2599" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2599">
-        <v>66165</v>
+        <v>125948</v>
       </c>
       <c r="D2599">
-        <v>0</v>
+        <v>22670.64</v>
       </c>
       <c r="E2599">
-        <v>78074.7</v>
+        <v>148619</v>
       </c>
       <c r="F2599">
-        <v>20.05</v>
+        <v>34.04</v>
       </c>
       <c r="G2599">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="H2599">
         <v>1</v>
       </c>
       <c r="I2599" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2599" s="2">
@@ -98733,7 +98733,7 @@
     <row r="2600">
       <c r="A2600" t="inlineStr">
         <is>
-          <t>BEEPATH CASTINGS PVT LTD</t>
+          <t>KUTTIPPULAN IRON AND STEEL COMPANY PVT LTD</t>
         </is>
       </c>
       <c r="B2600" t="inlineStr">
@@ -98742,19 +98742,19 @@
         </is>
       </c>
       <c r="C2600">
-        <v>123480</v>
+        <v>216492.5</v>
       </c>
       <c r="D2600">
-        <v>22226.4</v>
+        <v>38968.65</v>
       </c>
       <c r="E2600">
-        <v>145706</v>
+        <v>255461</v>
       </c>
       <c r="F2600">
-        <v>17.64</v>
+        <v>31.15</v>
       </c>
       <c r="G2600">
-        <v>7000</v>
+        <v>6950</v>
       </c>
       <c r="H2600">
         <v>1</v>
@@ -98771,7 +98771,7 @@
     <row r="2601">
       <c r="A2601" t="inlineStr">
         <is>
-          <t>KRISHNA STEEL ROLLING MILLS</t>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B2601" t="inlineStr">
@@ -98780,26 +98780,26 @@
         </is>
       </c>
       <c r="C2601">
-        <v>123410</v>
+        <v>182182</v>
       </c>
       <c r="D2601">
-        <v>22213.8</v>
+        <v>35617.24</v>
       </c>
       <c r="E2601">
-        <v>145624</v>
+        <v>233491</v>
       </c>
       <c r="F2601">
-        <v>17.63</v>
+        <v>21.56</v>
       </c>
       <c r="G2601">
-        <v>7000</v>
+        <v>8450</v>
       </c>
       <c r="H2601">
         <v>1</v>
       </c>
       <c r="I2601" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2601" s="2">
@@ -98809,35 +98809,35 @@
     <row r="2602">
       <c r="A2602" t="inlineStr">
         <is>
-          <t>Pulkit Metals Pvt Ltd</t>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
         </is>
       </c>
       <c r="B2602" t="inlineStr">
         <is>
-          <t>Tundish Ramming Mix</t>
+          <t>Quartz Powder</t>
         </is>
       </c>
       <c r="C2602">
-        <v>418500</v>
+        <v>60681.5</v>
       </c>
       <c r="D2602">
-        <v>75330</v>
+        <v>3034.08</v>
       </c>
       <c r="E2602">
-        <v>493830</v>
+        <v>63716</v>
       </c>
       <c r="F2602">
-        <v>15.5</v>
+        <v>20.57</v>
       </c>
       <c r="G2602">
-        <v>27000</v>
+        <v>2950</v>
       </c>
       <c r="H2602">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2602" t="inlineStr">
         <is>
-          <t>Abhijit Maloo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2602" s="2">
@@ -98847,35 +98847,35 @@
     <row r="2603">
       <c r="A2603" t="inlineStr">
         <is>
-          <t>SNAM ALLOYS PVT LTD</t>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
         </is>
       </c>
       <c r="B2603" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2603">
-        <v>100893</v>
+        <v>66165</v>
       </c>
       <c r="D2603">
-        <v>24406.65</v>
+        <v>0</v>
       </c>
       <c r="E2603">
-        <v>159999</v>
+        <v>78074.7</v>
       </c>
       <c r="F2603">
-        <v>11.94</v>
+        <v>20.05</v>
       </c>
       <c r="G2603">
-        <v>8450</v>
+        <v>3300</v>
       </c>
       <c r="H2603">
         <v>1</v>
       </c>
       <c r="I2603" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2603" s="2">
@@ -98885,35 +98885,35 @@
     <row r="2604">
       <c r="A2604" t="inlineStr">
         <is>
-          <t>E RAMAMURTHY MINERALS AND METALS PVT LTD</t>
+          <t>BEEPATH CASTINGS PVT LTD</t>
         </is>
       </c>
       <c r="B2604" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2604">
-        <v>44795</v>
+        <v>123480</v>
       </c>
       <c r="D2604">
-        <v>8063.1</v>
+        <v>22226.4</v>
       </c>
       <c r="E2604">
-        <v>52858</v>
+        <v>145706</v>
       </c>
       <c r="F2604">
-        <v>10.54</v>
+        <v>17.64</v>
       </c>
       <c r="G2604">
-        <v>4250</v>
+        <v>7000</v>
       </c>
       <c r="H2604">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2604" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2604" s="2">
@@ -98923,35 +98923,35 @@
     <row r="2605">
       <c r="A2605" t="inlineStr">
         <is>
-          <t>KAIRAV STEELS PVT LTD</t>
+          <t>KRISHNA STEEL ROLLING MILLS</t>
         </is>
       </c>
       <c r="B2605" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Boric Acid Premix</t>
         </is>
       </c>
       <c r="C2605">
-        <v>35768</v>
+        <v>123410</v>
       </c>
       <c r="D2605">
-        <v>5439.17</v>
+        <v>22213.8</v>
       </c>
       <c r="E2605">
-        <v>55075.08</v>
+        <v>145624</v>
       </c>
       <c r="F2605">
-        <v>10.52</v>
+        <v>17.63</v>
       </c>
       <c r="G2605">
-        <v>3400</v>
+        <v>7000</v>
       </c>
       <c r="H2605">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2605" t="inlineStr">
         <is>
-          <t>Sunil Rathi</t>
+          <t>Vishnu Kankani</t>
         </is>
       </c>
       <c r="J2605" s="2">
@@ -98966,26 +98966,26 @@
       </c>
       <c r="B2606" t="inlineStr">
         <is>
-          <t>Ordinary Ramming Mass</t>
+          <t>Boron Oxide Premix</t>
         </is>
       </c>
       <c r="C2606">
-        <v>34699.5</v>
+        <v>131735.5</v>
       </c>
       <c r="D2606">
-        <v>0</v>
+        <v>23712.39</v>
       </c>
       <c r="E2606">
-        <v>40945.41</v>
+        <v>155448</v>
       </c>
       <c r="F2606">
-        <v>7.01</v>
+        <v>15.59</v>
       </c>
       <c r="G2606">
-        <v>4950</v>
+        <v>8450</v>
       </c>
       <c r="H2606">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2606" t="inlineStr">
         <is>
@@ -98999,35 +98999,35 @@
     <row r="2607">
       <c r="A2607" t="inlineStr">
         <is>
-          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+          <t>Pulkit Metals Pvt Ltd</t>
         </is>
       </c>
       <c r="B2607" t="inlineStr">
         <is>
-          <t>Nali Top</t>
+          <t>Tundish Ramming Mix</t>
         </is>
       </c>
       <c r="C2607">
-        <v>35880</v>
+        <v>418500</v>
       </c>
       <c r="D2607">
-        <v>18368.1</v>
+        <v>75330</v>
       </c>
       <c r="E2607">
-        <v>120413</v>
+        <v>493830</v>
       </c>
       <c r="F2607">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="G2607">
-        <v>6900</v>
+        <v>27000</v>
       </c>
       <c r="H2607">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2607" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Abhijit Maloo</t>
         </is>
       </c>
       <c r="J2607" s="2">
@@ -99037,7 +99037,7 @@
     <row r="2608">
       <c r="A2608" t="inlineStr">
         <is>
-          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+          <t>SNAM ALLOYS PVT LTD</t>
         </is>
       </c>
       <c r="B2608" t="inlineStr">
@@ -99046,26 +99046,26 @@
         </is>
       </c>
       <c r="C2608">
-        <v>28897</v>
+        <v>100893</v>
       </c>
       <c r="D2608">
-        <v>3897.9</v>
+        <v>24406.65</v>
       </c>
       <c r="E2608">
-        <v>34098.56</v>
+        <v>159999</v>
       </c>
       <c r="F2608">
-        <v>4.07</v>
+        <v>11.94</v>
       </c>
       <c r="G2608">
-        <v>7099.999999999999</v>
+        <v>8450</v>
       </c>
       <c r="H2608">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2608" t="inlineStr">
         <is>
-          <t>Vishnu Kankani</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2608" s="2">
@@ -99075,35 +99075,35 @@
     <row r="2609">
       <c r="A2609" t="inlineStr">
         <is>
-          <t>Speed International India Pvt Ltd</t>
+          <t>E RAMAMURTHY MINERALS AND METALS PVT LTD</t>
         </is>
       </c>
       <c r="B2609" t="inlineStr">
         <is>
-          <t>Boron Oxide Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2609">
-        <v>900000</v>
+        <v>44795</v>
       </c>
       <c r="D2609">
-        <v>162000</v>
+        <v>8063.1</v>
       </c>
       <c r="E2609">
-        <v>1062000</v>
+        <v>52858</v>
       </c>
       <c r="F2609">
-        <v>2.5</v>
+        <v>10.54</v>
       </c>
       <c r="G2609">
-        <v>360000</v>
+        <v>4250</v>
       </c>
       <c r="H2609">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2609" t="inlineStr">
         <is>
-          <t>Shresth Maheshwari</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="J2609" s="2">
@@ -99113,35 +99113,35 @@
     <row r="2610">
       <c r="A2610" t="inlineStr">
         <is>
-          <t>Mahrishi Meltchems Pvt Ltd</t>
+          <t>KAIRAV STEELS PVT LTD</t>
         </is>
       </c>
       <c r="B2610" t="inlineStr">
         <is>
-          <t>Boric Acid Premix</t>
+          <t>Nali Top</t>
         </is>
       </c>
       <c r="C2610">
-        <v>330000</v>
+        <v>35768</v>
       </c>
       <c r="D2610">
-        <v>59400</v>
+        <v>5439.17</v>
       </c>
       <c r="E2610">
-        <v>389400</v>
+        <v>55075.08</v>
       </c>
       <c r="F2610">
+        <v>10.52</v>
+      </c>
+      <c r="G2610">
+        <v>3400</v>
+      </c>
+      <c r="H2610">
         <v>2</v>
       </c>
-      <c r="G2610">
-        <v>165000</v>
-      </c>
-      <c r="H2610">
-        <v>1</v>
-      </c>
       <c r="I2610" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Sunil Rathi</t>
         </is>
       </c>
       <c r="J2610" s="2">
@@ -99151,38 +99151,266 @@
     <row r="2611">
       <c r="A2611" t="inlineStr">
         <is>
+          <t>Mahrishi Meltchems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2611">
+        <v>1485000</v>
+      </c>
+      <c r="D2611">
+        <v>267300</v>
+      </c>
+      <c r="E2611">
+        <v>1752300</v>
+      </c>
+      <c r="F2611">
+        <v>9</v>
+      </c>
+      <c r="G2611">
+        <v>165000</v>
+      </c>
+      <c r="H2611">
+        <v>2</v>
+      </c>
+      <c r="I2611" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2611" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2612">
+      <c r="A2612" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2612" t="inlineStr">
+        <is>
+          <t>Ordinary Ramming Mass</t>
+        </is>
+      </c>
+      <c r="C2612">
+        <v>34699.5</v>
+      </c>
+      <c r="D2612">
+        <v>0</v>
+      </c>
+      <c r="E2612">
+        <v>40945.41</v>
+      </c>
+      <c r="F2612">
+        <v>7.01</v>
+      </c>
+      <c r="G2612">
+        <v>4950</v>
+      </c>
+      <c r="H2612">
+        <v>1</v>
+      </c>
+      <c r="I2612" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2612" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2613">
+      <c r="A2613" t="inlineStr">
+        <is>
+          <t>PREMIUM FERRO ALLOYS LIMITED</t>
+        </is>
+      </c>
+      <c r="B2613" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2613">
+        <v>35880</v>
+      </c>
+      <c r="D2613">
+        <v>18368.1</v>
+      </c>
+      <c r="E2613">
+        <v>120413</v>
+      </c>
+      <c r="F2613">
+        <v>5.2</v>
+      </c>
+      <c r="G2613">
+        <v>6900</v>
+      </c>
+      <c r="H2613">
+        <v>1</v>
+      </c>
+      <c r="I2613" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2613" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2614">
+      <c r="A2614" t="inlineStr">
+        <is>
+          <t>GOVAAN STEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2614" t="inlineStr">
+        <is>
+          <t>Boric Acid Premix</t>
+        </is>
+      </c>
+      <c r="C2614">
+        <v>28897</v>
+      </c>
+      <c r="D2614">
+        <v>3897.9</v>
+      </c>
+      <c r="E2614">
+        <v>34098.56</v>
+      </c>
+      <c r="F2614">
+        <v>4.07</v>
+      </c>
+      <c r="G2614">
+        <v>7099.999999999999</v>
+      </c>
+      <c r="H2614">
+        <v>2</v>
+      </c>
+      <c r="I2614" t="inlineStr">
+        <is>
+          <t>Vishnu Kankani</t>
+        </is>
+      </c>
+      <c r="J2614" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2615">
+      <c r="A2615" t="inlineStr">
+        <is>
+          <t>SNAM ALLOYS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2615" t="inlineStr">
+        <is>
+          <t>Ordinary Ramming Mass</t>
+        </is>
+      </c>
+      <c r="C2615">
+        <v>15691.5</v>
+      </c>
+      <c r="D2615">
+        <v>0</v>
+      </c>
+      <c r="E2615">
+        <v>18515.97</v>
+      </c>
+      <c r="F2615">
+        <v>3.17</v>
+      </c>
+      <c r="G2615">
+        <v>4950</v>
+      </c>
+      <c r="H2615">
+        <v>1</v>
+      </c>
+      <c r="I2615" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2615" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" t="inlineStr">
+        <is>
+          <t>Speed International India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2616" t="inlineStr">
+        <is>
+          <t>Boron Oxide Premix</t>
+        </is>
+      </c>
+      <c r="C2616">
+        <v>900000</v>
+      </c>
+      <c r="D2616">
+        <v>162000</v>
+      </c>
+      <c r="E2616">
+        <v>1062000</v>
+      </c>
+      <c r="F2616">
+        <v>2</v>
+      </c>
+      <c r="G2616">
+        <v>450000</v>
+      </c>
+      <c r="H2616">
+        <v>1</v>
+      </c>
+      <c r="I2616" t="inlineStr">
+        <is>
+          <t>Shresth Maheshwari</t>
+        </is>
+      </c>
+      <c r="J2616" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" t="inlineStr">
+        <is>
           <t>KANNAPPAN IRON AND STEEL COMPANY LIMITED</t>
         </is>
       </c>
-      <c r="B2611" t="inlineStr">
+      <c r="B2617" t="inlineStr">
         <is>
           <t>Nali Top</t>
         </is>
       </c>
-      <c r="C2611">
+      <c r="C2617">
         <v>247.5</v>
       </c>
-      <c r="D2611">
+      <c r="D2617">
         <v>0</v>
       </c>
-      <c r="E2611">
+      <c r="E2617">
         <v>292.05</v>
       </c>
-      <c r="F2611">
+      <c r="F2617">
         <v>0.05</v>
       </c>
-      <c r="G2611">
+      <c r="G2617">
         <v>4950</v>
       </c>
-      <c r="H2611">
+      <c r="H2617">
         <v>1</v>
       </c>
-      <c r="I2611" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="J2611" s="2">
+      <c r="I2617" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="J2617" s="2">
         <v>46204</v>
       </c>
     </row>
